--- a/Outcome/Publish/figure_data/fig1.xlsx
+++ b/Outcome/Publish/figure_data/fig1.xlsx
@@ -30502,7 +30502,7 @@
         <v>59</v>
       </c>
       <c r="C44" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -30829,7 +30829,7 @@
         <v>1.54747733185568</v>
       </c>
       <c r="D24" t="n">
-        <v>1.20316782688397</v>
+        <v>1.18225686080645</v>
       </c>
     </row>
     <row r="25">
@@ -30843,7 +30843,7 @@
         <v>0.769759973291176</v>
       </c>
       <c r="D25" t="n">
-        <v>0.00852283888286707</v>
+        <v>0.0153517048076012</v>
       </c>
     </row>
     <row r="26">
@@ -30857,7 +30857,7 @@
         <v>0.764211580412933</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>0.00702676749479686</v>
       </c>
     </row>
     <row r="27">
@@ -30867,8 +30867,12 @@
       <c r="B27" t="n">
         <v>2016</v>
       </c>
-      <c r="C27"/>
-      <c r="D27"/>
+      <c r="C27" t="n">
+        <v>0.759528389986353</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
@@ -30881,7 +30885,7 @@
         <v>1.36239726332537</v>
       </c>
       <c r="D28" t="n">
-        <v>0.918867915336739</v>
+        <v>0.904558434942233</v>
       </c>
     </row>
     <row r="29">
@@ -30895,7 +30899,7 @@
         <v>2.47195547204809</v>
       </c>
       <c r="D29" t="n">
-        <v>2.62325079730394</v>
+        <v>2.56936529617678</v>
       </c>
     </row>
     <row r="30">
@@ -30909,7 +30913,7 @@
         <v>2.31221004596997</v>
       </c>
       <c r="D30" t="n">
-        <v>2.37786721351384</v>
+        <v>2.32967955522603</v>
       </c>
     </row>
     <row r="31">
@@ -30923,7 +30927,7 @@
         <v>1.65730462815425</v>
       </c>
       <c r="D31" t="n">
-        <v>1.37187259812757</v>
+        <v>1.34704428249493</v>
       </c>
     </row>
     <row r="32">
@@ -30937,7 +30941,7 @@
         <v>1.05773602212046</v>
       </c>
       <c r="D32" t="n">
-        <v>0.450880386402795</v>
+        <v>0.447437645133441</v>
       </c>
     </row>
     <row r="33">
@@ -30951,7 +30955,7 @@
         <v>2.26822666425348</v>
       </c>
       <c r="D33" t="n">
-        <v>2.31030471674774</v>
+        <v>2.26368586955341</v>
       </c>
     </row>
     <row r="34">
@@ -30965,7 +30969,7 @@
         <v>2.31320314050328</v>
       </c>
       <c r="D34" t="n">
-        <v>2.37939269753932</v>
+        <v>2.33116961728849</v>
       </c>
     </row>
     <row r="35">
@@ -30979,7 +30983,7 @@
         <v>1.07949479890153</v>
       </c>
       <c r="D35" t="n">
-        <v>0.484303857462404</v>
+        <v>0.480085018288286</v>
       </c>
     </row>
     <row r="36">
@@ -40994,8 +40998,12 @@
       <c r="B27" t="n">
         <v>2016</v>
       </c>
-      <c r="C27"/>
-      <c r="D27"/>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="s">

--- a/Outcome/Publish/figure_data/fig1.xlsx
+++ b/Outcome/Publish/figure_data/fig1.xlsx
@@ -220,9 +220,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -259,7 +257,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/Outcome/Publish/figure_data/fig1.xlsx
+++ b/Outcome/Publish/figure_data/fig1.xlsx
@@ -220,7 +220,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -257,7 +259,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/Outcome/Publish/figure_data/fig1.xlsx
+++ b/Outcome/Publish/figure_data/fig1.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Chikungunya</t>
   </si>
   <si>
-    <t xml:space="preserve">CA</t>
+    <t xml:space="preserve">CA (HPV)</t>
   </si>
   <si>
     <t xml:space="preserve">Leptospirosis</t>
@@ -217,7 +217,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -254,7 +256,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/Outcome/Publish/figure_data/fig1.xlsx
+++ b/Outcome/Publish/figure_data/fig1.xlsx
@@ -15,12 +15,13 @@
     <sheet name="panel G" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="panel H" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="panel I" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="APC" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
   <si>
     <t xml:space="preserve">Group</t>
   </si>
@@ -224,6 +225,162 @@
   </si>
   <si>
     <t xml:space="preserve">Mortality_joinpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slope_SE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APC_LCI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APC_UCI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start_Idx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End_Idx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StartDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StartDateLabel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EndDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EndDateLabel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DateRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P_value_Label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APC_CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008/01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008/01~2019/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.11%,6.47%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019/11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021/05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019/11~2021/05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(-64.52%,-31.64%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021/06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021/06~2025/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(60.67%,83.52%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012/01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008/01~2012/01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.63%,34.75%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012/02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021/04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012/02~2021/04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(-16.65%,-13.55%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021/05~2025/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(37.51%,57.34%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008/01~2013/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(-7.25%,2.17%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013/11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016/07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013/11~2016/07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(-52.25%,-25.28%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016/08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016/08~2025/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(-2.52%,2.64%)</t>
   </si>
 </sst>
 </file>
@@ -1048,6 +1205,547 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J1" t="s">
+        <v>77</v>
+      </c>
+      <c r="K1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L1" t="s">
+        <v>79</v>
+      </c>
+      <c r="M1" t="s">
+        <v>80</v>
+      </c>
+      <c r="N1" t="s">
+        <v>81</v>
+      </c>
+      <c r="O1" t="s">
+        <v>82</v>
+      </c>
+      <c r="P1" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.0038874</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.00067763</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.00000003336150780691</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>142</v>
+      </c>
+      <c r="K2" s="1" t="n">
+        <v>39448</v>
+      </c>
+      <c r="L2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M2" s="1" t="n">
+        <v>43739</v>
+      </c>
+      <c r="N2" t="s">
+        <v>86</v>
+      </c>
+      <c r="O2" t="s">
+        <v>87</v>
+      </c>
+      <c r="P2" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.059026</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.013864</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0000311677586910016</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-50.75</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-64.52</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-31.64</v>
+      </c>
+      <c r="I3" t="n">
+        <v>143</v>
+      </c>
+      <c r="J3" t="n">
+        <v>161</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>43770</v>
+      </c>
+      <c r="L3" t="s">
+        <v>90</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>44317</v>
+      </c>
+      <c r="N3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O3" t="s">
+        <v>92</v>
+      </c>
+      <c r="P3" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.045055</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0028115</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0000000000000000000000000000000000000277106974669292</v>
+      </c>
+      <c r="F4" t="n">
+        <v>71.71</v>
+      </c>
+      <c r="G4" t="n">
+        <v>60.67</v>
+      </c>
+      <c r="H4" t="n">
+        <v>83.52</v>
+      </c>
+      <c r="I4" t="n">
+        <v>162</v>
+      </c>
+      <c r="J4" t="n">
+        <v>216</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>44348</v>
+      </c>
+      <c r="L4" t="s">
+        <v>94</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="N4" t="s">
+        <v>95</v>
+      </c>
+      <c r="O4" t="s">
+        <v>96</v>
+      </c>
+      <c r="P4" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.013101</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0059608</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.029056304190268</v>
+      </c>
+      <c r="F5" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H5" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>49</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>39448</v>
+      </c>
+      <c r="L5" t="s">
+        <v>85</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>40909</v>
+      </c>
+      <c r="N5" t="s">
+        <v>98</v>
+      </c>
+      <c r="O5" t="s">
+        <v>99</v>
+      </c>
+      <c r="P5" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.013657</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.00077091</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.000000000000000000000000000000000000000000147572281055896</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-15.12</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-16.65</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-13.55</v>
+      </c>
+      <c r="I6" t="n">
+        <v>50</v>
+      </c>
+      <c r="J6" t="n">
+        <v>160</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>40940</v>
+      </c>
+      <c r="L6" t="s">
+        <v>102</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>44287</v>
+      </c>
+      <c r="N6" t="s">
+        <v>103</v>
+      </c>
+      <c r="O6" t="s">
+        <v>104</v>
+      </c>
+      <c r="P6" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.032157</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0028468</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0000000000000000000000199114298673316</v>
+      </c>
+      <c r="F7" t="n">
+        <v>47.09</v>
+      </c>
+      <c r="G7" t="n">
+        <v>37.51</v>
+      </c>
+      <c r="H7" t="n">
+        <v>57.34</v>
+      </c>
+      <c r="I7" t="n">
+        <v>161</v>
+      </c>
+      <c r="J7" t="n">
+        <v>216</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>44317</v>
+      </c>
+      <c r="L7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="N7" t="s">
+        <v>95</v>
+      </c>
+      <c r="O7" t="s">
+        <v>106</v>
+      </c>
+      <c r="P7" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.002239</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.0020436</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.27450875602387</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-7.25</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>70</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>39448</v>
+      </c>
+      <c r="L8" t="s">
+        <v>85</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>41548</v>
+      </c>
+      <c r="N8" t="s">
+        <v>109</v>
+      </c>
+      <c r="O8" t="s">
+        <v>110</v>
+      </c>
+      <c r="P8" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.042943</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0094669</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.00000962709918881104</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-40.27</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-52.25</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-25.28</v>
+      </c>
+      <c r="I9" t="n">
+        <v>71</v>
+      </c>
+      <c r="J9" t="n">
+        <v>103</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>41579</v>
+      </c>
+      <c r="L9" t="s">
+        <v>113</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>42552</v>
+      </c>
+      <c r="N9" t="s">
+        <v>114</v>
+      </c>
+      <c r="O9" t="s">
+        <v>115</v>
+      </c>
+      <c r="P9" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.000022139</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0010905</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.983821736877964</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-2.52</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I10" t="n">
+        <v>104</v>
+      </c>
+      <c r="J10" t="n">
+        <v>216</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>42583</v>
+      </c>
+      <c r="L10" t="s">
+        <v>117</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="N10" t="s">
+        <v>95</v>
+      </c>
+      <c r="O10" t="s">
+        <v>118</v>
+      </c>
+      <c r="P10" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>

--- a/Outcome/Publish/figure_data/fig1.xlsx
+++ b/Outcome/Publish/figure_data/fig1.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
   <si>
     <t xml:space="preserve">Group</t>
   </si>
@@ -345,42 +345,6 @@
   </si>
   <si>
     <t xml:space="preserve">(37.51%,57.34%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CFR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2013/10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2008/01~2013/10</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">(-7.25%,2.17%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2013/11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2016/07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2013/11~2016/07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(-52.25%,-25.28%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2016/08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2016/08~2025/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(-2.52%,2.64%)</t>
   </si>
 </sst>
 </file>
@@ -1581,165 +1545,6 @@
         <v>107</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>108</v>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.002239</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.0020436</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.27450875602387</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-2.65</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-7.25</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>70</v>
-      </c>
-      <c r="K8" s="1" t="n">
-        <v>39448</v>
-      </c>
-      <c r="L8" t="s">
-        <v>85</v>
-      </c>
-      <c r="M8" s="1" t="n">
-        <v>41548</v>
-      </c>
-      <c r="N8" t="s">
-        <v>109</v>
-      </c>
-      <c r="O8" t="s">
-        <v>110</v>
-      </c>
-      <c r="P8" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.042943</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.0094669</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.00000962709918881104</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-40.27</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-52.25</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-25.28</v>
-      </c>
-      <c r="I9" t="n">
-        <v>71</v>
-      </c>
-      <c r="J9" t="n">
-        <v>103</v>
-      </c>
-      <c r="K9" s="1" t="n">
-        <v>41579</v>
-      </c>
-      <c r="L9" t="s">
-        <v>113</v>
-      </c>
-      <c r="M9" s="1" t="n">
-        <v>42552</v>
-      </c>
-      <c r="N9" t="s">
-        <v>114</v>
-      </c>
-      <c r="O9" t="s">
-        <v>115</v>
-      </c>
-      <c r="P9" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>108</v>
-      </c>
-      <c r="B10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.000022139</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.0010905</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.983821736877964</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-2.52</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="I10" t="n">
-        <v>104</v>
-      </c>
-      <c r="J10" t="n">
-        <v>216</v>
-      </c>
-      <c r="K10" s="1" t="n">
-        <v>42583</v>
-      </c>
-      <c r="L10" t="s">
-        <v>117</v>
-      </c>
-      <c r="M10" s="1" t="n">
-        <v>45992</v>
-      </c>
-      <c r="N10" t="s">
-        <v>95</v>
-      </c>
-      <c r="O10" t="s">
-        <v>118</v>
-      </c>
-      <c r="P10" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>119</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -23714,7 +23519,7 @@
         <v>52.9606534949093</v>
       </c>
       <c r="E2" t="n">
-        <v>52.6223862768737</v>
+        <v>52.6223862760916</v>
       </c>
     </row>
     <row r="3">
@@ -23731,7 +23536,7 @@
         <v>53.5877563650519</v>
       </c>
       <c r="E3" t="n">
-        <v>52.8273477099703</v>
+        <v>52.8273477091924</v>
       </c>
     </row>
     <row r="4">
@@ -23748,7 +23553,7 @@
         <v>54.2148592351945</v>
       </c>
       <c r="E4" t="n">
-        <v>53.0331074570955</v>
+        <v>53.0331074563333</v>
       </c>
     </row>
     <row r="5">
@@ -23765,7 +23570,7 @@
         <v>54.8419621053371</v>
       </c>
       <c r="E5" t="n">
-        <v>53.2396686276389</v>
+        <v>53.23966862689</v>
       </c>
     </row>
     <row r="6">
@@ -23782,7 +23587,7 @@
         <v>55.6730358124072</v>
       </c>
       <c r="E6" t="n">
-        <v>53.4470343431015</v>
+        <v>53.4470343423668</v>
       </c>
     </row>
     <row r="7">
@@ -23799,7 +23604,7 @@
         <v>56.5041095194772</v>
       </c>
       <c r="E7" t="n">
-        <v>53.6552077371439</v>
+        <v>53.6552077364237</v>
       </c>
     </row>
     <row r="8">
@@ -23816,7 +23621,7 @@
         <v>57.3351832265472</v>
       </c>
       <c r="E8" t="n">
-        <v>53.8641919556319</v>
+        <v>53.8641919549262</v>
       </c>
     </row>
     <row r="9">
@@ -23833,7 +23638,7 @@
         <v>58.2459823903846</v>
       </c>
       <c r="E9" t="n">
-        <v>54.0739901566841</v>
+        <v>54.073990155993</v>
       </c>
     </row>
     <row r="10">
@@ -23850,7 +23655,7 @@
         <v>59.1567815542219</v>
       </c>
       <c r="E10" t="n">
-        <v>54.2846055107198</v>
+        <v>54.2846055100436</v>
       </c>
     </row>
     <row r="11">
@@ -23867,7 +23672,7 @@
         <v>60.0675807180593</v>
       </c>
       <c r="E11" t="n">
-        <v>54.4960412005072</v>
+        <v>54.4960411998458</v>
       </c>
     </row>
     <row r="12">
@@ -23884,7 +23689,7 @@
         <v>60.8264404975824</v>
       </c>
       <c r="E12" t="n">
-        <v>54.7083004212108</v>
+        <v>54.7083004205644</v>
       </c>
     </row>
     <row r="13">
@@ -23901,7 +23706,7 @@
         <v>61.5853002771055</v>
       </c>
       <c r="E13" t="n">
-        <v>54.9213863804404</v>
+        <v>54.9213863798092</v>
       </c>
     </row>
     <row r="14">
@@ -23918,7 +23723,7 @@
         <v>62.3441600566286</v>
       </c>
       <c r="E14" t="n">
-        <v>55.1353022982991</v>
+        <v>55.1353022976832</v>
       </c>
     </row>
     <row r="15">
@@ -23935,7 +23740,7 @@
         <v>63.3248826212604</v>
       </c>
       <c r="E15" t="n">
-        <v>55.3500514074324</v>
+        <v>55.3500514068318</v>
       </c>
     </row>
     <row r="16">
@@ -23952,7 +23757,7 @@
         <v>64.3056051858921</v>
       </c>
       <c r="E16" t="n">
-        <v>55.5656369530763</v>
+        <v>55.5656369524913</v>
       </c>
     </row>
     <row r="17">
@@ -23969,7 +23774,7 @@
         <v>65.2863277505239</v>
       </c>
       <c r="E17" t="n">
-        <v>55.7820621931073</v>
+        <v>55.7820621925379</v>
       </c>
     </row>
     <row r="18">
@@ -23986,7 +23791,7 @@
         <v>66.0987253027954</v>
       </c>
       <c r="E18" t="n">
-        <v>55.999330398091</v>
+        <v>55.9993303975374</v>
       </c>
     </row>
     <row r="19">
@@ -24003,7 +23808,7 @@
         <v>66.9111228550668</v>
       </c>
       <c r="E19" t="n">
-        <v>56.2174448513315</v>
+        <v>56.2174448507939</v>
       </c>
     </row>
     <row r="20">
@@ -24020,7 +23825,7 @@
         <v>67.7235204073383</v>
       </c>
       <c r="E20" t="n">
-        <v>56.4364088489215</v>
+        <v>56.4364088483999</v>
       </c>
     </row>
     <row r="21">
@@ -24037,7 +23842,7 @@
         <v>67.8250945738005</v>
       </c>
       <c r="E21" t="n">
-        <v>56.6562256997916</v>
+        <v>56.6562256992862</v>
       </c>
     </row>
     <row r="22">
@@ -24054,7 +23859,7 @@
         <v>67.9266687402626</v>
       </c>
       <c r="E22" t="n">
-        <v>56.8768987257606</v>
+        <v>56.8768987252715</v>
       </c>
     </row>
     <row r="23">
@@ -24071,7 +23876,7 @@
         <v>68.0282429067248</v>
       </c>
       <c r="E23" t="n">
-        <v>57.0984312615856</v>
+        <v>57.0984312611129</v>
       </c>
     </row>
     <row r="24">
@@ -24088,7 +23893,7 @@
         <v>67.6657739498362</v>
       </c>
       <c r="E24" t="n">
-        <v>57.3208266550123</v>
+        <v>57.3208266545562</v>
       </c>
     </row>
     <row r="25">
@@ -24105,7 +23910,7 @@
         <v>67.3033049929475</v>
       </c>
       <c r="E25" t="n">
-        <v>57.5440882668258</v>
+        <v>57.5440882663864</v>
       </c>
     </row>
     <row r="26">
@@ -24122,7 +23927,7 @@
         <v>66.9408360360589</v>
       </c>
       <c r="E26" t="n">
-        <v>57.7682194709013</v>
+        <v>57.7682194704788</v>
       </c>
     </row>
     <row r="27">
@@ -24139,7 +23944,7 @@
         <v>66.5489759319587</v>
       </c>
       <c r="E27" t="n">
-        <v>57.993223654255</v>
+        <v>57.9932236538495</v>
       </c>
     </row>
     <row r="28">
@@ -24156,7 +23961,7 @@
         <v>66.1571158278584</v>
       </c>
       <c r="E28" t="n">
-        <v>58.2191042170953</v>
+        <v>58.219104216707</v>
       </c>
     </row>
     <row r="29">
@@ -24173,7 +23978,7 @@
         <v>65.7652557237581</v>
       </c>
       <c r="E29" t="n">
-        <v>58.4458645728745</v>
+        <v>58.4458645725035</v>
       </c>
     </row>
     <row r="30">
@@ -24190,7 +23995,7 @@
         <v>65.5467072693592</v>
       </c>
       <c r="E30" t="n">
-        <v>58.6735081483398</v>
+        <v>58.6735081479862</v>
       </c>
     </row>
     <row r="31">
@@ -24207,7 +24012,7 @@
         <v>65.3281588149602</v>
       </c>
       <c r="E31" t="n">
-        <v>58.9020383835855</v>
+        <v>58.9020383832495</v>
       </c>
     </row>
     <row r="32">
@@ -24224,7 +24029,7 @@
         <v>65.1096103605612</v>
       </c>
       <c r="E32" t="n">
-        <v>59.131458732105</v>
+        <v>59.1314587317867</v>
       </c>
     </row>
     <row r="33">
@@ -24241,7 +24046,7 @@
         <v>65.0688640358459</v>
       </c>
       <c r="E33" t="n">
-        <v>59.3617726608428</v>
+        <v>59.3617726605423</v>
       </c>
     </row>
     <row r="34">
@@ -24258,7 +24063,7 @@
         <v>65.0281177111307</v>
       </c>
       <c r="E34" t="n">
-        <v>59.5929836502469</v>
+        <v>59.5929836499644</v>
       </c>
     </row>
     <row r="35">
@@ -24275,7 +24080,7 @@
         <v>64.9873713864154</v>
       </c>
       <c r="E35" t="n">
-        <v>59.8250951943215</v>
+        <v>59.8250951940572</v>
       </c>
     </row>
     <row r="36">
@@ -24292,7 +24097,7 @@
         <v>64.6606400569347</v>
       </c>
       <c r="E36" t="n">
-        <v>60.0581108006799</v>
+        <v>60.0581108004339</v>
       </c>
     </row>
     <row r="37">
@@ -24309,7 +24114,7 @@
         <v>64.333908727454</v>
       </c>
       <c r="E37" t="n">
-        <v>60.2920339905971</v>
+        <v>60.2920339903695</v>
       </c>
     </row>
     <row r="38">
@@ -24326,7 +24131,7 @@
         <v>64.0071773979734</v>
       </c>
       <c r="E38" t="n">
-        <v>60.5268682990636</v>
+        <v>60.5268682988545</v>
       </c>
     </row>
     <row r="39">
@@ -24343,7 +24148,7 @@
         <v>63.2769946618867</v>
       </c>
       <c r="E39" t="n">
-        <v>60.7626172748382</v>
+        <v>60.7626172746479</v>
       </c>
     </row>
     <row r="40">
@@ -24360,7 +24165,7 @@
         <v>62.5468119258001</v>
       </c>
       <c r="E40" t="n">
-        <v>60.9992844805021</v>
+        <v>60.9992844803307</v>
       </c>
     </row>
     <row r="41">
@@ -24377,7 +24182,7 @@
         <v>61.8166291897135</v>
       </c>
       <c r="E41" t="n">
-        <v>61.2368734925125</v>
+        <v>61.2368734923601</v>
       </c>
     </row>
     <row r="42">
@@ -24394,7 +24199,7 @@
         <v>61.202957160841</v>
       </c>
       <c r="E42" t="n">
-        <v>61.4753879012569</v>
+        <v>61.4753879011237</v>
       </c>
     </row>
     <row r="43">
@@ -24411,7 +24216,7 @@
         <v>60.5892851319684</v>
       </c>
       <c r="E43" t="n">
-        <v>61.7148313111068</v>
+        <v>61.7148313109929</v>
       </c>
     </row>
     <row r="44">
@@ -24428,7 +24233,7 @@
         <v>59.9756131030959</v>
       </c>
       <c r="E44" t="n">
-        <v>61.955207340473</v>
+        <v>61.9552073403785</v>
       </c>
     </row>
     <row r="45">
@@ -24445,7 +24250,7 @@
         <v>59.8817031106424</v>
       </c>
       <c r="E45" t="n">
-        <v>62.1965196218593</v>
+        <v>62.1965196217845</v>
       </c>
     </row>
     <row r="46">
@@ -24462,7 +24267,7 @@
         <v>59.787793118189</v>
       </c>
       <c r="E46" t="n">
-        <v>62.4387718019184</v>
+        <v>62.4387718018634</v>
       </c>
     </row>
     <row r="47">
@@ -24479,7 +24284,7 @@
         <v>59.6938831257355</v>
       </c>
       <c r="E47" t="n">
-        <v>62.6819675415062</v>
+        <v>62.6819675414712</v>
       </c>
     </row>
     <row r="48">
@@ -24496,7 +24301,7 @@
         <v>59.6624158587651</v>
       </c>
       <c r="E48" t="n">
-        <v>62.9261105157376</v>
+        <v>62.9261105157227</v>
       </c>
     </row>
     <row r="49">
@@ -24513,7 +24318,7 @@
         <v>59.6309485917948</v>
       </c>
       <c r="E49" t="n">
-        <v>63.1712044140419</v>
+        <v>63.1712044140472</v>
       </c>
     </row>
     <row r="50">
@@ -24530,7 +24335,7 @@
         <v>59.5994813248244</v>
       </c>
       <c r="E50" t="n">
-        <v>63.4172529402183</v>
+        <v>63.417252940244</v>
       </c>
     </row>
     <row r="51">
@@ -24547,7 +24352,7 @@
         <v>59.9598549853372</v>
       </c>
       <c r="E51" t="n">
-        <v>63.6642598124923</v>
+        <v>63.6642598125386</v>
       </c>
     </row>
     <row r="52">
@@ -24564,7 +24369,7 @@
         <v>60.32022864585</v>
       </c>
       <c r="E52" t="n">
-        <v>63.9122287635718</v>
+        <v>63.9122287636388</v>
       </c>
     </row>
     <row r="53">
@@ -24581,7 +24386,7 @@
         <v>60.6806023063629</v>
       </c>
       <c r="E53" t="n">
-        <v>64.1611635407031</v>
+        <v>64.161163540791</v>
       </c>
     </row>
     <row r="54">
@@ -24598,7 +24403,7 @@
         <v>61.4717559663315</v>
       </c>
       <c r="E54" t="n">
-        <v>64.4110679057281</v>
+        <v>64.411067905837</v>
       </c>
     </row>
     <row r="55">
@@ -24615,7 +24420,7 @@
         <v>62.2629096263002</v>
       </c>
       <c r="E55" t="n">
-        <v>64.6619456351407</v>
+        <v>64.6619456352709</v>
       </c>
     </row>
     <row r="56">
@@ -24632,7 +24437,7 @@
         <v>63.0540632862688</v>
       </c>
       <c r="E56" t="n">
-        <v>64.9138005201441</v>
+        <v>64.9138005202957</v>
       </c>
     </row>
     <row r="57">
@@ -24649,7 +24454,7 @@
         <v>64.0616439866885</v>
       </c>
       <c r="E57" t="n">
-        <v>65.166636366708</v>
+        <v>65.1666363668812</v>
       </c>
     </row>
     <row r="58">
@@ -24666,7 +24471,7 @@
         <v>65.0692246871081</v>
       </c>
       <c r="E58" t="n">
-        <v>65.4204569956264</v>
+        <v>65.4204569958213</v>
       </c>
     </row>
     <row r="59">
@@ -24683,7 +24488,7 @@
         <v>66.0768053875278</v>
       </c>
       <c r="E59" t="n">
-        <v>65.6752662425747</v>
+        <v>65.6752662427915</v>
       </c>
     </row>
     <row r="60">
@@ -24700,7 +24505,7 @@
         <v>66.6663312608161</v>
       </c>
       <c r="E60" t="n">
-        <v>65.9310679581684</v>
+        <v>65.9310679584072</v>
       </c>
     </row>
     <row r="61">
@@ -24717,7 +24522,7 @@
         <v>67.2558571341044</v>
       </c>
       <c r="E61" t="n">
-        <v>66.1878660080206</v>
+        <v>66.1878660082816</v>
       </c>
     </row>
     <row r="62">
@@ -24734,7 +24539,7 @@
         <v>67.8453830073927</v>
       </c>
       <c r="E62" t="n">
-        <v>66.4456642728012</v>
+        <v>66.4456642730845</v>
       </c>
     </row>
     <row r="63">
@@ -24751,7 +24556,7 @@
         <v>67.6991093243815</v>
       </c>
       <c r="E63" t="n">
-        <v>66.7044666482946</v>
+        <v>66.7044666486005</v>
       </c>
     </row>
     <row r="64">
@@ -24768,7 +24573,7 @@
         <v>67.5528356413703</v>
       </c>
       <c r="E64" t="n">
-        <v>66.9642770454595</v>
+        <v>66.9642770457881</v>
       </c>
     </row>
     <row r="65">
@@ -24785,7 +24590,7 @@
         <v>67.4065619583591</v>
       </c>
       <c r="E65" t="n">
-        <v>67.2250993904873</v>
+        <v>67.2250993908389</v>
       </c>
     </row>
     <row r="66">
@@ -24802,7 +24607,7 @@
         <v>67.3919276907092</v>
       </c>
       <c r="E66" t="n">
-        <v>67.486937624862</v>
+        <v>67.4869376252366</v>
       </c>
     </row>
     <row r="67">
@@ -24819,7 +24624,7 @@
         <v>67.3772934230592</v>
       </c>
       <c r="E67" t="n">
-        <v>67.7497957054191</v>
+        <v>67.7497957058169</v>
       </c>
     </row>
     <row r="68">
@@ -24836,7 +24641,7 @@
         <v>67.3626591554093</v>
       </c>
       <c r="E68" t="n">
-        <v>68.013677604406</v>
+        <v>68.0136776048273</v>
       </c>
     </row>
     <row r="69">
@@ -24853,7 +24658,7 @@
         <v>67.3156897800839</v>
       </c>
       <c r="E69" t="n">
-        <v>68.2785873095419</v>
+        <v>68.2785873099868</v>
       </c>
     </row>
     <row r="70">
@@ -24870,7 +24675,7 @@
         <v>67.2687204047586</v>
       </c>
       <c r="E70" t="n">
-        <v>68.5445288240777</v>
+        <v>68.5445288245464</v>
       </c>
     </row>
     <row r="71">
@@ -24887,7 +24692,7 @@
         <v>67.2217510294332</v>
       </c>
       <c r="E71" t="n">
-        <v>68.8115061668569</v>
+        <v>68.8115061673495</v>
       </c>
     </row>
     <row r="72">
@@ -24904,7 +24709,7 @@
         <v>66.4039518297106</v>
       </c>
       <c r="E72" t="n">
-        <v>69.0795233723761</v>
+        <v>69.0795233728928</v>
       </c>
     </row>
     <row r="73">
@@ -24921,7 +24726,7 @@
         <v>65.5861526299881</v>
       </c>
       <c r="E73" t="n">
-        <v>69.3485844908461</v>
+        <v>69.3485844913872</v>
       </c>
     </row>
     <row r="74">
@@ -24938,7 +24743,7 @@
         <v>64.7683534302655</v>
       </c>
       <c r="E74" t="n">
-        <v>69.6186935882532</v>
+        <v>69.6186935888187</v>
       </c>
     </row>
     <row r="75">
@@ -24955,7 +24760,7 @@
         <v>63.8760298052676</v>
       </c>
       <c r="E75" t="n">
-        <v>69.8898547464202</v>
+        <v>69.8898547470104</v>
       </c>
     </row>
     <row r="76">
@@ -24972,7 +24777,7 @@
         <v>62.9837061802696</v>
       </c>
       <c r="E76" t="n">
-        <v>70.1620720630686</v>
+        <v>70.1620720636837</v>
       </c>
     </row>
     <row r="77">
@@ -24989,7 +24794,7 @@
         <v>62.0913825552717</v>
       </c>
       <c r="E77" t="n">
-        <v>70.4353496518803</v>
+        <v>70.4353496525205</v>
       </c>
     </row>
     <row r="78">
@@ -25006,7 +24811,7 @@
         <v>61.9884601968422</v>
       </c>
       <c r="E78" t="n">
-        <v>70.7096916425597</v>
+        <v>70.7096916432251</v>
       </c>
     </row>
     <row r="79">
@@ -25023,7 +24828,7 @@
         <v>61.8855378384127</v>
       </c>
       <c r="E79" t="n">
-        <v>70.9851021808963</v>
+        <v>70.9851021815871</v>
       </c>
     </row>
     <row r="80">
@@ -25040,7 +24845,7 @@
         <v>61.7826154799832</v>
       </c>
       <c r="E80" t="n">
-        <v>71.261585428827</v>
+        <v>71.2615854295434</v>
       </c>
     </row>
     <row r="81">
@@ -25057,7 +24862,7 @@
         <v>61.5700741565645</v>
       </c>
       <c r="E81" t="n">
-        <v>71.5391455644995</v>
+        <v>71.5391455652418</v>
       </c>
     </row>
     <row r="82">
@@ -25074,7 +24879,7 @@
         <v>61.3575328331458</v>
       </c>
       <c r="E82" t="n">
-        <v>71.817786782335</v>
+        <v>71.8177867831032</v>
       </c>
     </row>
     <row r="83">
@@ -25091,7 +24896,7 @@
         <v>61.1449915097271</v>
       </c>
       <c r="E83" t="n">
-        <v>72.0975132930918</v>
+        <v>72.0975132938862</v>
       </c>
     </row>
     <row r="84">
@@ -25108,7 +24913,7 @@
         <v>61.0614374909758</v>
       </c>
       <c r="E84" t="n">
-        <v>72.3783293239289</v>
+        <v>72.3783293247497</v>
       </c>
     </row>
     <row r="85">
@@ -25125,7 +24930,7 @@
         <v>60.9778834722245</v>
       </c>
       <c r="E85" t="n">
-        <v>72.6602391184698</v>
+        <v>72.6602391193171</v>
       </c>
     </row>
     <row r="86">
@@ -25142,7 +24947,7 @@
         <v>60.8943294534732</v>
       </c>
       <c r="E86" t="n">
-        <v>72.9432469368667</v>
+        <v>72.9432469377408</v>
       </c>
     </row>
     <row r="87">
@@ -25159,7 +24964,7 @@
         <v>62.1128317551398</v>
       </c>
       <c r="E87" t="n">
-        <v>73.227357055865</v>
+        <v>73.2273570567661</v>
       </c>
     </row>
     <row r="88">
@@ -25176,7 +24981,7 @@
         <v>63.3313340568064</v>
       </c>
       <c r="E88" t="n">
-        <v>73.5125737688676</v>
+        <v>73.5125737697959</v>
       </c>
     </row>
     <row r="89">
@@ -25193,7 +24998,7 @@
         <v>64.549836358473</v>
       </c>
       <c r="E89" t="n">
-        <v>73.7989013860001</v>
+        <v>73.7989013869557</v>
       </c>
     </row>
     <row r="90">
@@ -25210,7 +25015,7 @@
         <v>66.148053805717</v>
       </c>
       <c r="E90" t="n">
-        <v>74.0863442341759</v>
+        <v>74.086344235159</v>
       </c>
     </row>
     <row r="91">
@@ -25227,7 +25032,7 @@
         <v>67.7462712529611</v>
       </c>
       <c r="E91" t="n">
-        <v>74.3749066571612</v>
+        <v>74.3749066581721</v>
       </c>
     </row>
     <row r="92">
@@ -25244,7 +25049,7 @@
         <v>69.3444887002051</v>
       </c>
       <c r="E92" t="n">
-        <v>74.6645930156412</v>
+        <v>74.6645930166801</v>
       </c>
     </row>
     <row r="93">
@@ -25261,7 +25066,7 @@
         <v>70.187837354764</v>
       </c>
       <c r="E93" t="n">
-        <v>74.9554076872858</v>
+        <v>74.9554076883528</v>
       </c>
     </row>
     <row r="94">
@@ -25278,7 +25083,7 @@
         <v>71.0311860093229</v>
       </c>
       <c r="E94" t="n">
-        <v>75.2473550668154</v>
+        <v>75.2473550679107</v>
       </c>
     </row>
     <row r="95">
@@ -25295,7 +25100,7 @@
         <v>71.8745346638819</v>
       </c>
       <c r="E95" t="n">
-        <v>75.5404395660678</v>
+        <v>75.5404395671917</v>
       </c>
     </row>
     <row r="96">
@@ -25312,7 +25117,7 @@
         <v>72.7681319153596</v>
       </c>
       <c r="E96" t="n">
-        <v>75.8346656140647</v>
+        <v>75.8346656152174</v>
       </c>
     </row>
     <row r="97">
@@ -25329,7 +25134,7 @@
         <v>73.6617291668373</v>
       </c>
       <c r="E97" t="n">
-        <v>76.1300376570785</v>
+        <v>76.1300376582602</v>
       </c>
     </row>
     <row r="98">
@@ -25346,7 +25151,7 @@
         <v>74.555326418315</v>
       </c>
       <c r="E98" t="n">
-        <v>76.4265601586998</v>
+        <v>76.4265601599106</v>
       </c>
     </row>
     <row r="99">
@@ -25363,7 +25168,7 @@
         <v>75.5648017152812</v>
       </c>
       <c r="E99" t="n">
-        <v>76.7242375999042</v>
+        <v>76.7242376011445</v>
       </c>
     </row>
     <row r="100">
@@ -25380,7 +25185,7 @@
         <v>76.5742770122474</v>
       </c>
       <c r="E100" t="n">
-        <v>77.0230744791213</v>
+        <v>77.023074480391</v>
       </c>
     </row>
     <row r="101">
@@ -25397,7 +25202,7 @@
         <v>77.5837523092135</v>
       </c>
       <c r="E101" t="n">
-        <v>77.3230753123007</v>
+        <v>77.3230753136003</v>
       </c>
     </row>
     <row r="102">
@@ -25414,7 +25219,7 @@
         <v>77.6689309856049</v>
       </c>
       <c r="E102" t="n">
-        <v>77.6242446329823</v>
+        <v>77.624244634312</v>
       </c>
     </row>
     <row r="103">
@@ -25431,7 +25236,7 @@
         <v>77.7541096619962</v>
       </c>
       <c r="E103" t="n">
-        <v>77.9265869923637</v>
+        <v>77.9265869937236</v>
       </c>
     </row>
     <row r="104">
@@ -25448,7 +25253,7 @@
         <v>77.8392883383875</v>
       </c>
       <c r="E104" t="n">
-        <v>78.2301069593689</v>
+        <v>78.2301069607592</v>
       </c>
     </row>
     <row r="105">
@@ -25465,7 +25270,7 @@
         <v>77.7312007640555</v>
       </c>
       <c r="E105" t="n">
-        <v>78.5348091207179</v>
+        <v>78.5348091221388</v>
       </c>
     </row>
     <row r="106">
@@ -25482,7 +25287,7 @@
         <v>77.6231131897234</v>
       </c>
       <c r="E106" t="n">
-        <v>78.8406980809955</v>
+        <v>78.8406980824474</v>
       </c>
     </row>
     <row r="107">
@@ -25499,7 +25304,7 @@
         <v>77.5150256153914</v>
       </c>
       <c r="E107" t="n">
-        <v>79.1477784627214</v>
+        <v>79.1477784642044</v>
       </c>
     </row>
     <row r="108">
@@ -25516,7 +25321,7 @@
         <v>78.4665220286386</v>
       </c>
       <c r="E108" t="n">
-        <v>79.4560549064195</v>
+        <v>79.4560549079338</v>
       </c>
     </row>
     <row r="109">
@@ -25533,7 +25338,7 @@
         <v>79.4180184418858</v>
       </c>
       <c r="E109" t="n">
-        <v>79.7655320706885</v>
+        <v>79.7655320722344</v>
       </c>
     </row>
     <row r="110">
@@ -25550,7 +25355,7 @@
         <v>80.369514855133</v>
       </c>
       <c r="E110" t="n">
-        <v>80.076214632272</v>
+        <v>80.0762146338497</v>
       </c>
     </row>
     <row r="111">
@@ -25567,7 +25372,7 @@
         <v>81.2258750766526</v>
       </c>
       <c r="E111" t="n">
-        <v>80.3881072861293</v>
+        <v>80.3881072877389</v>
       </c>
     </row>
     <row r="112">
@@ -25584,7 +25389,7 @@
         <v>82.0822352981723</v>
       </c>
       <c r="E112" t="n">
-        <v>80.7012147455062</v>
+        <v>80.7012147471481</v>
       </c>
     </row>
     <row r="113">
@@ -25601,7 +25406,7 @@
         <v>82.9385955196918</v>
       </c>
       <c r="E113" t="n">
-        <v>81.0155417420066</v>
+        <v>81.0155417436809</v>
       </c>
     </row>
     <row r="114">
@@ -25618,7 +25423,7 @@
         <v>83.0546227333876</v>
       </c>
       <c r="E114" t="n">
-        <v>81.3310930256635</v>
+        <v>81.3310930273705</v>
       </c>
     </row>
     <row r="115">
@@ -25635,7 +25440,7 @@
         <v>83.1706499470833</v>
       </c>
       <c r="E115" t="n">
-        <v>81.6478733650113</v>
+        <v>81.6478733667511</v>
       </c>
     </row>
     <row r="116">
@@ -25652,7 +25457,7 @@
         <v>83.286677160779</v>
       </c>
       <c r="E116" t="n">
-        <v>81.965887547157</v>
+        <v>81.9658875489301</v>
       </c>
     </row>
     <row r="117">
@@ -25669,7 +25474,7 @@
         <v>83.8833623068731</v>
       </c>
       <c r="E117" t="n">
-        <v>82.285140377854</v>
+        <v>82.2851403796604</v>
       </c>
     </row>
     <row r="118">
@@ -25686,7 +25491,7 @@
         <v>84.4800474529671</v>
       </c>
       <c r="E118" t="n">
-        <v>82.6056366815732</v>
+        <v>82.6056366834133</v>
       </c>
     </row>
     <row r="119">
@@ -25703,7 +25508,7 @@
         <v>85.0767325990612</v>
       </c>
       <c r="E119" t="n">
-        <v>82.9273813015768</v>
+        <v>82.9273813034507</v>
       </c>
     </row>
     <row r="120">
@@ -25720,7 +25525,7 @@
         <v>86.062689158349</v>
       </c>
       <c r="E120" t="n">
-        <v>83.2503790999912</v>
+        <v>83.2503791018991</v>
       </c>
     </row>
     <row r="121">
@@ -25737,7 +25542,7 @@
         <v>87.0486457176369</v>
       </c>
       <c r="E121" t="n">
-        <v>83.5746349578806</v>
+        <v>83.5746349598228</v>
       </c>
     </row>
     <row r="122">
@@ -25754,7 +25559,7 @@
         <v>88.0346022769247</v>
       </c>
       <c r="E122" t="n">
-        <v>83.9001537753205</v>
+        <v>83.9001537772973</v>
       </c>
     </row>
     <row r="123">
@@ -25771,7 +25576,7 @@
         <v>88.4337637039942</v>
       </c>
       <c r="E123" t="n">
-        <v>84.2269404714723</v>
+        <v>84.2269404734839</v>
       </c>
     </row>
     <row r="124">
@@ -25788,7 +25593,7 @@
         <v>88.8329251310637</v>
       </c>
       <c r="E124" t="n">
-        <v>84.5549999846568</v>
+        <v>84.5549999867035</v>
       </c>
     </row>
     <row r="125">
@@ -25805,7 +25610,7 @@
         <v>89.2320865581332</v>
       </c>
       <c r="E125" t="n">
-        <v>84.8843372724298</v>
+        <v>84.8843372745117</v>
       </c>
     </row>
     <row r="126">
@@ -25822,7 +25627,7 @@
         <v>90.3088216825565</v>
       </c>
       <c r="E126" t="n">
-        <v>85.2149573116561</v>
+        <v>85.2149573137735</v>
       </c>
     </row>
     <row r="127">
@@ -25839,7 +25644,7 @@
         <v>91.3855568069798</v>
       </c>
       <c r="E127" t="n">
-        <v>85.5468650985853</v>
+        <v>85.5468651007384</v>
       </c>
     </row>
     <row r="128">
@@ -25856,7 +25661,7 @@
         <v>92.462291931403</v>
       </c>
       <c r="E128" t="n">
-        <v>85.8800656489272</v>
+        <v>85.8800656511163</v>
       </c>
     </row>
     <row r="129">
@@ -25873,7 +25678,7 @@
         <v>94.2743143123654</v>
       </c>
       <c r="E129" t="n">
-        <v>86.2145639979274</v>
+        <v>86.2145640001528</v>
       </c>
     </row>
     <row r="130">
@@ -25890,7 +25695,7 @@
         <v>96.0863366933277</v>
       </c>
       <c r="E130" t="n">
-        <v>86.5503652004435</v>
+        <v>86.5503652027055</v>
       </c>
     </row>
     <row r="131">
@@ -25907,7 +25712,7 @@
         <v>97.8983590742901</v>
       </c>
       <c r="E131" t="n">
-        <v>86.8874743310218</v>
+        <v>86.8874743333205</v>
       </c>
     </row>
     <row r="132">
@@ -25924,7 +25729,7 @@
         <v>99.5659380796031</v>
       </c>
       <c r="E132" t="n">
-        <v>87.2258964839733</v>
+        <v>87.225896486309</v>
       </c>
     </row>
     <row r="133">
@@ -25941,7 +25746,7 @@
         <v>101.233517084916</v>
       </c>
       <c r="E133" t="n">
-        <v>87.5656367734512</v>
+        <v>87.5656367758242</v>
       </c>
     </row>
     <row r="134">
@@ -25958,7 +25763,7 @@
         <v>102.901096090229</v>
       </c>
       <c r="E134" t="n">
-        <v>87.9067003335282</v>
+        <v>87.9067003359387</v>
       </c>
     </row>
     <row r="135">
@@ -25975,7 +25780,7 @@
         <v>104.156618877232</v>
       </c>
       <c r="E135" t="n">
-        <v>88.2490923182739</v>
+        <v>88.2490923207221</v>
       </c>
     </row>
     <row r="136">
@@ -25992,7 +25797,7 @@
         <v>105.412141664236</v>
       </c>
       <c r="E136" t="n">
-        <v>88.5928179018325</v>
+        <v>88.5928179043188</v>
       </c>
     </row>
     <row r="137">
@@ -26009,7 +25814,7 @@
         <v>106.667664451239</v>
       </c>
       <c r="E137" t="n">
-        <v>88.9378822785015</v>
+        <v>88.937882281026</v>
       </c>
     </row>
     <row r="138">
@@ -26026,7 +25831,7 @@
         <v>106.31714758968</v>
       </c>
       <c r="E138" t="n">
-        <v>89.2842906628098</v>
+        <v>89.2842906653728</v>
       </c>
     </row>
     <row r="139">
@@ -26043,7 +25848,7 @@
         <v>105.966630728121</v>
       </c>
       <c r="E139" t="n">
-        <v>89.6320482895966</v>
+        <v>89.6320482921985</v>
       </c>
     </row>
     <row r="140">
@@ -26060,7 +25865,7 @@
         <v>105.616113866562</v>
       </c>
       <c r="E140" t="n">
-        <v>89.9811604140905</v>
+        <v>89.9811604167314</v>
       </c>
     </row>
     <row r="141">
@@ -26077,7 +25882,7 @@
         <v>102.441571529924</v>
       </c>
       <c r="E141" t="n">
-        <v>90.3316323119891</v>
+        <v>90.3316323146694</v>
       </c>
     </row>
     <row r="142">
@@ -26094,7 +25899,7 @@
         <v>99.2670291932854</v>
       </c>
       <c r="E142" t="n">
-        <v>90.6834692795384</v>
+        <v>90.6834692822584</v>
       </c>
     </row>
     <row r="143">
@@ -26111,7 +25916,7 @@
         <v>96.0924868566471</v>
       </c>
       <c r="E143" t="n">
-        <v>91.0366766336131</v>
+        <v>91.0366766363728</v>
       </c>
     </row>
     <row r="144">
@@ -26128,7 +25933,7 @@
         <v>91.4220483929578</v>
       </c>
       <c r="E144" t="n">
-        <v>87.544534056886</v>
+        <v>87.5445340250358</v>
       </c>
     </row>
     <row r="145">
@@ -26145,7 +25950,7 @@
         <v>86.7516099292686</v>
       </c>
       <c r="E145" t="n">
-        <v>82.5266934027441</v>
+        <v>82.5266933762034</v>
       </c>
     </row>
     <row r="146">
@@ -26162,7 +25967,7 @@
         <v>82.0811714655793</v>
       </c>
       <c r="E146" t="n">
-        <v>77.796463221393</v>
+        <v>77.7964631996578</v>
       </c>
     </row>
     <row r="147">
@@ -26179,7 +25984,7 @@
         <v>77.8259285016056</v>
       </c>
       <c r="E147" t="n">
-        <v>73.3373583771421</v>
+        <v>73.3373583597485</v>
       </c>
     </row>
     <row r="148">
@@ -26196,7 +26001,7 @@
         <v>73.5706855376318</v>
       </c>
       <c r="E148" t="n">
-        <v>69.1338386223498</v>
+        <v>69.1338386088718</v>
       </c>
     </row>
     <row r="149">
@@ -26213,7 +26018,7 @@
         <v>69.315442573658</v>
       </c>
       <c r="E149" t="n">
-        <v>65.1712544387308</v>
+        <v>65.1712544287765</v>
       </c>
     </row>
     <row r="150">
@@ -26230,7 +26035,7 @@
         <v>65.0619351112434</v>
       </c>
       <c r="E150" t="n">
-        <v>61.4357959829054</v>
+        <v>61.4357959761152</v>
       </c>
     </row>
     <row r="151">
@@ -26247,7 +26052,7 @@
         <v>60.8084276488287</v>
       </c>
       <c r="E151" t="n">
-        <v>57.9144449582683</v>
+        <v>57.9144449543122</v>
       </c>
     </row>
     <row r="152">
@@ -26264,7 +26069,7 @@
         <v>56.554920186414</v>
       </c>
       <c r="E152" t="n">
-        <v>54.5949292454447</v>
+        <v>54.59492924402</v>
       </c>
     </row>
     <row r="153">
@@ -26281,7 +26086,7 @@
         <v>53.3831544102782</v>
       </c>
       <c r="E153" t="n">
-        <v>51.4656801332182</v>
+        <v>51.4656801340477</v>
       </c>
     </row>
     <row r="154">
@@ -26298,7 +26103,7 @@
         <v>50.2113886341425</v>
       </c>
       <c r="E154" t="n">
-        <v>48.5157920008795</v>
+        <v>48.5157920037096</v>
       </c>
     </row>
     <row r="155">
@@ -26315,7 +26120,7 @@
         <v>47.0396228580068</v>
       </c>
       <c r="E155" t="n">
-        <v>45.7349843114843</v>
+        <v>45.7349843160829</v>
       </c>
     </row>
     <row r="156">
@@ -26332,7 +26137,7 @@
         <v>44.9534072070397</v>
       </c>
       <c r="E156" t="n">
-        <v>43.1135657835659</v>
+        <v>43.1135657897209</v>
       </c>
     </row>
     <row r="157">
@@ -26349,7 +26154,7 @@
         <v>42.8671915560727</v>
       </c>
       <c r="E157" t="n">
-        <v>40.6424006164382</v>
+        <v>40.6424006239562</v>
       </c>
     </row>
     <row r="158">
@@ -26366,7 +26171,7 @@
         <v>40.7809759051056</v>
       </c>
       <c r="E158" t="n">
-        <v>38.3128766513833</v>
+        <v>38.3128766600877</v>
       </c>
     </row>
     <row r="159">
@@ -26383,7 +26188,7 @@
         <v>39.3834924916548</v>
       </c>
       <c r="E159" t="n">
-        <v>36.1168753577615</v>
+        <v>36.1168753674917</v>
       </c>
     </row>
     <row r="160">
@@ -26400,7 +26205,7 @@
         <v>37.986009078204</v>
       </c>
       <c r="E160" t="n">
-        <v>34.0467435394462</v>
+        <v>34.0467435500559</v>
       </c>
     </row>
     <row r="161">
@@ -26417,7 +26222,7 @@
         <v>36.5885256647532</v>
       </c>
       <c r="E161" t="n">
-        <v>32.0952666629759</v>
+        <v>32.0952666743324</v>
       </c>
     </row>
     <row r="162">
@@ -26434,7 +26239,7 @@
         <v>35.6442372840716</v>
       </c>
       <c r="E162" t="n">
-        <v>30.2556437144734</v>
+        <v>30.2556437264563</v>
       </c>
     </row>
     <row r="163">
@@ -26451,7 +26256,7 @@
         <v>34.69994890339</v>
       </c>
       <c r="E163" t="n">
-        <v>29.194085041219</v>
+        <v>29.19408503833</v>
       </c>
     </row>
     <row r="164">
@@ -26468,7 +26273,7 @@
         <v>33.7556605227084</v>
       </c>
       <c r="E164" t="n">
-        <v>30.5394961840855</v>
+        <v>30.5394961811468</v>
       </c>
     </row>
     <row r="165">
@@ -26485,7 +26290,7 @@
         <v>33.6246995861829</v>
       </c>
       <c r="E165" t="n">
-        <v>31.9469106793706</v>
+        <v>31.9469106763837</v>
       </c>
     </row>
     <row r="166">
@@ -26502,7 +26307,7 @@
         <v>33.4937386496574</v>
       </c>
       <c r="E166" t="n">
-        <v>33.4191859552528</v>
+        <v>33.4191859522194</v>
       </c>
     </row>
     <row r="167">
@@ -26519,7 +26324,7 @@
         <v>33.362777713132</v>
       </c>
       <c r="E167" t="n">
-        <v>34.9593111246576</v>
+        <v>34.9593111215799</v>
       </c>
     </row>
     <row r="168">
@@ -26536,7 +26341,7 @@
         <v>34.953813783425</v>
       </c>
       <c r="E168" t="n">
-        <v>36.5704130539575</v>
+        <v>36.5704130508378</v>
       </c>
     </row>
     <row r="169">
@@ -26553,7 +26358,7 @@
         <v>36.5448498537181</v>
       </c>
       <c r="E169" t="n">
-        <v>38.2557627113473</v>
+        <v>38.2557627081882</v>
       </c>
     </row>
     <row r="170">
@@ -26570,7 +26375,7 @@
         <v>38.1358859240112</v>
       </c>
       <c r="E170" t="n">
-        <v>40.0187818077854</v>
+        <v>40.0187818045899</v>
       </c>
     </row>
     <row r="171">
@@ -26587,7 +26392,7 @@
         <v>41.7141977772194</v>
       </c>
       <c r="E171" t="n">
-        <v>41.8630497439827</v>
+        <v>41.8630497407543</v>
       </c>
     </row>
     <row r="172">
@@ -26604,7 +26409,7 @@
         <v>45.2925096304276</v>
       </c>
       <c r="E172" t="n">
-        <v>43.7923108775448</v>
+        <v>43.7923108742871</v>
       </c>
     </row>
     <row r="173">
@@ -26621,7 +26426,7 @@
         <v>48.8708214836359</v>
       </c>
       <c r="E173" t="n">
-        <v>45.8104821250197</v>
+        <v>45.810482121737</v>
       </c>
     </row>
     <row r="174">
@@ -26638,7 +26443,7 @@
         <v>52.6868608739992</v>
       </c>
       <c r="E174" t="n">
-        <v>47.9216609142871</v>
+        <v>47.9216609109839</v>
       </c>
     </row>
     <row r="175">
@@ -26655,7 +26460,7 @@
         <v>56.5029002643626</v>
       </c>
       <c r="E175" t="n">
-        <v>50.130133503434</v>
+        <v>50.1301335001153</v>
       </c>
     </row>
     <row r="176">
@@ -26672,7 +26477,7 @@
         <v>60.3189396547259</v>
       </c>
       <c r="E176" t="n">
-        <v>52.4403836830057</v>
+        <v>52.4403836796773</v>
       </c>
     </row>
     <row r="177">
@@ -26689,7 +26494,7 @@
         <v>63.5432416791373</v>
       </c>
       <c r="E177" t="n">
-        <v>54.8571018793013</v>
+        <v>54.8571018759692</v>
       </c>
     </row>
     <row r="178">
@@ -26706,7 +26511,7 @@
         <v>66.7675437035487</v>
       </c>
       <c r="E178" t="n">
-        <v>57.3851946771941</v>
+        <v>57.3851946738652</v>
       </c>
     </row>
     <row r="179">
@@ -26723,7 +26528,7 @@
         <v>69.9918457279601</v>
       </c>
       <c r="E179" t="n">
-        <v>60.0297947818131</v>
+        <v>60.0297947784946</v>
       </c>
     </row>
     <row r="180">
@@ -26740,7 +26545,7 @@
         <v>73.0385937863855</v>
       </c>
       <c r="E180" t="n">
-        <v>62.7962714393076</v>
+        <v>62.7962714360076</v>
       </c>
     </row>
     <row r="181">
@@ -26757,7 +26562,7 @@
         <v>76.0853418448109</v>
       </c>
       <c r="E181" t="n">
-        <v>65.6902413378549</v>
+        <v>65.6902413345822</v>
       </c>
     </row>
     <row r="182">
@@ -26774,7 +26579,7 @@
         <v>79.1320899032363</v>
       </c>
       <c r="E182" t="n">
-        <v>68.7175800110401</v>
+        <v>68.7175800078043</v>
       </c>
     </row>
     <row r="183">
@@ -26791,7 +26596,7 @@
         <v>82.313616735394</v>
       </c>
       <c r="E183" t="n">
-        <v>71.8844337667631</v>
+        <v>71.8844337635742</v>
       </c>
     </row>
     <row r="184">
@@ -26808,7 +26613,7 @@
         <v>85.4951435675517</v>
       </c>
       <c r="E184" t="n">
-        <v>75.1972321658875</v>
+        <v>75.197232162757</v>
       </c>
     </row>
     <row r="185">
@@ -26825,7 +26630,7 @@
         <v>88.6766703997095</v>
       </c>
       <c r="E185" t="n">
-        <v>78.6627010759721</v>
+        <v>78.662701072912</v>
       </c>
     </row>
     <row r="186">
@@ -26842,7 +26647,7 @@
         <v>92.5557970035985</v>
       </c>
       <c r="E186" t="n">
-        <v>82.2878763265807</v>
+        <v>82.2878763236043</v>
       </c>
     </row>
     <row r="187">
@@ -26859,7 +26664,7 @@
         <v>96.4349236074875</v>
       </c>
       <c r="E187" t="n">
-        <v>86.0801179939012</v>
+        <v>86.0801179910225</v>
       </c>
     </row>
     <row r="188">
@@ -26876,7 +26681,7 @@
         <v>100.314050211377</v>
       </c>
       <c r="E188" t="n">
-        <v>90.047125343669</v>
+        <v>90.0471253409035</v>
       </c>
     </row>
     <row r="189">
@@ -26893,7 +26698,7 @@
         <v>104.765887156734</v>
       </c>
       <c r="E189" t="n">
-        <v>94.1969524627386</v>
+        <v>94.1969524601027</v>
       </c>
     </row>
     <row r="190">
@@ -26910,7 +26715,7 @@
         <v>109.217724102092</v>
       </c>
       <c r="E190" t="n">
-        <v>98.5380246110351</v>
+        <v>98.5380246085469</v>
       </c>
     </row>
     <row r="191">
@@ -26927,7 +26732,7 @@
         <v>113.669561047449</v>
       </c>
       <c r="E191" t="n">
-        <v>103.079155327088</v>
+        <v>103.079155324767</v>
       </c>
     </row>
     <row r="192">
@@ -26944,7 +26749,7 @@
         <v>119.823598381423</v>
       </c>
       <c r="E192" t="n">
-        <v>107.829564321874</v>
+        <v>107.829564319739</v>
       </c>
     </row>
     <row r="193">
@@ -26961,7 +26766,7 @@
         <v>125.977635715396</v>
       </c>
       <c r="E193" t="n">
-        <v>112.798896197295</v>
+        <v>112.79889619537</v>
       </c>
     </row>
     <row r="194">
@@ -26978,7 +26783,7 @@
         <v>132.13167304937</v>
       </c>
       <c r="E194" t="n">
-        <v>117.997240027308</v>
+        <v>117.997240025616</v>
       </c>
     </row>
     <row r="195">
@@ -26995,7 +26800,7 @@
         <v>138.630712010976</v>
       </c>
       <c r="E195" t="n">
-        <v>123.43514984144</v>
+        <v>123.435149840007</v>
       </c>
     </row>
     <row r="196">
@@ -27012,7 +26817,7 @@
         <v>145.129750972582</v>
       </c>
       <c r="E196" t="n">
-        <v>129.123666052295</v>
+        <v>129.123666051149</v>
       </c>
     </row>
     <row r="197">
@@ -27029,7 +26834,7 @@
         <v>151.628789934187</v>
       </c>
       <c r="E197" t="n">
-        <v>135.074337870551</v>
+        <v>135.074337869721</v>
       </c>
     </row>
     <row r="198">
@@ -27046,7 +26851,7 @@
         <v>158.64203447226</v>
       </c>
       <c r="E198" t="n">
-        <v>141.299246752941</v>
+        <v>141.299246752459</v>
       </c>
     </row>
     <row r="199">
@@ -27063,7 +26868,7 @@
         <v>165.655279010333</v>
       </c>
       <c r="E199" t="n">
-        <v>147.811030930854</v>
+        <v>147.811030930754</v>
       </c>
     </row>
     <row r="200">
@@ -27080,7 +26885,7 @@
         <v>172.668523548405</v>
       </c>
       <c r="E200" t="n">
-        <v>154.62291106932</v>
+        <v>154.622911069637</v>
       </c>
     </row>
     <row r="201">
@@ -27097,7 +26902,7 @@
         <v>180.756146040923</v>
       </c>
       <c r="E201" t="n">
-        <v>161.748717108503</v>
+        <v>161.748717109276</v>
       </c>
     </row>
     <row r="202">
@@ -27114,7 +26919,7 @@
         <v>188.843768533441</v>
       </c>
       <c r="E202" t="n">
-        <v>169.20291634218</v>
+        <v>169.20291634345</v>
       </c>
     </row>
     <row r="203">
@@ -27131,7 +26936,7 @@
         <v>196.931391025958</v>
       </c>
       <c r="E203" t="n">
-        <v>177.000642790221</v>
+        <v>177.000642792033</v>
       </c>
     </row>
     <row r="204">
@@ -27148,7 +26953,7 @@
         <v>204.756026605648</v>
       </c>
       <c r="E204" t="n">
-        <v>185.157727924703</v>
+        <v>185.157727927103</v>
       </c>
     </row>
     <row r="205">
@@ -27165,7 +26970,7 @@
         <v>212.580662185338</v>
       </c>
       <c r="E205" t="n">
-        <v>193.690732812029</v>
+        <v>193.690732815069</v>
       </c>
     </row>
     <row r="206">
@@ -27182,7 +26987,7 @@
         <v>220.405297765029</v>
       </c>
       <c r="E206" t="n">
-        <v>202.616981736336</v>
+        <v>202.616981740068</v>
       </c>
     </row>
     <row r="207">
@@ -27199,7 +27004,7 @@
         <v>223.619215533872</v>
       </c>
       <c r="E207" t="n">
-        <v>211.95459737242</v>
+        <v>211.954597376903</v>
       </c>
     </row>
     <row r="208">
@@ -27216,7 +27021,7 @@
         <v>226.833133302715</v>
       </c>
       <c r="E208" t="n">
-        <v>221.722537579623</v>
+        <v>221.722537584918</v>
       </c>
     </row>
     <row r="209">
@@ -27233,7 +27038,7 @@
         <v>230.047051071558</v>
       </c>
       <c r="E209" t="n">
-        <v>231.940633891362</v>
+        <v>231.940633897535</v>
       </c>
     </row>
     <row r="210">
@@ -27250,7 +27055,7 @@
         <v>233.94105022472</v>
       </c>
       <c r="E210" t="n">
-        <v>242.629631778447</v>
+        <v>242.629631785566</v>
       </c>
     </row>
     <row r="211">
@@ -27267,7 +27072,7 @@
         <v>237.835049377882</v>
       </c>
       <c r="E211" t="n">
-        <v>253.811232767944</v>
+        <v>253.811232776084</v>
       </c>
     </row>
     <row r="212">
@@ -27284,7 +27089,7 @@
         <v>241.729048531044</v>
       </c>
       <c r="E212" t="n">
-        <v>265.508138503079</v>
+        <v>265.50813851232</v>
       </c>
     </row>
     <row r="213">
@@ -27301,7 +27106,7 @@
         <v>245.49755297727</v>
       </c>
       <c r="E213" t="n">
-        <v>277.74409683366</v>
+        <v>277.744096844085</v>
       </c>
     </row>
     <row r="214">
@@ -27318,7 +27123,7 @@
         <v>249.266057423497</v>
       </c>
       <c r="E214" t="n">
-        <v>290.54395003056</v>
+        <v>290.543950042258</v>
       </c>
     </row>
     <row r="215">
@@ -27335,7 +27140,7 @@
         <v>253.034561869723</v>
       </c>
       <c r="E215" t="n">
-        <v>303.933685222181</v>
+        <v>303.933685235248</v>
       </c>
     </row>
     <row r="216">
@@ -27352,7 +27157,7 @@
         <v>256.573967912691</v>
       </c>
       <c r="E216" t="n">
-        <v>317.940487155281</v>
+        <v>317.940487169817</v>
       </c>
     </row>
     <row r="217">
@@ -27369,7 +27174,7 @@
         <v>260.113373955659</v>
       </c>
       <c r="E217" t="n">
-        <v>332.592793387286</v>
+        <v>332.5927934034</v>
       </c>
     </row>
   </sheetData>
@@ -27414,7 +27219,7 @@
         <v>0.159098184570432</v>
       </c>
       <c r="E2" t="n">
-        <v>0.144842301664242</v>
+        <v>0.144842301664348</v>
       </c>
     </row>
     <row r="3">
@@ -27431,7 +27236,7 @@
         <v>0.158858250638995</v>
       </c>
       <c r="E3" t="n">
-        <v>0.14675232122941</v>
+        <v>0.146752321229508</v>
       </c>
     </row>
     <row r="4">
@@ -27448,7 +27253,7 @@
         <v>0.158618316707557</v>
       </c>
       <c r="E4" t="n">
-        <v>0.14868752801334</v>
+        <v>0.148687528013441</v>
       </c>
     </row>
     <row r="5">
@@ -27465,7 +27270,7 @@
         <v>0.15837838277612</v>
       </c>
       <c r="E5" t="n">
-        <v>0.150648254157138</v>
+        <v>0.150648254157238</v>
       </c>
     </row>
     <row r="6">
@@ -27482,7 +27287,7 @@
         <v>0.158243665856567</v>
       </c>
       <c r="E6" t="n">
-        <v>0.152634836181804</v>
+        <v>0.152634836181902</v>
       </c>
     </row>
     <row r="7">
@@ -27499,7 +27304,7 @@
         <v>0.158108948937014</v>
       </c>
       <c r="E7" t="n">
-        <v>0.154647615046008</v>
+        <v>0.154647615046104</v>
       </c>
     </row>
     <row r="8">
@@ -27516,7 +27321,7 @@
         <v>0.157974232017462</v>
       </c>
       <c r="E8" t="n">
-        <v>0.156686936204602</v>
+        <v>0.156686936204697</v>
       </c>
     </row>
     <row r="9">
@@ -27533,7 +27338,7 @@
         <v>0.158043187548997</v>
       </c>
       <c r="E9" t="n">
-        <v>0.158753149667915</v>
+        <v>0.158753149668008</v>
       </c>
     </row>
     <row r="10">
@@ -27550,7 +27355,7 @@
         <v>0.158112143080532</v>
       </c>
       <c r="E10" t="n">
-        <v>0.160846610061824</v>
+        <v>0.160846610061915</v>
       </c>
     </row>
     <row r="11">
@@ -27567,7 +27372,7 @@
         <v>0.158181098612066</v>
       </c>
       <c r="E11" t="n">
-        <v>0.162967676688617</v>
+        <v>0.162967676688706</v>
       </c>
     </row>
     <row r="12">
@@ -27584,7 +27389,7 @@
         <v>0.158536017536113</v>
       </c>
       <c r="E12" t="n">
-        <v>0.165116713588663</v>
+        <v>0.165116713588751</v>
       </c>
     </row>
     <row r="13">
@@ -27601,7 +27406,7 @@
         <v>0.158890936460159</v>
       </c>
       <c r="E13" t="n">
-        <v>0.167294089602892</v>
+        <v>0.167294089602978</v>
       </c>
     </row>
     <row r="14">
@@ -27618,7 +27423,7 @@
         <v>0.159245855384205</v>
       </c>
       <c r="E14" t="n">
-        <v>0.169500178436098</v>
+        <v>0.169500178436182</v>
       </c>
     </row>
     <row r="15">
@@ -27635,7 +27440,7 @@
         <v>0.160806216921749</v>
       </c>
       <c r="E15" t="n">
-        <v>0.171735358721079</v>
+        <v>0.171735358721161</v>
       </c>
     </row>
     <row r="16">
@@ -27652,7 +27457,7 @@
         <v>0.162366578459293</v>
       </c>
       <c r="E16" t="n">
-        <v>0.174000014083624</v>
+        <v>0.174000014083703</v>
       </c>
     </row>
     <row r="17">
@@ -27669,7 +27474,7 @@
         <v>0.163926939996836</v>
       </c>
       <c r="E17" t="n">
-        <v>0.17629453320835</v>
+        <v>0.176294533208428</v>
       </c>
     </row>
     <row r="18">
@@ -27686,7 +27491,7 @@
         <v>0.16619823314299</v>
       </c>
       <c r="E18" t="n">
-        <v>0.178619309905419</v>
+        <v>0.178619309905494</v>
       </c>
     </row>
     <row r="19">
@@ -27703,7 +27508,7 @@
         <v>0.168469526289143</v>
       </c>
       <c r="E19" t="n">
-        <v>0.180974743178123</v>
+        <v>0.180974743178196</v>
       </c>
     </row>
     <row r="20">
@@ -27720,7 +27525,7 @@
         <v>0.170740819435297</v>
       </c>
       <c r="E20" t="n">
-        <v>0.183361237291365</v>
+        <v>0.183361237291436</v>
       </c>
     </row>
     <row r="21">
@@ -27737,7 +27542,7 @@
         <v>0.173928506424126</v>
       </c>
       <c r="E21" t="n">
-        <v>0.185779201841048</v>
+        <v>0.185779201841116</v>
       </c>
     </row>
     <row r="22">
@@ -27754,7 +27559,7 @@
         <v>0.177116193412954</v>
       </c>
       <c r="E22" t="n">
-        <v>0.18822905182437</v>
+        <v>0.188229051824435</v>
       </c>
     </row>
     <row r="23">
@@ -27771,7 +27576,7 @@
         <v>0.180303880401783</v>
       </c>
       <c r="E23" t="n">
-        <v>0.19071120771105</v>
+        <v>0.190711207711113</v>
       </c>
     </row>
     <row r="24">
@@ -27788,7 +27593,7 @@
         <v>0.183233529405899</v>
       </c>
       <c r="E24" t="n">
-        <v>0.193226095515498</v>
+        <v>0.193226095515558</v>
       </c>
     </row>
     <row r="25">
@@ -27805,7 +27610,7 @@
         <v>0.186163178410016</v>
       </c>
       <c r="E25" t="n">
-        <v>0.195774146869928</v>
+        <v>0.195774146869985</v>
       </c>
     </row>
     <row r="26">
@@ -27822,7 +27627,7 @@
         <v>0.189092827414132</v>
       </c>
       <c r="E26" t="n">
-        <v>0.19835579909844</v>
+        <v>0.198355799098494</v>
       </c>
     </row>
     <row r="27">
@@ -27839,7 +27644,7 @@
         <v>0.190237798287628</v>
       </c>
       <c r="E27" t="n">
-        <v>0.200971495292079</v>
+        <v>0.200971495292131</v>
       </c>
     </row>
     <row r="28">
@@ -27856,7 +27661,7 @@
         <v>0.191382769161124</v>
       </c>
       <c r="E28" t="n">
-        <v>0.203621684384886</v>
+        <v>0.203621684384934</v>
       </c>
     </row>
     <row r="29">
@@ -27873,7 +27678,7 @@
         <v>0.192527740034621</v>
       </c>
       <c r="E29" t="n">
-        <v>0.206306821230941</v>
+        <v>0.206306821230987</v>
       </c>
     </row>
     <row r="30">
@@ -27890,7 +27695,7 @@
         <v>0.192479631622702</v>
       </c>
       <c r="E30" t="n">
-        <v>0.20902736668244</v>
+        <v>0.209027366682482</v>
       </c>
     </row>
     <row r="31">
@@ -27907,7 +27712,7 @@
         <v>0.192431523210784</v>
       </c>
       <c r="E31" t="n">
-        <v>0.211783787668783</v>
+        <v>0.211783787668822</v>
       </c>
     </row>
     <row r="32">
@@ -27924,7 +27729,7 @@
         <v>0.192383414798865</v>
       </c>
       <c r="E32" t="n">
-        <v>0.214576557276719</v>
+        <v>0.214576557276754</v>
       </c>
     </row>
     <row r="33">
@@ -27941,7 +27746,7 @@
         <v>0.191994996056851</v>
       </c>
       <c r="E33" t="n">
-        <v>0.217406154831537</v>
+        <v>0.217406154831569</v>
       </c>
     </row>
     <row r="34">
@@ -27958,7 +27763,7 @@
         <v>0.191606577314838</v>
       </c>
       <c r="E34" t="n">
-        <v>0.22027306597934</v>
+        <v>0.220273065979368</v>
       </c>
     </row>
     <row r="35">
@@ -27975,7 +27780,7 @@
         <v>0.191218158572824</v>
       </c>
       <c r="E35" t="n">
-        <v>0.217285725761754</v>
+        <v>0.217285725761663</v>
       </c>
     </row>
     <row r="36">
@@ -27992,7 +27797,7 @@
         <v>0.189678830685113</v>
       </c>
       <c r="E36" t="n">
-        <v>0.214338494530671</v>
+        <v>0.214338494530582</v>
       </c>
     </row>
     <row r="37">
@@ -28009,7 +27814,7 @@
         <v>0.188139502797403</v>
       </c>
       <c r="E37" t="n">
-        <v>0.211431239105173</v>
+        <v>0.211431239105086</v>
       </c>
     </row>
     <row r="38">
@@ -28026,7 +27831,7 @@
         <v>0.186600174909693</v>
       </c>
       <c r="E38" t="n">
-        <v>0.208563417259385</v>
+        <v>0.2085634172593</v>
       </c>
     </row>
     <row r="39">
@@ -28043,7 +27848,7 @@
         <v>0.184646740819725</v>
       </c>
       <c r="E39" t="n">
-        <v>0.205734494122104</v>
+        <v>0.205734494122021</v>
       </c>
     </row>
     <row r="40">
@@ -28060,7 +27865,7 @@
         <v>0.182693306729757</v>
       </c>
       <c r="E40" t="n">
-        <v>0.202943942077039</v>
+        <v>0.202943942076959</v>
       </c>
     </row>
     <row r="41">
@@ -28077,7 +27882,7 @@
         <v>0.18073987263979</v>
       </c>
       <c r="E41" t="n">
-        <v>0.20019124066441</v>
+        <v>0.200191240664331</v>
       </c>
     </row>
     <row r="42">
@@ -28094,7 +27899,7 @@
         <v>0.17992286005204</v>
       </c>
       <c r="E42" t="n">
-        <v>0.197475876483873</v>
+        <v>0.197475876483796</v>
       </c>
     </row>
     <row r="43">
@@ -28111,7 +27916,7 @@
         <v>0.179105847464291</v>
       </c>
       <c r="E43" t="n">
-        <v>0.194797343098771</v>
+        <v>0.194797343098697</v>
       </c>
     </row>
     <row r="44">
@@ -28128,7 +27933,7 @@
         <v>0.178288834876541</v>
       </c>
       <c r="E44" t="n">
-        <v>0.192155140941681</v>
+        <v>0.192155140941608</v>
       </c>
     </row>
     <row r="45">
@@ -28145,7 +27950,7 @@
         <v>0.179042431173914</v>
       </c>
       <c r="E45" t="n">
-        <v>0.189548777221233</v>
+        <v>0.189548777221163</v>
       </c>
     </row>
     <row r="46">
@@ -28162,7 +27967,7 @@
         <v>0.179796027471287</v>
       </c>
       <c r="E46" t="n">
-        <v>0.186977765830211</v>
+        <v>0.186977765830142</v>
       </c>
     </row>
     <row r="47">
@@ -28179,7 +27984,7 @@
         <v>0.180549623768661</v>
       </c>
       <c r="E47" t="n">
-        <v>0.18444162725488</v>
+        <v>0.184441627254814</v>
       </c>
     </row>
     <row r="48">
@@ -28196,7 +28001,7 @@
         <v>0.181027987213799</v>
       </c>
       <c r="E48" t="n">
-        <v>0.181939888485563</v>
+        <v>0.181939888485498</v>
       </c>
     </row>
     <row r="49">
@@ -28213,7 +28018,7 @@
         <v>0.181506350658937</v>
       </c>
       <c r="E49" t="n">
-        <v>0.179472082928412</v>
+        <v>0.179472082928349</v>
       </c>
     </row>
     <row r="50">
@@ -28230,7 +28035,7 @@
         <v>0.181984714104075</v>
       </c>
       <c r="E50" t="n">
-        <v>0.17703775031839</v>
+        <v>0.177037750318329</v>
       </c>
     </row>
     <row r="51">
@@ -28247,7 +28052,7 @@
         <v>0.182821390041931</v>
       </c>
       <c r="E51" t="n">
-        <v>0.174636436633426</v>
+        <v>0.174636436633366</v>
       </c>
     </row>
     <row r="52">
@@ -28264,7 +28069,7 @@
         <v>0.183658065979786</v>
       </c>
       <c r="E52" t="n">
-        <v>0.172267694009736</v>
+        <v>0.172267694009678</v>
       </c>
     </row>
     <row r="53">
@@ -28281,7 +28086,7 @@
         <v>0.184494741917642</v>
       </c>
       <c r="E53" t="n">
-        <v>0.169931080658297</v>
+        <v>0.16993108065824</v>
       </c>
     </row>
     <row r="54">
@@ -28298,7 +28103,7 @@
         <v>0.185611022650923</v>
       </c>
       <c r="E54" t="n">
-        <v>0.167626160782441</v>
+        <v>0.167626160782387</v>
       </c>
     </row>
     <row r="55">
@@ -28315,7 +28120,7 @@
         <v>0.186727303384205</v>
       </c>
       <c r="E55" t="n">
-        <v>0.165352504496587</v>
+        <v>0.165352504496534</v>
       </c>
     </row>
     <row r="56">
@@ -28332,7 +28137,7 @@
         <v>0.187843584117486</v>
       </c>
       <c r="E56" t="n">
-        <v>0.163109687746054</v>
+        <v>0.163109687746002</v>
       </c>
     </row>
     <row r="57">
@@ -28349,7 +28154,7 @@
         <v>0.187607462630365</v>
       </c>
       <c r="E57" t="n">
-        <v>0.160897292227977</v>
+        <v>0.160897292227927</v>
       </c>
     </row>
     <row r="58">
@@ -28366,7 +28171,7 @@
         <v>0.187371341143244</v>
       </c>
       <c r="E58" t="n">
-        <v>0.158714905313289</v>
+        <v>0.15871490531324</v>
       </c>
     </row>
     <row r="59">
@@ -28383,7 +28188,7 @@
         <v>0.187135219656123</v>
       </c>
       <c r="E59" t="n">
-        <v>0.156562119969761</v>
+        <v>0.156562119969713</v>
       </c>
     </row>
     <row r="60">
@@ -28400,7 +28205,7 @@
         <v>0.185283572613553</v>
       </c>
       <c r="E60" t="n">
-        <v>0.154438534686089</v>
+        <v>0.154438534686044</v>
       </c>
     </row>
     <row r="61">
@@ -28417,7 +28222,7 @@
         <v>0.183431925570982</v>
       </c>
       <c r="E61" t="n">
-        <v>0.152343753397011</v>
+        <v>0.152343753396966</v>
       </c>
     </row>
     <row r="62">
@@ -28434,7 +28239,7 @@
         <v>0.181580278528411</v>
       </c>
       <c r="E62" t="n">
-        <v>0.150277385409431</v>
+        <v>0.150277385409388</v>
       </c>
     </row>
     <row r="63">
@@ -28451,7 +28256,7 @@
         <v>0.179671220405439</v>
       </c>
       <c r="E63" t="n">
-        <v>0.148239045329559</v>
+        <v>0.148239045329517</v>
       </c>
     </row>
     <row r="64">
@@ -28468,7 +28273,7 @@
         <v>0.177762162282467</v>
       </c>
       <c r="E64" t="n">
-        <v>0.146228352991028</v>
+        <v>0.146228352990988</v>
       </c>
     </row>
     <row r="65">
@@ -28485,7 +28290,7 @@
         <v>0.175853104159495</v>
       </c>
       <c r="E65" t="n">
-        <v>0.144244933383992</v>
+        <v>0.144244933383953</v>
       </c>
     </row>
     <row r="66">
@@ -28502,7 +28307,7 @@
         <v>0.173123725462984</v>
       </c>
       <c r="E66" t="n">
-        <v>0.14228841658518</v>
+        <v>0.142288416585142</v>
       </c>
     </row>
     <row r="67">
@@ -28519,7 +28324,7 @@
         <v>0.170394346766474</v>
       </c>
       <c r="E67" t="n">
-        <v>0.140358437688909</v>
+        <v>0.140358437688872</v>
       </c>
     </row>
     <row r="68">
@@ -28536,7 +28341,7 @@
         <v>0.167664968069964</v>
       </c>
       <c r="E68" t="n">
-        <v>0.138454636739019</v>
+        <v>0.138454636738983</v>
       </c>
     </row>
     <row r="69">
@@ -28553,7 +28358,7 @@
         <v>0.164146244938319</v>
       </c>
       <c r="E69" t="n">
-        <v>0.136576658661743</v>
+        <v>0.136576658661708</v>
       </c>
     </row>
     <row r="70">
@@ -28570,7 +28375,7 @@
         <v>0.160627521806675</v>
       </c>
       <c r="E70" t="n">
-        <v>0.134724153199482</v>
+        <v>0.134724153199449</v>
       </c>
     </row>
     <row r="71">
@@ -28587,7 +28392,7 @@
         <v>0.15710879867503</v>
       </c>
       <c r="E71" t="n">
-        <v>0.13289677484548</v>
+        <v>0.132896774845447</v>
       </c>
     </row>
     <row r="72">
@@ -28604,7 +28409,7 @@
         <v>0.15295556166299</v>
       </c>
       <c r="E72" t="n">
-        <v>0.13109418277938</v>
+        <v>0.131094182779349</v>
       </c>
     </row>
     <row r="73">
@@ -28621,7 +28426,7 @@
         <v>0.14880232465095</v>
       </c>
       <c r="E73" t="n">
-        <v>0.129316040803665</v>
+        <v>0.129316040803635</v>
       </c>
     </row>
     <row r="74">
@@ -28638,7 +28443,7 @@
         <v>0.14464908763891</v>
       </c>
       <c r="E74" t="n">
-        <v>0.127562017280948</v>
+        <v>0.127562017280919</v>
       </c>
     </row>
     <row r="75">
@@ -28655,7 +28460,7 @@
         <v>0.140739141606624</v>
       </c>
       <c r="E75" t="n">
-        <v>0.125831785072126</v>
+        <v>0.125831785072098</v>
       </c>
     </row>
     <row r="76">
@@ -28672,7 +28477,7 @@
         <v>0.136829195574339</v>
       </c>
       <c r="E76" t="n">
-        <v>0.124125021475357</v>
+        <v>0.12412502147533</v>
       </c>
     </row>
     <row r="77">
@@ -28689,7 +28494,7 @@
         <v>0.132919249542053</v>
       </c>
       <c r="E77" t="n">
-        <v>0.122441408165884</v>
+        <v>0.122441408165858</v>
       </c>
     </row>
     <row r="78">
@@ -28706,7 +28511,7 @@
         <v>0.129514006435575</v>
       </c>
       <c r="E78" t="n">
-        <v>0.120780631136656</v>
+        <v>0.120780631136631</v>
       </c>
     </row>
     <row r="79">
@@ -28723,7 +28528,7 @@
         <v>0.126108763329097</v>
       </c>
       <c r="E79" t="n">
-        <v>0.119142380639768</v>
+        <v>0.119142380639743</v>
       </c>
     </row>
     <row r="80">
@@ -28740,7 +28545,7 @@
         <v>0.122703520222618</v>
       </c>
       <c r="E80" t="n">
-        <v>0.117526351128689</v>
+        <v>0.117526351128666</v>
       </c>
     </row>
     <row r="81">
@@ -28757,7 +28562,7 @@
         <v>0.1193967365134</v>
       </c>
       <c r="E81" t="n">
-        <v>0.115932241201277</v>
+        <v>0.115932241201255</v>
       </c>
     </row>
     <row r="82">
@@ -28774,7 +28579,7 @@
         <v>0.116089952804181</v>
       </c>
       <c r="E82" t="n">
-        <v>0.114359753543563</v>
+        <v>0.114359753543541</v>
       </c>
     </row>
     <row r="83">
@@ -28791,7 +28596,7 @@
         <v>0.112783169094962</v>
       </c>
       <c r="E83" t="n">
-        <v>0.112808594874299</v>
+        <v>0.112808594874278</v>
       </c>
     </row>
     <row r="84">
@@ -28808,7 +28613,7 @@
         <v>0.109169063864951</v>
       </c>
       <c r="E84" t="n">
-        <v>0.111278475890263</v>
+        <v>0.111278475890243</v>
       </c>
     </row>
     <row r="85">
@@ -28825,7 +28630,7 @@
         <v>0.10555495863494</v>
       </c>
       <c r="E85" t="n">
-        <v>0.109769111212296</v>
+        <v>0.109769111212277</v>
       </c>
     </row>
     <row r="86">
@@ -28842,7 +28647,7 @@
         <v>0.101940853404929</v>
       </c>
       <c r="E86" t="n">
-        <v>0.108280219332082</v>
+        <v>0.108280219332064</v>
       </c>
     </row>
     <row r="87">
@@ -28859,7 +28664,7 @@
         <v>0.099340565500944</v>
       </c>
       <c r="E87" t="n">
-        <v>0.106811522559639</v>
+        <v>0.106811522559622</v>
       </c>
     </row>
     <row r="88">
@@ -28876,7 +28681,7 @@
         <v>0.0967402775969591</v>
       </c>
       <c r="E88" t="n">
-        <v>0.105362746971534</v>
+        <v>0.105362746971518</v>
       </c>
     </row>
     <row r="89">
@@ -28893,7 +28698,7 @@
         <v>0.0941399896929743</v>
       </c>
       <c r="E89" t="n">
-        <v>0.103933622359788</v>
+        <v>0.103933622359772</v>
       </c>
     </row>
     <row r="90">
@@ -28910,7 +28715,7 @@
         <v>0.0922033306712248</v>
       </c>
       <c r="E90" t="n">
-        <v>0.102523882181484</v>
+        <v>0.102523882181469</v>
       </c>
     </row>
     <row r="91">
@@ -28927,7 +28732,7 @@
         <v>0.0902666716494752</v>
       </c>
       <c r="E91" t="n">
-        <v>0.101133263509052</v>
+        <v>0.101133263509038</v>
       </c>
     </row>
     <row r="92">
@@ -28944,7 +28749,7 @@
         <v>0.0883300126277257</v>
       </c>
       <c r="E92" t="n">
-        <v>0.0997615069812346</v>
+        <v>0.0997615069812207</v>
       </c>
     </row>
     <row r="93">
@@ -28961,7 +28766,7 @@
         <v>0.0861294300285648</v>
       </c>
       <c r="E93" t="n">
-        <v>0.0984083567547102</v>
+        <v>0.098408356754697</v>
       </c>
     </row>
     <row r="94">
@@ -28978,7 +28783,7 @@
         <v>0.0839288474294038</v>
       </c>
       <c r="E94" t="n">
-        <v>0.0970735604563787</v>
+        <v>0.0970735604563662</v>
       </c>
     </row>
     <row r="95">
@@ -28995,7 +28800,7 @@
         <v>0.0817282648302429</v>
       </c>
       <c r="E95" t="n">
-        <v>0.0957568691362908</v>
+        <v>0.0957568691362789</v>
       </c>
     </row>
     <row r="96">
@@ -29012,7 +28817,7 @@
         <v>0.0798845367710929</v>
       </c>
       <c r="E96" t="n">
-        <v>0.0944580372212175</v>
+        <v>0.0944580372212062</v>
       </c>
     </row>
     <row r="97">
@@ -29029,7 +28834,7 @@
         <v>0.0780408087119429</v>
       </c>
       <c r="E97" t="n">
-        <v>0.0931768224688483</v>
+        <v>0.0931768224688377</v>
       </c>
     </row>
     <row r="98">
@@ -29046,7 +28851,7 @@
         <v>0.0761970806527929</v>
       </c>
       <c r="E98" t="n">
-        <v>0.0919129859226115</v>
+        <v>0.0919129859226015</v>
       </c>
     </row>
     <row r="99">
@@ -29063,7 +28868,7 @@
         <v>0.0752817988300912</v>
       </c>
       <c r="E99" t="n">
-        <v>0.0906662918671066</v>
+        <v>0.0906662918670971</v>
       </c>
     </row>
     <row r="100">
@@ -29080,7 +28885,7 @@
         <v>0.0743665170073895</v>
       </c>
       <c r="E100" t="n">
-        <v>0.0894365077841418</v>
+        <v>0.089436507784133</v>
       </c>
     </row>
     <row r="101">
@@ -29097,7 +28902,7 @@
         <v>0.0734512351846878</v>
       </c>
       <c r="E101" t="n">
-        <v>0.0882234043093675</v>
+        <v>0.0882234043093591</v>
       </c>
     </row>
     <row r="102">
@@ -29114,7 +28919,7 @@
         <v>0.0730436949264373</v>
       </c>
       <c r="E102" t="n">
-        <v>0.0870267551894978</v>
+        <v>0.08702675518949</v>
       </c>
     </row>
     <row r="103">
@@ -29131,7 +28936,7 @@
         <v>0.0726361546681869</v>
       </c>
       <c r="E103" t="n">
-        <v>0.0858463372401128</v>
+        <v>0.0858463372401055</v>
       </c>
     </row>
     <row r="104">
@@ -29148,7 +28953,7 @@
         <v>0.0722286144099365</v>
       </c>
       <c r="E104" t="n">
-        <v>0.0846819303040327</v>
+        <v>0.084681930304026</v>
       </c>
     </row>
     <row r="105">
@@ -29165,7 +28970,7 @@
         <v>0.0725086623425093</v>
       </c>
       <c r="E105" t="n">
-        <v>0.0835333172102572</v>
+        <v>0.0835333172102509</v>
       </c>
     </row>
     <row r="106">
@@ -29182,7 +28987,7 @@
         <v>0.0727887102750822</v>
       </c>
       <c r="E106" t="n">
-        <v>0.0824002837334608</v>
+        <v>0.0824002837334551</v>
       </c>
     </row>
     <row r="107">
@@ -29199,7 +29004,7 @@
         <v>0.073068758207655</v>
       </c>
       <c r="E107" t="n">
-        <v>0.0812826185540387</v>
+        <v>0.0812826185540334</v>
       </c>
     </row>
     <row r="108">
@@ -29216,7 +29021,7 @@
         <v>0.0748444863132765</v>
       </c>
       <c r="E108" t="n">
-        <v>0.0801801132186934</v>
+        <v>0.0801801132186886</v>
       </c>
     </row>
     <row r="109">
@@ -29233,7 +29038,7 @@
         <v>0.076620214418898</v>
       </c>
       <c r="E109" t="n">
-        <v>0.0790925621015573</v>
+        <v>0.079092562101553</v>
       </c>
     </row>
     <row r="110">
@@ -29250,7 +29055,7 @@
         <v>0.0783959425245195</v>
       </c>
       <c r="E110" t="n">
-        <v>0.0780197623658411</v>
+        <v>0.0780197623658372</v>
       </c>
     </row>
     <row r="111">
@@ -29267,7 +29072,7 @@
         <v>0.0798718103144731</v>
       </c>
       <c r="E111" t="n">
-        <v>0.0769615139260038</v>
+        <v>0.0769615139260003</v>
       </c>
     </row>
     <row r="112">
@@ -29284,7 +29089,7 @@
         <v>0.0813476781044268</v>
       </c>
       <c r="E112" t="n">
-        <v>0.0759176194104346</v>
+        <v>0.0759176194104315</v>
       </c>
     </row>
     <row r="113">
@@ -29301,7 +29106,7 @@
         <v>0.0828235458943804</v>
       </c>
       <c r="E113" t="n">
-        <v>0.074887884124642</v>
+        <v>0.0748878841246393</v>
       </c>
     </row>
     <row r="114">
@@ -29318,7 +29123,7 @@
         <v>0.0825822811937095</v>
       </c>
       <c r="E114" t="n">
-        <v>0.0738721160149415</v>
+        <v>0.0738721160149394</v>
       </c>
     </row>
     <row r="115">
@@ -29335,7 +29140,7 @@
         <v>0.0823410164930386</v>
       </c>
       <c r="E115" t="n">
-        <v>0.0728701256326366</v>
+        <v>0.0728701256326347</v>
       </c>
     </row>
     <row r="116">
@@ -29352,7 +29157,7 @@
         <v>0.0820997517923678</v>
       </c>
       <c r="E116" t="n">
-        <v>0.0718817260986839</v>
+        <v>0.0718817260986824</v>
       </c>
     </row>
     <row r="117">
@@ -29369,7 +29174,7 @@
         <v>0.0815237508588604</v>
       </c>
       <c r="E117" t="n">
-        <v>0.0709067330688403</v>
+        <v>0.0709067330688392</v>
       </c>
     </row>
     <row r="118">
@@ -29386,7 +29191,7 @@
         <v>0.080947749925353</v>
       </c>
       <c r="E118" t="n">
-        <v>0.0699449646992802</v>
+        <v>0.0699449646992795</v>
       </c>
     </row>
     <row r="119">
@@ -29403,7 +29208,7 @@
         <v>0.0803717489918457</v>
       </c>
       <c r="E119" t="n">
-        <v>0.0689962416126806</v>
+        <v>0.0689962416126802</v>
       </c>
     </row>
     <row r="120">
@@ -29420,7 +29225,7 @@
         <v>0.0796837868369671</v>
       </c>
       <c r="E120" t="n">
-        <v>0.0680603868647657</v>
+        <v>0.0680603868647656</v>
       </c>
     </row>
     <row r="121">
@@ -29437,7 +29242,7 @@
         <v>0.0789958246820886</v>
       </c>
       <c r="E121" t="n">
-        <v>0.0671372259113058</v>
+        <v>0.0671372259113061</v>
       </c>
     </row>
     <row r="122">
@@ -29454,7 +29259,7 @@
         <v>0.0783078625272101</v>
       </c>
       <c r="E122" t="n">
-        <v>0.0662265865755629</v>
+        <v>0.0662265865755635</v>
       </c>
     </row>
     <row r="123">
@@ -29471,7 +29276,7 @@
         <v>0.0772176727510095</v>
       </c>
       <c r="E123" t="n">
-        <v>0.0653282990161787</v>
+        <v>0.0653282990161796</v>
       </c>
     </row>
     <row r="124">
@@ -29488,7 +29293,7 @@
         <v>0.0761274829748089</v>
       </c>
       <c r="E124" t="n">
-        <v>0.0644421956954979</v>
+        <v>0.0644421956954991</v>
       </c>
     </row>
     <row r="125">
@@ -29505,7 +29310,7 @@
         <v>0.0750372931986082</v>
       </c>
       <c r="E125" t="n">
-        <v>0.0635681113483208</v>
+        <v>0.0635681113483224</v>
       </c>
     </row>
     <row r="126">
@@ -29522,7 +29327,7 @@
         <v>0.0748704799939035</v>
       </c>
       <c r="E126" t="n">
-        <v>0.0627058829510806</v>
+        <v>0.0627058829510824</v>
       </c>
     </row>
     <row r="127">
@@ -29539,7 +29344,7 @@
         <v>0.0747036667891987</v>
       </c>
       <c r="E127" t="n">
-        <v>0.0618553496914374</v>
+        <v>0.0618553496914395</v>
       </c>
     </row>
     <row r="128">
@@ -29556,7 +29361,7 @@
         <v>0.0745368535844939</v>
       </c>
       <c r="E128" t="n">
-        <v>0.0610163529382863</v>
+        <v>0.0610163529382887</v>
       </c>
     </row>
     <row r="129">
@@ -29573,7 +29378,7 @@
         <v>0.074678027945408</v>
       </c>
       <c r="E129" t="n">
-        <v>0.0601887362121711</v>
+        <v>0.0601887362121737</v>
       </c>
     </row>
     <row r="130">
@@ -29590,7 +29395,7 @@
         <v>0.0748192023063221</v>
       </c>
       <c r="E130" t="n">
-        <v>0.0593723451560994</v>
+        <v>0.0593723451561022</v>
       </c>
     </row>
     <row r="131">
@@ -29607,7 +29412,7 @@
         <v>0.0749603766672362</v>
       </c>
       <c r="E131" t="n">
-        <v>0.0585670275067542</v>
+        <v>0.0585670275067573</v>
       </c>
     </row>
     <row r="132">
@@ -29624,7 +29429,7 @@
         <v>0.0747204129519306</v>
       </c>
       <c r="E132" t="n">
-        <v>0.0577726330660955</v>
+        <v>0.0577726330660989</v>
       </c>
     </row>
     <row r="133">
@@ -29641,7 +29446,7 @@
         <v>0.0744804492366251</v>
       </c>
       <c r="E133" t="n">
-        <v>0.0569890136733471</v>
+        <v>0.0569890136733508</v>
       </c>
     </row>
     <row r="134">
@@ -29658,7 +29463,7 @@
         <v>0.0742404855213196</v>
       </c>
       <c r="E134" t="n">
-        <v>0.0562160231773636</v>
+        <v>0.0562160231773674</v>
       </c>
     </row>
     <row r="135">
@@ -29675,7 +29480,7 @@
         <v>0.0732173188197152</v>
       </c>
       <c r="E135" t="n">
-        <v>0.0554535174093718</v>
+        <v>0.0554535174093758</v>
       </c>
     </row>
     <row r="136">
@@ -29692,7 +29497,7 @@
         <v>0.0721941521181107</v>
       </c>
       <c r="E136" t="n">
-        <v>0.0547013541560823</v>
+        <v>0.0547013541560866</v>
       </c>
     </row>
     <row r="137">
@@ -29709,7 +29514,7 @@
         <v>0.0711709854165062</v>
       </c>
       <c r="E137" t="n">
-        <v>0.0539593931331658</v>
+        <v>0.0539593931331703</v>
       </c>
     </row>
     <row r="138">
@@ -29726,7 +29531,7 @@
         <v>0.0690729130644046</v>
       </c>
       <c r="E138" t="n">
-        <v>0.0532274959590884</v>
+        <v>0.0532274959590931</v>
       </c>
     </row>
     <row r="139">
@@ -29743,7 +29548,7 @@
         <v>0.0669748407123029</v>
       </c>
       <c r="E139" t="n">
-        <v>0.0525055261293032</v>
+        <v>0.052505526129308</v>
       </c>
     </row>
     <row r="140">
@@ -29760,7 +29565,7 @@
         <v>0.0648767683602012</v>
       </c>
       <c r="E140" t="n">
-        <v>0.0517933489907901</v>
+        <v>0.0517933489907952</v>
       </c>
     </row>
     <row r="141">
@@ -29777,7 +29582,7 @@
         <v>0.0621932007607709</v>
       </c>
       <c r="E141" t="n">
-        <v>0.0510908317169429</v>
+        <v>0.0510908317169481</v>
       </c>
     </row>
     <row r="142">
@@ -29794,7 +29599,7 @@
         <v>0.0595096331613406</v>
       </c>
       <c r="E142" t="n">
-        <v>0.0503978432827956</v>
+        <v>0.050397843282801</v>
       </c>
     </row>
     <row r="143">
@@ -29811,7 +29616,7 @@
         <v>0.0568260655619103</v>
       </c>
       <c r="E143" t="n">
-        <v>0.0497142544405853</v>
+        <v>0.0497142544405909</v>
       </c>
     </row>
     <row r="144">
@@ -29828,7 +29633,7 @@
         <v>0.0541419079988634</v>
       </c>
       <c r="E144" t="n">
-        <v>0.0490399376956466</v>
+        <v>0.0490399376956523</v>
       </c>
     </row>
     <row r="145">
@@ -29845,7 +29650,7 @@
         <v>0.0514577504358166</v>
       </c>
       <c r="E145" t="n">
-        <v>0.0483747672826326</v>
+        <v>0.0483747672826385</v>
       </c>
     </row>
     <row r="146">
@@ -29862,7 +29667,7 @@
         <v>0.0487735928727697</v>
       </c>
       <c r="E146" t="n">
-        <v>0.047718619142059</v>
+        <v>0.0477186191420651</v>
       </c>
     </row>
     <row r="147">
@@ -29879,7 +29684,7 @@
         <v>0.0464856258293992</v>
       </c>
       <c r="E147" t="n">
-        <v>0.0470713708971658</v>
+        <v>0.047071370897172</v>
       </c>
     </row>
     <row r="148">
@@ -29896,7 +29701,7 @@
         <v>0.0441976587860287</v>
       </c>
       <c r="E148" t="n">
-        <v>0.0464329018310931</v>
+        <v>0.0464329018310995</v>
       </c>
     </row>
     <row r="149">
@@ -29913,7 +29718,7 @@
         <v>0.0419096917426581</v>
       </c>
       <c r="E149" t="n">
-        <v>0.0458030928643666</v>
+        <v>0.0458030928643731</v>
       </c>
     </row>
     <row r="150">
@@ -29930,7 +29735,7 @@
         <v>0.0402963708585038</v>
       </c>
       <c r="E150" t="n">
-        <v>0.0451818265326883</v>
+        <v>0.0451818265326949</v>
       </c>
     </row>
     <row r="151">
@@ -29947,7 +29752,7 @@
         <v>0.0386830499743494</v>
       </c>
       <c r="E151" t="n">
-        <v>0.0445689869650282</v>
+        <v>0.044568986965035</v>
       </c>
     </row>
     <row r="152">
@@ -29964,7 +29769,7 @@
         <v>0.037069729090195</v>
       </c>
       <c r="E152" t="n">
-        <v>0.0439644598620141</v>
+        <v>0.043964459862021</v>
       </c>
     </row>
     <row r="153">
@@ -29981,7 +29786,7 @@
         <v>0.0365102183279321</v>
       </c>
       <c r="E153" t="n">
-        <v>0.0433681324746131</v>
+        <v>0.0433681324746201</v>
       </c>
     </row>
     <row r="154">
@@ -29998,7 +29803,7 @@
         <v>0.0359507075656692</v>
       </c>
       <c r="E154" t="n">
-        <v>0.0427798935831036</v>
+        <v>0.0427798935831107</v>
       </c>
     </row>
     <row r="155">
@@ -30015,7 +29820,7 @@
         <v>0.0353911968034063</v>
       </c>
       <c r="E155" t="n">
-        <v>0.0421996334763316</v>
+        <v>0.0421996334763388</v>
       </c>
     </row>
     <row r="156">
@@ -30032,7 +29837,7 @@
         <v>0.0352242210679906</v>
       </c>
       <c r="E156" t="n">
-        <v>0.041627243931249</v>
+        <v>0.0416272439312563</v>
       </c>
     </row>
     <row r="157">
@@ -30049,7 +29854,7 @@
         <v>0.035057245332575</v>
       </c>
       <c r="E157" t="n">
-        <v>0.0410626181927289</v>
+        <v>0.0410626181927364</v>
       </c>
     </row>
     <row r="158">
@@ -30066,7 +29871,7 @@
         <v>0.0348902695971593</v>
       </c>
       <c r="E158" t="n">
-        <v>0.0405056509536552</v>
+        <v>0.0405056509536627</v>
       </c>
     </row>
     <row r="159">
@@ -30083,7 +29888,7 @@
         <v>0.0352373236055518</v>
       </c>
       <c r="E159" t="n">
-        <v>0.0399562383352816</v>
+        <v>0.0399562383352892</v>
       </c>
     </row>
     <row r="160">
@@ -30100,7 +29905,7 @@
         <v>0.0355843776139443</v>
       </c>
       <c r="E160" t="n">
-        <v>0.0394142778678578</v>
+        <v>0.0394142778678656</v>
       </c>
     </row>
     <row r="161">
@@ -30117,7 +29922,7 @@
         <v>0.0359314316223368</v>
       </c>
       <c r="E161" t="n">
-        <v>0.038879668471518</v>
+        <v>0.0388796684715258</v>
       </c>
     </row>
     <row r="162">
@@ -30134,7 +29939,7 @@
         <v>0.036670597495294</v>
       </c>
       <c r="E162" t="n">
-        <v>0.0383523104374285</v>
+        <v>0.0383523104374364</v>
       </c>
     </row>
     <row r="163">
@@ -30151,7 +29956,7 @@
         <v>0.0374097633682512</v>
       </c>
       <c r="E163" t="n">
-        <v>0.0378321054091915</v>
+        <v>0.0378321054091995</v>
       </c>
     </row>
     <row r="164">
@@ -30168,7 +29973,7 @@
         <v>0.0381489292412084</v>
       </c>
       <c r="E164" t="n">
-        <v>0.0390440101888165</v>
+        <v>0.0390440101888203</v>
       </c>
     </row>
     <row r="165">
@@ -30185,7 +29990,7 @@
         <v>0.0393599130645852</v>
       </c>
       <c r="E165" t="n">
-        <v>0.0403199459001794</v>
+        <v>0.0403199459001833</v>
       </c>
     </row>
     <row r="166">
@@ -30202,7 +30007,7 @@
         <v>0.040570896887962</v>
       </c>
       <c r="E166" t="n">
-        <v>0.041637578453943</v>
+        <v>0.0416375784539469</v>
       </c>
     </row>
     <row r="167">
@@ -30219,7 +30024,7 @@
         <v>0.0417818807113388</v>
       </c>
       <c r="E167" t="n">
-        <v>0.0429982704788436</v>
+        <v>0.0429982704788475</v>
       </c>
     </row>
     <row r="168">
@@ -30236,7 +30041,7 @@
         <v>0.0438895624274346</v>
       </c>
       <c r="E168" t="n">
-        <v>0.0444034291335383</v>
+        <v>0.0444034291335422</v>
       </c>
     </row>
     <row r="169">
@@ -30253,7 +30058,7 @@
         <v>0.0459972441435304</v>
       </c>
       <c r="E169" t="n">
-        <v>0.0458545075618162</v>
+        <v>0.0458545075618201</v>
       </c>
     </row>
     <row r="170">
@@ -30270,7 +30075,7 @@
         <v>0.0481049258596261</v>
       </c>
       <c r="E170" t="n">
-        <v>0.0473530063953669</v>
+        <v>0.0473530063953708</v>
       </c>
     </row>
     <row r="171">
@@ -30287,7 +30092,7 @@
         <v>0.0509578531798852</v>
       </c>
       <c r="E171" t="n">
-        <v>0.0489004753056571</v>
+        <v>0.048900475305661</v>
       </c>
     </row>
     <row r="172">
@@ -30304,7 +30109,7 @@
         <v>0.0538107805001442</v>
       </c>
       <c r="E172" t="n">
-        <v>0.0504985146065223</v>
+        <v>0.0504985146065261</v>
       </c>
     </row>
     <row r="173">
@@ -30321,7 +30126,7 @@
         <v>0.0566637078204032</v>
       </c>
       <c r="E173" t="n">
-        <v>0.0521487769091302</v>
+        <v>0.0521487769091342</v>
       </c>
     </row>
     <row r="174">
@@ -30338,7 +30143,7 @@
         <v>0.0589635465265577</v>
       </c>
       <c r="E174" t="n">
-        <v>0.0538529688310276</v>
+        <v>0.0538529688310315</v>
       </c>
     </row>
     <row r="175">
@@ -30355,7 +30160,7 @@
         <v>0.0612633852327123</v>
       </c>
       <c r="E175" t="n">
-        <v>0.0556128527610371</v>
+        <v>0.0556128527610409</v>
       </c>
     </row>
     <row r="176">
@@ -30372,7 +30177,7 @@
         <v>0.0635632239388668</v>
       </c>
       <c r="E176" t="n">
-        <v>0.0574302486818306</v>
+        <v>0.0574302486818344</v>
       </c>
     </row>
     <row r="177">
@@ -30389,7 +30194,7 @@
         <v>0.0651696274321297</v>
       </c>
       <c r="E177" t="n">
-        <v>0.0593070360520632</v>
+        <v>0.059307036052067</v>
       </c>
     </row>
     <row r="178">
@@ -30406,7 +30211,7 @@
         <v>0.0667760309253926</v>
       </c>
       <c r="E178" t="n">
-        <v>0.0612451557500135</v>
+        <v>0.0612451557500173</v>
       </c>
     </row>
     <row r="179">
@@ -30423,7 +30228,7 @@
         <v>0.0683824344186555</v>
       </c>
       <c r="E179" t="n">
-        <v>0.0632466120807418</v>
+        <v>0.0632466120807455</v>
       </c>
     </row>
     <row r="180">
@@ -30440,7 +30245,7 @@
         <v>0.0708046928987432</v>
       </c>
       <c r="E180" t="n">
-        <v>0.0653134748488407</v>
+        <v>0.0653134748488443</v>
       </c>
     </row>
     <row r="181">
@@ -30457,7 +30262,7 @@
         <v>0.0732269513788308</v>
       </c>
       <c r="E181" t="n">
-        <v>0.0674478814989217</v>
+        <v>0.0674478814989253</v>
       </c>
     </row>
     <row r="182">
@@ -30474,7 +30279,7 @@
         <v>0.0756492098589185</v>
       </c>
       <c r="E182" t="n">
-        <v>0.0696520393260524</v>
+        <v>0.0696520393260559</v>
       </c>
     </row>
     <row r="183">
@@ -30491,7 +30296,7 @@
         <v>0.0789633714666181</v>
       </c>
       <c r="E183" t="n">
-        <v>0.0719282277584287</v>
+        <v>0.0719282277584322</v>
       </c>
     </row>
     <row r="184">
@@ -30508,7 +30313,7 @@
         <v>0.0822775330743177</v>
       </c>
       <c r="E184" t="n">
-        <v>0.074278800714644</v>
+        <v>0.0742788007146474</v>
       </c>
     </row>
     <row r="185">
@@ -30525,7 +30330,7 @@
         <v>0.0855916946820174</v>
       </c>
       <c r="E185" t="n">
-        <v>0.0767061890379923</v>
+        <v>0.0767061890379956</v>
       </c>
     </row>
     <row r="186">
@@ -30542,7 +30347,7 @@
         <v>0.0896021243828024</v>
       </c>
       <c r="E186" t="n">
-        <v>0.079212903010323</v>
+        <v>0.0792129030103263</v>
       </c>
     </row>
     <row r="187">
@@ -30559,7 +30364,7 @@
         <v>0.0936125540835875</v>
       </c>
       <c r="E187" t="n">
-        <v>0.0818015349480473</v>
+        <v>0.0818015349480504</v>
       </c>
     </row>
     <row r="188">
@@ -30576,7 +30381,7 @@
         <v>0.0976229837843726</v>
       </c>
       <c r="E188" t="n">
-        <v>0.0844747618829797</v>
+        <v>0.0844747618829826</v>
       </c>
     </row>
     <row r="189">
@@ -30593,7 +30398,7 @@
         <v>0.102805504868052</v>
       </c>
       <c r="E189" t="n">
-        <v>0.087235348330789</v>
+        <v>0.0872353483307919</v>
       </c>
     </row>
     <row r="190">
@@ -30610,7 +30415,7 @@
         <v>0.107988025951732</v>
       </c>
       <c r="E190" t="n">
-        <v>0.09008614914992</v>
+        <v>0.0900861491499228</v>
       </c>
     </row>
     <row r="191">
@@ -30627,7 +30432,7 @@
         <v>0.113170547035412</v>
       </c>
       <c r="E191" t="n">
-        <v>0.0930301124939434</v>
+        <v>0.093030112493946</v>
       </c>
     </row>
     <row r="192">
@@ -30644,7 +30449,7 @@
         <v>0.118621371633391</v>
       </c>
       <c r="E192" t="n">
-        <v>0.0960702828603864</v>
+        <v>0.0960702828603888</v>
       </c>
     </row>
     <row r="193">
@@ -30661,7 +30466,7 @@
         <v>0.12407219623137</v>
       </c>
       <c r="E193" t="n">
-        <v>0.0992098042391975</v>
+        <v>0.0992098042391996</v>
       </c>
     </row>
     <row r="194">
@@ -30678,7 +30483,7 @@
         <v>0.129523020829349</v>
       </c>
       <c r="E194" t="n">
-        <v>0.102451923364102</v>
+        <v>0.102451923364104</v>
       </c>
     </row>
     <row r="195">
@@ -30695,7 +30500,7 @@
         <v>0.133255050719583</v>
       </c>
       <c r="E195" t="n">
-        <v>0.105799993070208</v>
+        <v>0.10579999307021</v>
       </c>
     </row>
     <row r="196">
@@ -30712,7 +30517,7 @@
         <v>0.136987080609816</v>
       </c>
       <c r="E196" t="n">
-        <v>0.10925747576134</v>
+        <v>0.109257475761342</v>
       </c>
     </row>
     <row r="197">
@@ -30729,7 +30534,7 @@
         <v>0.140719110500049</v>
       </c>
       <c r="E197" t="n">
-        <v>0.112827946990681</v>
+        <v>0.112827946990683</v>
       </c>
     </row>
     <row r="198">
@@ -30746,7 +30551,7 @@
         <v>0.143167855695475</v>
       </c>
       <c r="E198" t="n">
-        <v>0.116515099158427</v>
+        <v>0.116515099158428</v>
       </c>
     </row>
     <row r="199">
@@ -30763,7 +30568,7 @@
         <v>0.1456166008909</v>
       </c>
       <c r="E199" t="n">
-        <v>0.12032274533028</v>
+        <v>0.120322745330281</v>
       </c>
     </row>
     <row r="200">
@@ -30780,7 +30585,7 @@
         <v>0.148065346086325</v>
       </c>
       <c r="E200" t="n">
-        <v>0.124254823180728</v>
+        <v>0.124254823180729</v>
       </c>
     </row>
     <row r="201">
@@ -30831,7 +30636,7 @@
         <v>0.153701844328095</v>
       </c>
       <c r="E203" t="n">
-        <v>0.136838979131201</v>
+        <v>0.1368389791312</v>
       </c>
     </row>
     <row r="204">
@@ -30848,7 +30653,7 @@
         <v>0.15497808346027</v>
       </c>
       <c r="E204" t="n">
-        <v>0.141310797966807</v>
+        <v>0.141310797966806</v>
       </c>
     </row>
     <row r="205">
@@ -30865,7 +30670,7 @@
         <v>0.156254322592445</v>
       </c>
       <c r="E205" t="n">
-        <v>0.145928753260208</v>
+        <v>0.145928753260206</v>
       </c>
     </row>
     <row r="206">
@@ -30882,7 +30687,7 @@
         <v>0.157530561724619</v>
       </c>
       <c r="E206" t="n">
-        <v>0.150697620666474</v>
+        <v>0.150697620666472</v>
       </c>
     </row>
     <row r="207">
@@ -30899,7 +30704,7 @@
         <v>0.159122431072103</v>
       </c>
       <c r="E207" t="n">
-        <v>0.155622331906327</v>
+        <v>0.155622331906324</v>
       </c>
     </row>
     <row r="208">
@@ -30916,7 +30721,7 @@
         <v>0.160714300419586</v>
       </c>
       <c r="E208" t="n">
-        <v>0.160707979866272</v>
+        <v>0.16070797986627</v>
       </c>
     </row>
     <row r="209">
@@ -30933,7 +30738,7 @@
         <v>0.16230616976707</v>
       </c>
       <c r="E209" t="n">
-        <v>0.165959823865409</v>
+        <v>0.165959823865406</v>
       </c>
     </row>
     <row r="210">
@@ -30950,7 +30755,7 @@
         <v>0.164015892771449</v>
       </c>
       <c r="E210" t="n">
-        <v>0.171383295094347</v>
+        <v>0.171383295094342</v>
       </c>
     </row>
     <row r="211">
@@ -30967,7 +30772,7 @@
         <v>0.165725615775828</v>
       </c>
       <c r="E211" t="n">
-        <v>0.176984002231867</v>
+        <v>0.176984002231863</v>
       </c>
     </row>
     <row r="212">
@@ -30984,7 +30789,7 @@
         <v>0.167435338780208</v>
       </c>
       <c r="E212" t="n">
-        <v>0.182767737245138</v>
+        <v>0.182767737245133</v>
       </c>
     </row>
     <row r="213">
@@ -31001,7 +30806,7 @@
         <v>0.169240227554945</v>
       </c>
       <c r="E213" t="n">
-        <v>0.188740481379471</v>
+        <v>0.188740481379465</v>
       </c>
     </row>
     <row r="214">
@@ -31018,7 +30823,7 @@
         <v>0.171045116329683</v>
       </c>
       <c r="E214" t="n">
-        <v>0.194908411343819</v>
+        <v>0.194908411343812</v>
       </c>
     </row>
     <row r="215">
@@ -31035,7 +30840,7 @@
         <v>0.172850005104421</v>
       </c>
       <c r="E215" t="n">
-        <v>0.201277905698418</v>
+        <v>0.201277905698411</v>
       </c>
     </row>
     <row r="216">
@@ -31052,7 +30857,7 @@
         <v>0.174789554015267</v>
       </c>
       <c r="E216" t="n">
-        <v>0.207855551451173</v>
+        <v>0.207855551451164</v>
       </c>
     </row>
     <row r="217">
@@ -31069,7 +30874,7 @@
         <v>0.176729102926113</v>
       </c>
       <c r="E217" t="n">
-        <v>0.214648150869599</v>
+        <v>0.21464815086959</v>
       </c>
     </row>
   </sheetData>

--- a/Outcome/Publish/figure_data/fig1.xlsx
+++ b/Outcome/Publish/figure_data/fig1.xlsx
@@ -351,7 +351,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -388,7 +390,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -23519,7 +23521,7 @@
         <v>52.9606534949093</v>
       </c>
       <c r="E2" t="n">
-        <v>52.6223862760916</v>
+        <v>52.6223862768737</v>
       </c>
     </row>
     <row r="3">
@@ -23536,7 +23538,7 @@
         <v>53.5877563650519</v>
       </c>
       <c r="E3" t="n">
-        <v>52.8273477091924</v>
+        <v>52.8273477099703</v>
       </c>
     </row>
     <row r="4">
@@ -23553,7 +23555,7 @@
         <v>54.2148592351945</v>
       </c>
       <c r="E4" t="n">
-        <v>53.0331074563333</v>
+        <v>53.0331074570955</v>
       </c>
     </row>
     <row r="5">
@@ -23570,7 +23572,7 @@
         <v>54.8419621053371</v>
       </c>
       <c r="E5" t="n">
-        <v>53.23966862689</v>
+        <v>53.2396686276389</v>
       </c>
     </row>
     <row r="6">
@@ -23587,7 +23589,7 @@
         <v>55.6730358124072</v>
       </c>
       <c r="E6" t="n">
-        <v>53.4470343423668</v>
+        <v>53.4470343431015</v>
       </c>
     </row>
     <row r="7">
@@ -23604,7 +23606,7 @@
         <v>56.5041095194772</v>
       </c>
       <c r="E7" t="n">
-        <v>53.6552077364237</v>
+        <v>53.6552077371439</v>
       </c>
     </row>
     <row r="8">
@@ -23621,7 +23623,7 @@
         <v>57.3351832265472</v>
       </c>
       <c r="E8" t="n">
-        <v>53.8641919549262</v>
+        <v>53.8641919556319</v>
       </c>
     </row>
     <row r="9">
@@ -23638,7 +23640,7 @@
         <v>58.2459823903846</v>
       </c>
       <c r="E9" t="n">
-        <v>54.073990155993</v>
+        <v>54.0739901566841</v>
       </c>
     </row>
     <row r="10">
@@ -23655,7 +23657,7 @@
         <v>59.1567815542219</v>
       </c>
       <c r="E10" t="n">
-        <v>54.2846055100436</v>
+        <v>54.2846055107198</v>
       </c>
     </row>
     <row r="11">
@@ -23672,7 +23674,7 @@
         <v>60.0675807180593</v>
       </c>
       <c r="E11" t="n">
-        <v>54.4960411998458</v>
+        <v>54.4960412005072</v>
       </c>
     </row>
     <row r="12">
@@ -23689,7 +23691,7 @@
         <v>60.8264404975824</v>
       </c>
       <c r="E12" t="n">
-        <v>54.7083004205644</v>
+        <v>54.7083004212108</v>
       </c>
     </row>
     <row r="13">
@@ -23706,7 +23708,7 @@
         <v>61.5853002771055</v>
       </c>
       <c r="E13" t="n">
-        <v>54.9213863798092</v>
+        <v>54.9213863804404</v>
       </c>
     </row>
     <row r="14">
@@ -23723,7 +23725,7 @@
         <v>62.3441600566286</v>
       </c>
       <c r="E14" t="n">
-        <v>55.1353022976832</v>
+        <v>55.1353022982991</v>
       </c>
     </row>
     <row r="15">
@@ -23740,7 +23742,7 @@
         <v>63.3248826212604</v>
       </c>
       <c r="E15" t="n">
-        <v>55.3500514068318</v>
+        <v>55.3500514074324</v>
       </c>
     </row>
     <row r="16">
@@ -23757,7 +23759,7 @@
         <v>64.3056051858921</v>
       </c>
       <c r="E16" t="n">
-        <v>55.5656369524913</v>
+        <v>55.5656369530763</v>
       </c>
     </row>
     <row r="17">
@@ -23774,7 +23776,7 @@
         <v>65.2863277505239</v>
       </c>
       <c r="E17" t="n">
-        <v>55.7820621925379</v>
+        <v>55.7820621931073</v>
       </c>
     </row>
     <row r="18">
@@ -23791,7 +23793,7 @@
         <v>66.0987253027954</v>
       </c>
       <c r="E18" t="n">
-        <v>55.9993303975374</v>
+        <v>55.999330398091</v>
       </c>
     </row>
     <row r="19">
@@ -23808,7 +23810,7 @@
         <v>66.9111228550668</v>
       </c>
       <c r="E19" t="n">
-        <v>56.2174448507939</v>
+        <v>56.2174448513315</v>
       </c>
     </row>
     <row r="20">
@@ -23825,7 +23827,7 @@
         <v>67.7235204073383</v>
       </c>
       <c r="E20" t="n">
-        <v>56.4364088483999</v>
+        <v>56.4364088489215</v>
       </c>
     </row>
     <row r="21">
@@ -23842,7 +23844,7 @@
         <v>67.8250945738005</v>
       </c>
       <c r="E21" t="n">
-        <v>56.6562256992862</v>
+        <v>56.6562256997916</v>
       </c>
     </row>
     <row r="22">
@@ -23859,7 +23861,7 @@
         <v>67.9266687402626</v>
       </c>
       <c r="E22" t="n">
-        <v>56.8768987252715</v>
+        <v>56.8768987257606</v>
       </c>
     </row>
     <row r="23">
@@ -23876,7 +23878,7 @@
         <v>68.0282429067248</v>
       </c>
       <c r="E23" t="n">
-        <v>57.0984312611129</v>
+        <v>57.0984312615856</v>
       </c>
     </row>
     <row r="24">
@@ -23893,7 +23895,7 @@
         <v>67.6657739498362</v>
       </c>
       <c r="E24" t="n">
-        <v>57.3208266545562</v>
+        <v>57.3208266550123</v>
       </c>
     </row>
     <row r="25">
@@ -23910,7 +23912,7 @@
         <v>67.3033049929475</v>
       </c>
       <c r="E25" t="n">
-        <v>57.5440882663864</v>
+        <v>57.5440882668258</v>
       </c>
     </row>
     <row r="26">
@@ -23927,7 +23929,7 @@
         <v>66.9408360360589</v>
       </c>
       <c r="E26" t="n">
-        <v>57.7682194704788</v>
+        <v>57.7682194709013</v>
       </c>
     </row>
     <row r="27">
@@ -23944,7 +23946,7 @@
         <v>66.5489759319587</v>
       </c>
       <c r="E27" t="n">
-        <v>57.9932236538495</v>
+        <v>57.993223654255</v>
       </c>
     </row>
     <row r="28">
@@ -23961,7 +23963,7 @@
         <v>66.1571158278584</v>
       </c>
       <c r="E28" t="n">
-        <v>58.219104216707</v>
+        <v>58.2191042170953</v>
       </c>
     </row>
     <row r="29">
@@ -23978,7 +23980,7 @@
         <v>65.7652557237581</v>
       </c>
       <c r="E29" t="n">
-        <v>58.4458645725035</v>
+        <v>58.4458645728745</v>
       </c>
     </row>
     <row r="30">
@@ -23995,7 +23997,7 @@
         <v>65.5467072693592</v>
       </c>
       <c r="E30" t="n">
-        <v>58.6735081479862</v>
+        <v>58.6735081483398</v>
       </c>
     </row>
     <row r="31">
@@ -24012,7 +24014,7 @@
         <v>65.3281588149602</v>
       </c>
       <c r="E31" t="n">
-        <v>58.9020383832495</v>
+        <v>58.9020383835855</v>
       </c>
     </row>
     <row r="32">
@@ -24029,7 +24031,7 @@
         <v>65.1096103605612</v>
       </c>
       <c r="E32" t="n">
-        <v>59.1314587317867</v>
+        <v>59.131458732105</v>
       </c>
     </row>
     <row r="33">
@@ -24046,7 +24048,7 @@
         <v>65.0688640358459</v>
       </c>
       <c r="E33" t="n">
-        <v>59.3617726605423</v>
+        <v>59.3617726608428</v>
       </c>
     </row>
     <row r="34">
@@ -24063,7 +24065,7 @@
         <v>65.0281177111307</v>
       </c>
       <c r="E34" t="n">
-        <v>59.5929836499644</v>
+        <v>59.5929836502469</v>
       </c>
     </row>
     <row r="35">
@@ -24080,7 +24082,7 @@
         <v>64.9873713864154</v>
       </c>
       <c r="E35" t="n">
-        <v>59.8250951940572</v>
+        <v>59.8250951943215</v>
       </c>
     </row>
     <row r="36">
@@ -24097,7 +24099,7 @@
         <v>64.6606400569347</v>
       </c>
       <c r="E36" t="n">
-        <v>60.0581108004339</v>
+        <v>60.0581108006799</v>
       </c>
     </row>
     <row r="37">
@@ -24114,7 +24116,7 @@
         <v>64.333908727454</v>
       </c>
       <c r="E37" t="n">
-        <v>60.2920339903695</v>
+        <v>60.2920339905971</v>
       </c>
     </row>
     <row r="38">
@@ -24131,7 +24133,7 @@
         <v>64.0071773979734</v>
       </c>
       <c r="E38" t="n">
-        <v>60.5268682988545</v>
+        <v>60.5268682990636</v>
       </c>
     </row>
     <row r="39">
@@ -24148,7 +24150,7 @@
         <v>63.2769946618867</v>
       </c>
       <c r="E39" t="n">
-        <v>60.7626172746479</v>
+        <v>60.7626172748382</v>
       </c>
     </row>
     <row r="40">
@@ -24165,7 +24167,7 @@
         <v>62.5468119258001</v>
       </c>
       <c r="E40" t="n">
-        <v>60.9992844803307</v>
+        <v>60.9992844805021</v>
       </c>
     </row>
     <row r="41">
@@ -24182,7 +24184,7 @@
         <v>61.8166291897135</v>
       </c>
       <c r="E41" t="n">
-        <v>61.2368734923601</v>
+        <v>61.2368734925125</v>
       </c>
     </row>
     <row r="42">
@@ -24199,7 +24201,7 @@
         <v>61.202957160841</v>
       </c>
       <c r="E42" t="n">
-        <v>61.4753879011237</v>
+        <v>61.4753879012569</v>
       </c>
     </row>
     <row r="43">
@@ -24216,7 +24218,7 @@
         <v>60.5892851319684</v>
       </c>
       <c r="E43" t="n">
-        <v>61.7148313109929</v>
+        <v>61.7148313111068</v>
       </c>
     </row>
     <row r="44">
@@ -24233,7 +24235,7 @@
         <v>59.9756131030959</v>
       </c>
       <c r="E44" t="n">
-        <v>61.9552073403785</v>
+        <v>61.955207340473</v>
       </c>
     </row>
     <row r="45">
@@ -24250,7 +24252,7 @@
         <v>59.8817031106424</v>
       </c>
       <c r="E45" t="n">
-        <v>62.1965196217845</v>
+        <v>62.1965196218593</v>
       </c>
     </row>
     <row r="46">
@@ -24267,7 +24269,7 @@
         <v>59.787793118189</v>
       </c>
       <c r="E46" t="n">
-        <v>62.4387718018634</v>
+        <v>62.4387718019184</v>
       </c>
     </row>
     <row r="47">
@@ -24284,7 +24286,7 @@
         <v>59.6938831257355</v>
       </c>
       <c r="E47" t="n">
-        <v>62.6819675414712</v>
+        <v>62.6819675415062</v>
       </c>
     </row>
     <row r="48">
@@ -24301,7 +24303,7 @@
         <v>59.6624158587651</v>
       </c>
       <c r="E48" t="n">
-        <v>62.9261105157227</v>
+        <v>62.9261105157376</v>
       </c>
     </row>
     <row r="49">
@@ -24318,7 +24320,7 @@
         <v>59.6309485917948</v>
       </c>
       <c r="E49" t="n">
-        <v>63.1712044140472</v>
+        <v>63.1712044140419</v>
       </c>
     </row>
     <row r="50">
@@ -24335,7 +24337,7 @@
         <v>59.5994813248244</v>
       </c>
       <c r="E50" t="n">
-        <v>63.417252940244</v>
+        <v>63.4172529402183</v>
       </c>
     </row>
     <row r="51">
@@ -24352,7 +24354,7 @@
         <v>59.9598549853372</v>
       </c>
       <c r="E51" t="n">
-        <v>63.6642598125386</v>
+        <v>63.6642598124923</v>
       </c>
     </row>
     <row r="52">
@@ -24369,7 +24371,7 @@
         <v>60.32022864585</v>
       </c>
       <c r="E52" t="n">
-        <v>63.9122287636388</v>
+        <v>63.9122287635718</v>
       </c>
     </row>
     <row r="53">
@@ -24386,7 +24388,7 @@
         <v>60.6806023063629</v>
       </c>
       <c r="E53" t="n">
-        <v>64.161163540791</v>
+        <v>64.1611635407031</v>
       </c>
     </row>
     <row r="54">
@@ -24403,7 +24405,7 @@
         <v>61.4717559663315</v>
       </c>
       <c r="E54" t="n">
-        <v>64.411067905837</v>
+        <v>64.4110679057281</v>
       </c>
     </row>
     <row r="55">
@@ -24420,7 +24422,7 @@
         <v>62.2629096263002</v>
       </c>
       <c r="E55" t="n">
-        <v>64.6619456352709</v>
+        <v>64.6619456351407</v>
       </c>
     </row>
     <row r="56">
@@ -24437,7 +24439,7 @@
         <v>63.0540632862688</v>
       </c>
       <c r="E56" t="n">
-        <v>64.9138005202957</v>
+        <v>64.9138005201441</v>
       </c>
     </row>
     <row r="57">
@@ -24454,7 +24456,7 @@
         <v>64.0616439866885</v>
       </c>
       <c r="E57" t="n">
-        <v>65.1666363668812</v>
+        <v>65.166636366708</v>
       </c>
     </row>
     <row r="58">
@@ -24471,7 +24473,7 @@
         <v>65.0692246871081</v>
       </c>
       <c r="E58" t="n">
-        <v>65.4204569958213</v>
+        <v>65.4204569956264</v>
       </c>
     </row>
     <row r="59">
@@ -24488,7 +24490,7 @@
         <v>66.0768053875278</v>
       </c>
       <c r="E59" t="n">
-        <v>65.6752662427915</v>
+        <v>65.6752662425747</v>
       </c>
     </row>
     <row r="60">
@@ -24505,7 +24507,7 @@
         <v>66.6663312608161</v>
       </c>
       <c r="E60" t="n">
-        <v>65.9310679584072</v>
+        <v>65.9310679581684</v>
       </c>
     </row>
     <row r="61">
@@ -24522,7 +24524,7 @@
         <v>67.2558571341044</v>
       </c>
       <c r="E61" t="n">
-        <v>66.1878660082816</v>
+        <v>66.1878660080206</v>
       </c>
     </row>
     <row r="62">
@@ -24539,7 +24541,7 @@
         <v>67.8453830073927</v>
       </c>
       <c r="E62" t="n">
-        <v>66.4456642730845</v>
+        <v>66.4456642728012</v>
       </c>
     </row>
     <row r="63">
@@ -24556,7 +24558,7 @@
         <v>67.6991093243815</v>
       </c>
       <c r="E63" t="n">
-        <v>66.7044666486005</v>
+        <v>66.7044666482946</v>
       </c>
     </row>
     <row r="64">
@@ -24573,7 +24575,7 @@
         <v>67.5528356413703</v>
       </c>
       <c r="E64" t="n">
-        <v>66.9642770457881</v>
+        <v>66.9642770454595</v>
       </c>
     </row>
     <row r="65">
@@ -24590,7 +24592,7 @@
         <v>67.4065619583591</v>
       </c>
       <c r="E65" t="n">
-        <v>67.2250993908389</v>
+        <v>67.2250993904873</v>
       </c>
     </row>
     <row r="66">
@@ -24607,7 +24609,7 @@
         <v>67.3919276907092</v>
       </c>
       <c r="E66" t="n">
-        <v>67.4869376252366</v>
+        <v>67.486937624862</v>
       </c>
     </row>
     <row r="67">
@@ -24624,7 +24626,7 @@
         <v>67.3772934230592</v>
       </c>
       <c r="E67" t="n">
-        <v>67.7497957058169</v>
+        <v>67.7497957054191</v>
       </c>
     </row>
     <row r="68">
@@ -24641,7 +24643,7 @@
         <v>67.3626591554093</v>
       </c>
       <c r="E68" t="n">
-        <v>68.0136776048273</v>
+        <v>68.013677604406</v>
       </c>
     </row>
     <row r="69">
@@ -24658,7 +24660,7 @@
         <v>67.3156897800839</v>
       </c>
       <c r="E69" t="n">
-        <v>68.2785873099868</v>
+        <v>68.2785873095419</v>
       </c>
     </row>
     <row r="70">
@@ -24675,7 +24677,7 @@
         <v>67.2687204047586</v>
       </c>
       <c r="E70" t="n">
-        <v>68.5445288245464</v>
+        <v>68.5445288240777</v>
       </c>
     </row>
     <row r="71">
@@ -24692,7 +24694,7 @@
         <v>67.2217510294332</v>
       </c>
       <c r="E71" t="n">
-        <v>68.8115061673495</v>
+        <v>68.8115061668569</v>
       </c>
     </row>
     <row r="72">
@@ -24709,7 +24711,7 @@
         <v>66.4039518297106</v>
       </c>
       <c r="E72" t="n">
-        <v>69.0795233728928</v>
+        <v>69.0795233723761</v>
       </c>
     </row>
     <row r="73">
@@ -24726,7 +24728,7 @@
         <v>65.5861526299881</v>
       </c>
       <c r="E73" t="n">
-        <v>69.3485844913872</v>
+        <v>69.3485844908461</v>
       </c>
     </row>
     <row r="74">
@@ -24743,7 +24745,7 @@
         <v>64.7683534302655</v>
       </c>
       <c r="E74" t="n">
-        <v>69.6186935888187</v>
+        <v>69.6186935882532</v>
       </c>
     </row>
     <row r="75">
@@ -24760,7 +24762,7 @@
         <v>63.8760298052676</v>
       </c>
       <c r="E75" t="n">
-        <v>69.8898547470104</v>
+        <v>69.8898547464202</v>
       </c>
     </row>
     <row r="76">
@@ -24777,7 +24779,7 @@
         <v>62.9837061802696</v>
       </c>
       <c r="E76" t="n">
-        <v>70.1620720636837</v>
+        <v>70.1620720630686</v>
       </c>
     </row>
     <row r="77">
@@ -24794,7 +24796,7 @@
         <v>62.0913825552717</v>
       </c>
       <c r="E77" t="n">
-        <v>70.4353496525205</v>
+        <v>70.4353496518803</v>
       </c>
     </row>
     <row r="78">
@@ -24811,7 +24813,7 @@
         <v>61.9884601968422</v>
       </c>
       <c r="E78" t="n">
-        <v>70.7096916432251</v>
+        <v>70.7096916425597</v>
       </c>
     </row>
     <row r="79">
@@ -24828,7 +24830,7 @@
         <v>61.8855378384127</v>
       </c>
       <c r="E79" t="n">
-        <v>70.9851021815871</v>
+        <v>70.9851021808963</v>
       </c>
     </row>
     <row r="80">
@@ -24845,7 +24847,7 @@
         <v>61.7826154799832</v>
       </c>
       <c r="E80" t="n">
-        <v>71.2615854295434</v>
+        <v>71.261585428827</v>
       </c>
     </row>
     <row r="81">
@@ -24862,7 +24864,7 @@
         <v>61.5700741565645</v>
       </c>
       <c r="E81" t="n">
-        <v>71.5391455652418</v>
+        <v>71.5391455644995</v>
       </c>
     </row>
     <row r="82">
@@ -24879,7 +24881,7 @@
         <v>61.3575328331458</v>
       </c>
       <c r="E82" t="n">
-        <v>71.8177867831032</v>
+        <v>71.817786782335</v>
       </c>
     </row>
     <row r="83">
@@ -24896,7 +24898,7 @@
         <v>61.1449915097271</v>
       </c>
       <c r="E83" t="n">
-        <v>72.0975132938862</v>
+        <v>72.0975132930918</v>
       </c>
     </row>
     <row r="84">
@@ -24913,7 +24915,7 @@
         <v>61.0614374909758</v>
       </c>
       <c r="E84" t="n">
-        <v>72.3783293247497</v>
+        <v>72.3783293239289</v>
       </c>
     </row>
     <row r="85">
@@ -24930,7 +24932,7 @@
         <v>60.9778834722245</v>
       </c>
       <c r="E85" t="n">
-        <v>72.6602391193171</v>
+        <v>72.6602391184698</v>
       </c>
     </row>
     <row r="86">
@@ -24947,7 +24949,7 @@
         <v>60.8943294534732</v>
       </c>
       <c r="E86" t="n">
-        <v>72.9432469377408</v>
+        <v>72.9432469368667</v>
       </c>
     </row>
     <row r="87">
@@ -24964,7 +24966,7 @@
         <v>62.1128317551398</v>
       </c>
       <c r="E87" t="n">
-        <v>73.2273570567661</v>
+        <v>73.227357055865</v>
       </c>
     </row>
     <row r="88">
@@ -24981,7 +24983,7 @@
         <v>63.3313340568064</v>
       </c>
       <c r="E88" t="n">
-        <v>73.5125737697959</v>
+        <v>73.5125737688676</v>
       </c>
     </row>
     <row r="89">
@@ -24998,7 +25000,7 @@
         <v>64.549836358473</v>
       </c>
       <c r="E89" t="n">
-        <v>73.7989013869557</v>
+        <v>73.7989013860001</v>
       </c>
     </row>
     <row r="90">
@@ -25015,7 +25017,7 @@
         <v>66.148053805717</v>
       </c>
       <c r="E90" t="n">
-        <v>74.086344235159</v>
+        <v>74.0863442341759</v>
       </c>
     </row>
     <row r="91">
@@ -25032,7 +25034,7 @@
         <v>67.7462712529611</v>
       </c>
       <c r="E91" t="n">
-        <v>74.3749066581721</v>
+        <v>74.3749066571612</v>
       </c>
     </row>
     <row r="92">
@@ -25049,7 +25051,7 @@
         <v>69.3444887002051</v>
       </c>
       <c r="E92" t="n">
-        <v>74.6645930166801</v>
+        <v>74.6645930156412</v>
       </c>
     </row>
     <row r="93">
@@ -25066,7 +25068,7 @@
         <v>70.187837354764</v>
       </c>
       <c r="E93" t="n">
-        <v>74.9554076883528</v>
+        <v>74.9554076872858</v>
       </c>
     </row>
     <row r="94">
@@ -25083,7 +25085,7 @@
         <v>71.0311860093229</v>
       </c>
       <c r="E94" t="n">
-        <v>75.2473550679107</v>
+        <v>75.2473550668154</v>
       </c>
     </row>
     <row r="95">
@@ -25100,7 +25102,7 @@
         <v>71.8745346638819</v>
       </c>
       <c r="E95" t="n">
-        <v>75.5404395671917</v>
+        <v>75.5404395660678</v>
       </c>
     </row>
     <row r="96">
@@ -25117,7 +25119,7 @@
         <v>72.7681319153596</v>
       </c>
       <c r="E96" t="n">
-        <v>75.8346656152174</v>
+        <v>75.8346656140647</v>
       </c>
     </row>
     <row r="97">
@@ -25134,7 +25136,7 @@
         <v>73.6617291668373</v>
       </c>
       <c r="E97" t="n">
-        <v>76.1300376582602</v>
+        <v>76.1300376570785</v>
       </c>
     </row>
     <row r="98">
@@ -25151,7 +25153,7 @@
         <v>74.555326418315</v>
       </c>
       <c r="E98" t="n">
-        <v>76.4265601599106</v>
+        <v>76.4265601586998</v>
       </c>
     </row>
     <row r="99">
@@ -25168,7 +25170,7 @@
         <v>75.5648017152812</v>
       </c>
       <c r="E99" t="n">
-        <v>76.7242376011445</v>
+        <v>76.7242375999042</v>
       </c>
     </row>
     <row r="100">
@@ -25185,7 +25187,7 @@
         <v>76.5742770122474</v>
       </c>
       <c r="E100" t="n">
-        <v>77.023074480391</v>
+        <v>77.0230744791213</v>
       </c>
     </row>
     <row r="101">
@@ -25202,7 +25204,7 @@
         <v>77.5837523092135</v>
       </c>
       <c r="E101" t="n">
-        <v>77.3230753136003</v>
+        <v>77.3230753123007</v>
       </c>
     </row>
     <row r="102">
@@ -25219,7 +25221,7 @@
         <v>77.6689309856049</v>
       </c>
       <c r="E102" t="n">
-        <v>77.624244634312</v>
+        <v>77.6242446329823</v>
       </c>
     </row>
     <row r="103">
@@ -25236,7 +25238,7 @@
         <v>77.7541096619962</v>
       </c>
       <c r="E103" t="n">
-        <v>77.9265869937236</v>
+        <v>77.9265869923637</v>
       </c>
     </row>
     <row r="104">
@@ -25253,7 +25255,7 @@
         <v>77.8392883383875</v>
       </c>
       <c r="E104" t="n">
-        <v>78.2301069607592</v>
+        <v>78.2301069593689</v>
       </c>
     </row>
     <row r="105">
@@ -25270,7 +25272,7 @@
         <v>77.7312007640555</v>
       </c>
       <c r="E105" t="n">
-        <v>78.5348091221388</v>
+        <v>78.5348091207179</v>
       </c>
     </row>
     <row r="106">
@@ -25287,7 +25289,7 @@
         <v>77.6231131897234</v>
       </c>
       <c r="E106" t="n">
-        <v>78.8406980824474</v>
+        <v>78.8406980809955</v>
       </c>
     </row>
     <row r="107">
@@ -25304,7 +25306,7 @@
         <v>77.5150256153914</v>
       </c>
       <c r="E107" t="n">
-        <v>79.1477784642044</v>
+        <v>79.1477784627214</v>
       </c>
     </row>
     <row r="108">
@@ -25321,7 +25323,7 @@
         <v>78.4665220286386</v>
       </c>
       <c r="E108" t="n">
-        <v>79.4560549079338</v>
+        <v>79.4560549064195</v>
       </c>
     </row>
     <row r="109">
@@ -25338,7 +25340,7 @@
         <v>79.4180184418858</v>
       </c>
       <c r="E109" t="n">
-        <v>79.7655320722344</v>
+        <v>79.7655320706885</v>
       </c>
     </row>
     <row r="110">
@@ -25355,7 +25357,7 @@
         <v>80.369514855133</v>
       </c>
       <c r="E110" t="n">
-        <v>80.0762146338497</v>
+        <v>80.076214632272</v>
       </c>
     </row>
     <row r="111">
@@ -25372,7 +25374,7 @@
         <v>81.2258750766526</v>
       </c>
       <c r="E111" t="n">
-        <v>80.3881072877389</v>
+        <v>80.3881072861293</v>
       </c>
     </row>
     <row r="112">
@@ -25389,7 +25391,7 @@
         <v>82.0822352981723</v>
       </c>
       <c r="E112" t="n">
-        <v>80.7012147471481</v>
+        <v>80.7012147455062</v>
       </c>
     </row>
     <row r="113">
@@ -25406,7 +25408,7 @@
         <v>82.9385955196918</v>
       </c>
       <c r="E113" t="n">
-        <v>81.0155417436809</v>
+        <v>81.0155417420066</v>
       </c>
     </row>
     <row r="114">
@@ -25423,7 +25425,7 @@
         <v>83.0546227333876</v>
       </c>
       <c r="E114" t="n">
-        <v>81.3310930273705</v>
+        <v>81.3310930256635</v>
       </c>
     </row>
     <row r="115">
@@ -25440,7 +25442,7 @@
         <v>83.1706499470833</v>
       </c>
       <c r="E115" t="n">
-        <v>81.6478733667511</v>
+        <v>81.6478733650113</v>
       </c>
     </row>
     <row r="116">
@@ -25457,7 +25459,7 @@
         <v>83.286677160779</v>
       </c>
       <c r="E116" t="n">
-        <v>81.9658875489301</v>
+        <v>81.965887547157</v>
       </c>
     </row>
     <row r="117">
@@ -25474,7 +25476,7 @@
         <v>83.8833623068731</v>
       </c>
       <c r="E117" t="n">
-        <v>82.2851403796604</v>
+        <v>82.285140377854</v>
       </c>
     </row>
     <row r="118">
@@ -25491,7 +25493,7 @@
         <v>84.4800474529671</v>
       </c>
       <c r="E118" t="n">
-        <v>82.6056366834133</v>
+        <v>82.6056366815732</v>
       </c>
     </row>
     <row r="119">
@@ -25508,7 +25510,7 @@
         <v>85.0767325990612</v>
       </c>
       <c r="E119" t="n">
-        <v>82.9273813034507</v>
+        <v>82.9273813015768</v>
       </c>
     </row>
     <row r="120">
@@ -25525,7 +25527,7 @@
         <v>86.062689158349</v>
       </c>
       <c r="E120" t="n">
-        <v>83.2503791018991</v>
+        <v>83.2503790999912</v>
       </c>
     </row>
     <row r="121">
@@ -25542,7 +25544,7 @@
         <v>87.0486457176369</v>
       </c>
       <c r="E121" t="n">
-        <v>83.5746349598228</v>
+        <v>83.5746349578806</v>
       </c>
     </row>
     <row r="122">
@@ -25559,7 +25561,7 @@
         <v>88.0346022769247</v>
       </c>
       <c r="E122" t="n">
-        <v>83.9001537772973</v>
+        <v>83.9001537753205</v>
       </c>
     </row>
     <row r="123">
@@ -25576,7 +25578,7 @@
         <v>88.4337637039942</v>
       </c>
       <c r="E123" t="n">
-        <v>84.2269404734839</v>
+        <v>84.2269404714723</v>
       </c>
     </row>
     <row r="124">
@@ -25593,7 +25595,7 @@
         <v>88.8329251310637</v>
       </c>
       <c r="E124" t="n">
-        <v>84.5549999867035</v>
+        <v>84.5549999846568</v>
       </c>
     </row>
     <row r="125">
@@ -25610,7 +25612,7 @@
         <v>89.2320865581332</v>
       </c>
       <c r="E125" t="n">
-        <v>84.8843372745117</v>
+        <v>84.8843372724298</v>
       </c>
     </row>
     <row r="126">
@@ -25627,7 +25629,7 @@
         <v>90.3088216825565</v>
       </c>
       <c r="E126" t="n">
-        <v>85.2149573137735</v>
+        <v>85.2149573116561</v>
       </c>
     </row>
     <row r="127">
@@ -25644,7 +25646,7 @@
         <v>91.3855568069798</v>
       </c>
       <c r="E127" t="n">
-        <v>85.5468651007384</v>
+        <v>85.5468650985853</v>
       </c>
     </row>
     <row r="128">
@@ -25661,7 +25663,7 @@
         <v>92.462291931403</v>
       </c>
       <c r="E128" t="n">
-        <v>85.8800656511163</v>
+        <v>85.8800656489272</v>
       </c>
     </row>
     <row r="129">
@@ -25678,7 +25680,7 @@
         <v>94.2743143123654</v>
       </c>
       <c r="E129" t="n">
-        <v>86.2145640001528</v>
+        <v>86.2145639979274</v>
       </c>
     </row>
     <row r="130">
@@ -25695,7 +25697,7 @@
         <v>96.0863366933277</v>
       </c>
       <c r="E130" t="n">
-        <v>86.5503652027055</v>
+        <v>86.5503652004435</v>
       </c>
     </row>
     <row r="131">
@@ -25712,7 +25714,7 @@
         <v>97.8983590742901</v>
       </c>
       <c r="E131" t="n">
-        <v>86.8874743333205</v>
+        <v>86.8874743310218</v>
       </c>
     </row>
     <row r="132">
@@ -25729,7 +25731,7 @@
         <v>99.5659380796031</v>
       </c>
       <c r="E132" t="n">
-        <v>87.225896486309</v>
+        <v>87.2258964839733</v>
       </c>
     </row>
     <row r="133">
@@ -25746,7 +25748,7 @@
         <v>101.233517084916</v>
       </c>
       <c r="E133" t="n">
-        <v>87.5656367758242</v>
+        <v>87.5656367734512</v>
       </c>
     </row>
     <row r="134">
@@ -25763,7 +25765,7 @@
         <v>102.901096090229</v>
       </c>
       <c r="E134" t="n">
-        <v>87.9067003359387</v>
+        <v>87.9067003335282</v>
       </c>
     </row>
     <row r="135">
@@ -25780,7 +25782,7 @@
         <v>104.156618877232</v>
       </c>
       <c r="E135" t="n">
-        <v>88.2490923207221</v>
+        <v>88.2490923182739</v>
       </c>
     </row>
     <row r="136">
@@ -25797,7 +25799,7 @@
         <v>105.412141664236</v>
       </c>
       <c r="E136" t="n">
-        <v>88.5928179043188</v>
+        <v>88.5928179018325</v>
       </c>
     </row>
     <row r="137">
@@ -25814,7 +25816,7 @@
         <v>106.667664451239</v>
       </c>
       <c r="E137" t="n">
-        <v>88.937882281026</v>
+        <v>88.9378822785015</v>
       </c>
     </row>
     <row r="138">
@@ -25831,7 +25833,7 @@
         <v>106.31714758968</v>
       </c>
       <c r="E138" t="n">
-        <v>89.2842906653728</v>
+        <v>89.2842906628098</v>
       </c>
     </row>
     <row r="139">
@@ -25848,7 +25850,7 @@
         <v>105.966630728121</v>
       </c>
       <c r="E139" t="n">
-        <v>89.6320482921985</v>
+        <v>89.6320482895966</v>
       </c>
     </row>
     <row r="140">
@@ -25865,7 +25867,7 @@
         <v>105.616113866562</v>
       </c>
       <c r="E140" t="n">
-        <v>89.9811604167314</v>
+        <v>89.9811604140905</v>
       </c>
     </row>
     <row r="141">
@@ -25882,7 +25884,7 @@
         <v>102.441571529924</v>
       </c>
       <c r="E141" t="n">
-        <v>90.3316323146694</v>
+        <v>90.3316323119891</v>
       </c>
     </row>
     <row r="142">
@@ -25899,7 +25901,7 @@
         <v>99.2670291932854</v>
       </c>
       <c r="E142" t="n">
-        <v>90.6834692822584</v>
+        <v>90.6834692795384</v>
       </c>
     </row>
     <row r="143">
@@ -25916,7 +25918,7 @@
         <v>96.0924868566471</v>
       </c>
       <c r="E143" t="n">
-        <v>91.0366766363728</v>
+        <v>91.0366766336131</v>
       </c>
     </row>
     <row r="144">
@@ -25933,7 +25935,7 @@
         <v>91.4220483929578</v>
       </c>
       <c r="E144" t="n">
-        <v>87.5445340250358</v>
+        <v>87.544534056886</v>
       </c>
     </row>
     <row r="145">
@@ -25950,7 +25952,7 @@
         <v>86.7516099292686</v>
       </c>
       <c r="E145" t="n">
-        <v>82.5266933762034</v>
+        <v>82.5266934027441</v>
       </c>
     </row>
     <row r="146">
@@ -25967,7 +25969,7 @@
         <v>82.0811714655793</v>
       </c>
       <c r="E146" t="n">
-        <v>77.7964631996578</v>
+        <v>77.796463221393</v>
       </c>
     </row>
     <row r="147">
@@ -25984,7 +25986,7 @@
         <v>77.8259285016056</v>
       </c>
       <c r="E147" t="n">
-        <v>73.3373583597485</v>
+        <v>73.3373583771421</v>
       </c>
     </row>
     <row r="148">
@@ -26001,7 +26003,7 @@
         <v>73.5706855376318</v>
       </c>
       <c r="E148" t="n">
-        <v>69.1338386088718</v>
+        <v>69.1338386223498</v>
       </c>
     </row>
     <row r="149">
@@ -26018,7 +26020,7 @@
         <v>69.315442573658</v>
       </c>
       <c r="E149" t="n">
-        <v>65.1712544287765</v>
+        <v>65.1712544387308</v>
       </c>
     </row>
     <row r="150">
@@ -26035,7 +26037,7 @@
         <v>65.0619351112434</v>
       </c>
       <c r="E150" t="n">
-        <v>61.4357959761152</v>
+        <v>61.4357959829054</v>
       </c>
     </row>
     <row r="151">
@@ -26052,7 +26054,7 @@
         <v>60.8084276488287</v>
       </c>
       <c r="E151" t="n">
-        <v>57.9144449543122</v>
+        <v>57.9144449582683</v>
       </c>
     </row>
     <row r="152">
@@ -26069,7 +26071,7 @@
         <v>56.554920186414</v>
       </c>
       <c r="E152" t="n">
-        <v>54.59492924402</v>
+        <v>54.5949292454447</v>
       </c>
     </row>
     <row r="153">
@@ -26086,7 +26088,7 @@
         <v>53.3831544102782</v>
       </c>
       <c r="E153" t="n">
-        <v>51.4656801340477</v>
+        <v>51.4656801332182</v>
       </c>
     </row>
     <row r="154">
@@ -26103,7 +26105,7 @@
         <v>50.2113886341425</v>
       </c>
       <c r="E154" t="n">
-        <v>48.5157920037096</v>
+        <v>48.5157920008795</v>
       </c>
     </row>
     <row r="155">
@@ -26120,7 +26122,7 @@
         <v>47.0396228580068</v>
       </c>
       <c r="E155" t="n">
-        <v>45.7349843160829</v>
+        <v>45.7349843114843</v>
       </c>
     </row>
     <row r="156">
@@ -26137,7 +26139,7 @@
         <v>44.9534072070397</v>
       </c>
       <c r="E156" t="n">
-        <v>43.1135657897209</v>
+        <v>43.1135657835659</v>
       </c>
     </row>
     <row r="157">
@@ -26154,7 +26156,7 @@
         <v>42.8671915560727</v>
       </c>
       <c r="E157" t="n">
-        <v>40.6424006239562</v>
+        <v>40.6424006164382</v>
       </c>
     </row>
     <row r="158">
@@ -26171,7 +26173,7 @@
         <v>40.7809759051056</v>
       </c>
       <c r="E158" t="n">
-        <v>38.3128766600877</v>
+        <v>38.3128766513833</v>
       </c>
     </row>
     <row r="159">
@@ -26188,7 +26190,7 @@
         <v>39.3834924916548</v>
       </c>
       <c r="E159" t="n">
-        <v>36.1168753674917</v>
+        <v>36.1168753577615</v>
       </c>
     </row>
     <row r="160">
@@ -26205,7 +26207,7 @@
         <v>37.986009078204</v>
       </c>
       <c r="E160" t="n">
-        <v>34.0467435500559</v>
+        <v>34.0467435394462</v>
       </c>
     </row>
     <row r="161">
@@ -26222,7 +26224,7 @@
         <v>36.5885256647532</v>
       </c>
       <c r="E161" t="n">
-        <v>32.0952666743324</v>
+        <v>32.0952666629759</v>
       </c>
     </row>
     <row r="162">
@@ -26239,7 +26241,7 @@
         <v>35.6442372840716</v>
       </c>
       <c r="E162" t="n">
-        <v>30.2556437264563</v>
+        <v>30.2556437144734</v>
       </c>
     </row>
     <row r="163">
@@ -26256,7 +26258,7 @@
         <v>34.69994890339</v>
       </c>
       <c r="E163" t="n">
-        <v>29.19408503833</v>
+        <v>29.194085041219</v>
       </c>
     </row>
     <row r="164">
@@ -26273,7 +26275,7 @@
         <v>33.7556605227084</v>
       </c>
       <c r="E164" t="n">
-        <v>30.5394961811468</v>
+        <v>30.5394961840855</v>
       </c>
     </row>
     <row r="165">
@@ -26290,7 +26292,7 @@
         <v>33.6246995861829</v>
       </c>
       <c r="E165" t="n">
-        <v>31.9469106763837</v>
+        <v>31.9469106793706</v>
       </c>
     </row>
     <row r="166">
@@ -26307,7 +26309,7 @@
         <v>33.4937386496574</v>
       </c>
       <c r="E166" t="n">
-        <v>33.4191859522194</v>
+        <v>33.4191859552528</v>
       </c>
     </row>
     <row r="167">
@@ -26324,7 +26326,7 @@
         <v>33.362777713132</v>
       </c>
       <c r="E167" t="n">
-        <v>34.9593111215799</v>
+        <v>34.9593111246576</v>
       </c>
     </row>
     <row r="168">
@@ -26341,7 +26343,7 @@
         <v>34.953813783425</v>
       </c>
       <c r="E168" t="n">
-        <v>36.5704130508378</v>
+        <v>36.5704130539575</v>
       </c>
     </row>
     <row r="169">
@@ -26358,7 +26360,7 @@
         <v>36.5448498537181</v>
       </c>
       <c r="E169" t="n">
-        <v>38.2557627081882</v>
+        <v>38.2557627113473</v>
       </c>
     </row>
     <row r="170">
@@ -26375,7 +26377,7 @@
         <v>38.1358859240112</v>
       </c>
       <c r="E170" t="n">
-        <v>40.0187818045899</v>
+        <v>40.0187818077854</v>
       </c>
     </row>
     <row r="171">
@@ -26392,7 +26394,7 @@
         <v>41.7141977772194</v>
       </c>
       <c r="E171" t="n">
-        <v>41.8630497407543</v>
+        <v>41.8630497439827</v>
       </c>
     </row>
     <row r="172">
@@ -26409,7 +26411,7 @@
         <v>45.2925096304276</v>
       </c>
       <c r="E172" t="n">
-        <v>43.7923108742871</v>
+        <v>43.7923108775448</v>
       </c>
     </row>
     <row r="173">
@@ -26426,7 +26428,7 @@
         <v>48.8708214836359</v>
       </c>
       <c r="E173" t="n">
-        <v>45.810482121737</v>
+        <v>45.8104821250197</v>
       </c>
     </row>
     <row r="174">
@@ -26443,7 +26445,7 @@
         <v>52.6868608739992</v>
       </c>
       <c r="E174" t="n">
-        <v>47.9216609109839</v>
+        <v>47.9216609142871</v>
       </c>
     </row>
     <row r="175">
@@ -26460,7 +26462,7 @@
         <v>56.5029002643626</v>
       </c>
       <c r="E175" t="n">
-        <v>50.1301335001153</v>
+        <v>50.130133503434</v>
       </c>
     </row>
     <row r="176">
@@ -26477,7 +26479,7 @@
         <v>60.3189396547259</v>
       </c>
       <c r="E176" t="n">
-        <v>52.4403836796773</v>
+        <v>52.4403836830057</v>
       </c>
     </row>
     <row r="177">
@@ -26494,7 +26496,7 @@
         <v>63.5432416791373</v>
       </c>
       <c r="E177" t="n">
-        <v>54.8571018759692</v>
+        <v>54.8571018793013</v>
       </c>
     </row>
     <row r="178">
@@ -26511,7 +26513,7 @@
         <v>66.7675437035487</v>
       </c>
       <c r="E178" t="n">
-        <v>57.3851946738652</v>
+        <v>57.3851946771941</v>
       </c>
     </row>
     <row r="179">
@@ -26528,7 +26530,7 @@
         <v>69.9918457279601</v>
       </c>
       <c r="E179" t="n">
-        <v>60.0297947784946</v>
+        <v>60.0297947818131</v>
       </c>
     </row>
     <row r="180">
@@ -26545,7 +26547,7 @@
         <v>73.0385937863855</v>
       </c>
       <c r="E180" t="n">
-        <v>62.7962714360076</v>
+        <v>62.7962714393076</v>
       </c>
     </row>
     <row r="181">
@@ -26562,7 +26564,7 @@
         <v>76.0853418448109</v>
       </c>
       <c r="E181" t="n">
-        <v>65.6902413345822</v>
+        <v>65.6902413378549</v>
       </c>
     </row>
     <row r="182">
@@ -26579,7 +26581,7 @@
         <v>79.1320899032363</v>
       </c>
       <c r="E182" t="n">
-        <v>68.7175800078043</v>
+        <v>68.7175800110401</v>
       </c>
     </row>
     <row r="183">
@@ -26596,7 +26598,7 @@
         <v>82.313616735394</v>
       </c>
       <c r="E183" t="n">
-        <v>71.8844337635742</v>
+        <v>71.8844337667631</v>
       </c>
     </row>
     <row r="184">
@@ -26613,7 +26615,7 @@
         <v>85.4951435675517</v>
       </c>
       <c r="E184" t="n">
-        <v>75.197232162757</v>
+        <v>75.1972321658875</v>
       </c>
     </row>
     <row r="185">
@@ -26630,7 +26632,7 @@
         <v>88.6766703997095</v>
       </c>
       <c r="E185" t="n">
-        <v>78.662701072912</v>
+        <v>78.6627010759721</v>
       </c>
     </row>
     <row r="186">
@@ -26647,7 +26649,7 @@
         <v>92.5557970035985</v>
       </c>
       <c r="E186" t="n">
-        <v>82.2878763236043</v>
+        <v>82.2878763265807</v>
       </c>
     </row>
     <row r="187">
@@ -26664,7 +26666,7 @@
         <v>96.4349236074875</v>
       </c>
       <c r="E187" t="n">
-        <v>86.0801179910225</v>
+        <v>86.0801179939012</v>
       </c>
     </row>
     <row r="188">
@@ -26681,7 +26683,7 @@
         <v>100.314050211377</v>
       </c>
       <c r="E188" t="n">
-        <v>90.0471253409035</v>
+        <v>90.047125343669</v>
       </c>
     </row>
     <row r="189">
@@ -26698,7 +26700,7 @@
         <v>104.765887156734</v>
       </c>
       <c r="E189" t="n">
-        <v>94.1969524601027</v>
+        <v>94.1969524627386</v>
       </c>
     </row>
     <row r="190">
@@ -26715,7 +26717,7 @@
         <v>109.217724102092</v>
       </c>
       <c r="E190" t="n">
-        <v>98.5380246085469</v>
+        <v>98.5380246110351</v>
       </c>
     </row>
     <row r="191">
@@ -26732,7 +26734,7 @@
         <v>113.669561047449</v>
       </c>
       <c r="E191" t="n">
-        <v>103.079155324767</v>
+        <v>103.079155327088</v>
       </c>
     </row>
     <row r="192">
@@ -26749,7 +26751,7 @@
         <v>119.823598381423</v>
       </c>
       <c r="E192" t="n">
-        <v>107.829564319739</v>
+        <v>107.829564321874</v>
       </c>
     </row>
     <row r="193">
@@ -26766,7 +26768,7 @@
         <v>125.977635715396</v>
       </c>
       <c r="E193" t="n">
-        <v>112.79889619537</v>
+        <v>112.798896197295</v>
       </c>
     </row>
     <row r="194">
@@ -26783,7 +26785,7 @@
         <v>132.13167304937</v>
       </c>
       <c r="E194" t="n">
-        <v>117.997240025616</v>
+        <v>117.997240027308</v>
       </c>
     </row>
     <row r="195">
@@ -26800,7 +26802,7 @@
         <v>138.630712010976</v>
       </c>
       <c r="E195" t="n">
-        <v>123.435149840007</v>
+        <v>123.43514984144</v>
       </c>
     </row>
     <row r="196">
@@ -26817,7 +26819,7 @@
         <v>145.129750972582</v>
       </c>
       <c r="E196" t="n">
-        <v>129.123666051149</v>
+        <v>129.123666052295</v>
       </c>
     </row>
     <row r="197">
@@ -26834,7 +26836,7 @@
         <v>151.628789934187</v>
       </c>
       <c r="E197" t="n">
-        <v>135.074337869721</v>
+        <v>135.074337870551</v>
       </c>
     </row>
     <row r="198">
@@ -26851,7 +26853,7 @@
         <v>158.64203447226</v>
       </c>
       <c r="E198" t="n">
-        <v>141.299246752459</v>
+        <v>141.299246752941</v>
       </c>
     </row>
     <row r="199">
@@ -26868,7 +26870,7 @@
         <v>165.655279010333</v>
       </c>
       <c r="E199" t="n">
-        <v>147.811030930754</v>
+        <v>147.811030930854</v>
       </c>
     </row>
     <row r="200">
@@ -26885,7 +26887,7 @@
         <v>172.668523548405</v>
       </c>
       <c r="E200" t="n">
-        <v>154.622911069637</v>
+        <v>154.62291106932</v>
       </c>
     </row>
     <row r="201">
@@ -26902,7 +26904,7 @@
         <v>180.756146040923</v>
       </c>
       <c r="E201" t="n">
-        <v>161.748717109276</v>
+        <v>161.748717108503</v>
       </c>
     </row>
     <row r="202">
@@ -26919,7 +26921,7 @@
         <v>188.843768533441</v>
       </c>
       <c r="E202" t="n">
-        <v>169.20291634345</v>
+        <v>169.20291634218</v>
       </c>
     </row>
     <row r="203">
@@ -26936,7 +26938,7 @@
         <v>196.931391025958</v>
       </c>
       <c r="E203" t="n">
-        <v>177.000642792033</v>
+        <v>177.000642790221</v>
       </c>
     </row>
     <row r="204">
@@ -26953,7 +26955,7 @@
         <v>204.756026605648</v>
       </c>
       <c r="E204" t="n">
-        <v>185.157727927103</v>
+        <v>185.157727924703</v>
       </c>
     </row>
     <row r="205">
@@ -26970,7 +26972,7 @@
         <v>212.580662185338</v>
       </c>
       <c r="E205" t="n">
-        <v>193.690732815069</v>
+        <v>193.690732812029</v>
       </c>
     </row>
     <row r="206">
@@ -26987,7 +26989,7 @@
         <v>220.405297765029</v>
       </c>
       <c r="E206" t="n">
-        <v>202.616981740068</v>
+        <v>202.616981736336</v>
       </c>
     </row>
     <row r="207">
@@ -27004,7 +27006,7 @@
         <v>223.619215533872</v>
       </c>
       <c r="E207" t="n">
-        <v>211.954597376903</v>
+        <v>211.95459737242</v>
       </c>
     </row>
     <row r="208">
@@ -27021,7 +27023,7 @@
         <v>226.833133302715</v>
       </c>
       <c r="E208" t="n">
-        <v>221.722537584918</v>
+        <v>221.722537579623</v>
       </c>
     </row>
     <row r="209">
@@ -27038,7 +27040,7 @@
         <v>230.047051071558</v>
       </c>
       <c r="E209" t="n">
-        <v>231.940633897535</v>
+        <v>231.940633891362</v>
       </c>
     </row>
     <row r="210">
@@ -27055,7 +27057,7 @@
         <v>233.94105022472</v>
       </c>
       <c r="E210" t="n">
-        <v>242.629631785566</v>
+        <v>242.629631778447</v>
       </c>
     </row>
     <row r="211">
@@ -27072,7 +27074,7 @@
         <v>237.835049377882</v>
       </c>
       <c r="E211" t="n">
-        <v>253.811232776084</v>
+        <v>253.811232767944</v>
       </c>
     </row>
     <row r="212">
@@ -27089,7 +27091,7 @@
         <v>241.729048531044</v>
       </c>
       <c r="E212" t="n">
-        <v>265.50813851232</v>
+        <v>265.508138503079</v>
       </c>
     </row>
     <row r="213">
@@ -27106,7 +27108,7 @@
         <v>245.49755297727</v>
       </c>
       <c r="E213" t="n">
-        <v>277.744096844085</v>
+        <v>277.74409683366</v>
       </c>
     </row>
     <row r="214">
@@ -27123,7 +27125,7 @@
         <v>249.266057423497</v>
       </c>
       <c r="E214" t="n">
-        <v>290.543950042258</v>
+        <v>290.54395003056</v>
       </c>
     </row>
     <row r="215">
@@ -27140,7 +27142,7 @@
         <v>253.034561869723</v>
       </c>
       <c r="E215" t="n">
-        <v>303.933685235248</v>
+        <v>303.933685222181</v>
       </c>
     </row>
     <row r="216">
@@ -27157,7 +27159,7 @@
         <v>256.573967912691</v>
       </c>
       <c r="E216" t="n">
-        <v>317.940487169817</v>
+        <v>317.940487155281</v>
       </c>
     </row>
     <row r="217">
@@ -27174,7 +27176,7 @@
         <v>260.113373955659</v>
       </c>
       <c r="E217" t="n">
-        <v>332.5927934034</v>
+        <v>332.592793387286</v>
       </c>
     </row>
   </sheetData>
@@ -27219,7 +27221,7 @@
         <v>0.159098184570432</v>
       </c>
       <c r="E2" t="n">
-        <v>0.144842301664348</v>
+        <v>0.144842301664242</v>
       </c>
     </row>
     <row r="3">
@@ -27236,7 +27238,7 @@
         <v>0.158858250638995</v>
       </c>
       <c r="E3" t="n">
-        <v>0.146752321229508</v>
+        <v>0.14675232122941</v>
       </c>
     </row>
     <row r="4">
@@ -27253,7 +27255,7 @@
         <v>0.158618316707557</v>
       </c>
       <c r="E4" t="n">
-        <v>0.148687528013441</v>
+        <v>0.14868752801334</v>
       </c>
     </row>
     <row r="5">
@@ -27270,7 +27272,7 @@
         <v>0.15837838277612</v>
       </c>
       <c r="E5" t="n">
-        <v>0.150648254157238</v>
+        <v>0.150648254157138</v>
       </c>
     </row>
     <row r="6">
@@ -27287,7 +27289,7 @@
         <v>0.158243665856567</v>
       </c>
       <c r="E6" t="n">
-        <v>0.152634836181902</v>
+        <v>0.152634836181804</v>
       </c>
     </row>
     <row r="7">
@@ -27304,7 +27306,7 @@
         <v>0.158108948937014</v>
       </c>
       <c r="E7" t="n">
-        <v>0.154647615046104</v>
+        <v>0.154647615046008</v>
       </c>
     </row>
     <row r="8">
@@ -27321,7 +27323,7 @@
         <v>0.157974232017462</v>
       </c>
       <c r="E8" t="n">
-        <v>0.156686936204697</v>
+        <v>0.156686936204602</v>
       </c>
     </row>
     <row r="9">
@@ -27338,7 +27340,7 @@
         <v>0.158043187548997</v>
       </c>
       <c r="E9" t="n">
-        <v>0.158753149668008</v>
+        <v>0.158753149667915</v>
       </c>
     </row>
     <row r="10">
@@ -27355,7 +27357,7 @@
         <v>0.158112143080532</v>
       </c>
       <c r="E10" t="n">
-        <v>0.160846610061915</v>
+        <v>0.160846610061824</v>
       </c>
     </row>
     <row r="11">
@@ -27372,7 +27374,7 @@
         <v>0.158181098612066</v>
       </c>
       <c r="E11" t="n">
-        <v>0.162967676688706</v>
+        <v>0.162967676688617</v>
       </c>
     </row>
     <row r="12">
@@ -27389,7 +27391,7 @@
         <v>0.158536017536113</v>
       </c>
       <c r="E12" t="n">
-        <v>0.165116713588751</v>
+        <v>0.165116713588663</v>
       </c>
     </row>
     <row r="13">
@@ -27406,7 +27408,7 @@
         <v>0.158890936460159</v>
       </c>
       <c r="E13" t="n">
-        <v>0.167294089602978</v>
+        <v>0.167294089602892</v>
       </c>
     </row>
     <row r="14">
@@ -27423,7 +27425,7 @@
         <v>0.159245855384205</v>
       </c>
       <c r="E14" t="n">
-        <v>0.169500178436182</v>
+        <v>0.169500178436098</v>
       </c>
     </row>
     <row r="15">
@@ -27440,7 +27442,7 @@
         <v>0.160806216921749</v>
       </c>
       <c r="E15" t="n">
-        <v>0.171735358721161</v>
+        <v>0.171735358721079</v>
       </c>
     </row>
     <row r="16">
@@ -27457,7 +27459,7 @@
         <v>0.162366578459293</v>
       </c>
       <c r="E16" t="n">
-        <v>0.174000014083703</v>
+        <v>0.174000014083624</v>
       </c>
     </row>
     <row r="17">
@@ -27474,7 +27476,7 @@
         <v>0.163926939996836</v>
       </c>
       <c r="E17" t="n">
-        <v>0.176294533208428</v>
+        <v>0.17629453320835</v>
       </c>
     </row>
     <row r="18">
@@ -27491,7 +27493,7 @@
         <v>0.16619823314299</v>
       </c>
       <c r="E18" t="n">
-        <v>0.178619309905494</v>
+        <v>0.178619309905419</v>
       </c>
     </row>
     <row r="19">
@@ -27508,7 +27510,7 @@
         <v>0.168469526289143</v>
       </c>
       <c r="E19" t="n">
-        <v>0.180974743178196</v>
+        <v>0.180974743178123</v>
       </c>
     </row>
     <row r="20">
@@ -27525,7 +27527,7 @@
         <v>0.170740819435297</v>
       </c>
       <c r="E20" t="n">
-        <v>0.183361237291436</v>
+        <v>0.183361237291365</v>
       </c>
     </row>
     <row r="21">
@@ -27542,7 +27544,7 @@
         <v>0.173928506424126</v>
       </c>
       <c r="E21" t="n">
-        <v>0.185779201841116</v>
+        <v>0.185779201841048</v>
       </c>
     </row>
     <row r="22">
@@ -27559,7 +27561,7 @@
         <v>0.177116193412954</v>
       </c>
       <c r="E22" t="n">
-        <v>0.188229051824435</v>
+        <v>0.18822905182437</v>
       </c>
     </row>
     <row r="23">
@@ -27576,7 +27578,7 @@
         <v>0.180303880401783</v>
       </c>
       <c r="E23" t="n">
-        <v>0.190711207711113</v>
+        <v>0.19071120771105</v>
       </c>
     </row>
     <row r="24">
@@ -27593,7 +27595,7 @@
         <v>0.183233529405899</v>
       </c>
       <c r="E24" t="n">
-        <v>0.193226095515558</v>
+        <v>0.193226095515498</v>
       </c>
     </row>
     <row r="25">
@@ -27610,7 +27612,7 @@
         <v>0.186163178410016</v>
       </c>
       <c r="E25" t="n">
-        <v>0.195774146869985</v>
+        <v>0.195774146869928</v>
       </c>
     </row>
     <row r="26">
@@ -27627,7 +27629,7 @@
         <v>0.189092827414132</v>
       </c>
       <c r="E26" t="n">
-        <v>0.198355799098494</v>
+        <v>0.19835579909844</v>
       </c>
     </row>
     <row r="27">
@@ -27644,7 +27646,7 @@
         <v>0.190237798287628</v>
       </c>
       <c r="E27" t="n">
-        <v>0.200971495292131</v>
+        <v>0.200971495292079</v>
       </c>
     </row>
     <row r="28">
@@ -27661,7 +27663,7 @@
         <v>0.191382769161124</v>
       </c>
       <c r="E28" t="n">
-        <v>0.203621684384934</v>
+        <v>0.203621684384886</v>
       </c>
     </row>
     <row r="29">
@@ -27678,7 +27680,7 @@
         <v>0.192527740034621</v>
       </c>
       <c r="E29" t="n">
-        <v>0.206306821230987</v>
+        <v>0.206306821230941</v>
       </c>
     </row>
     <row r="30">
@@ -27695,7 +27697,7 @@
         <v>0.192479631622702</v>
       </c>
       <c r="E30" t="n">
-        <v>0.209027366682482</v>
+        <v>0.20902736668244</v>
       </c>
     </row>
     <row r="31">
@@ -27712,7 +27714,7 @@
         <v>0.192431523210784</v>
       </c>
       <c r="E31" t="n">
-        <v>0.211783787668822</v>
+        <v>0.211783787668783</v>
       </c>
     </row>
     <row r="32">
@@ -27729,7 +27731,7 @@
         <v>0.192383414798865</v>
       </c>
       <c r="E32" t="n">
-        <v>0.214576557276754</v>
+        <v>0.214576557276719</v>
       </c>
     </row>
     <row r="33">
@@ -27746,7 +27748,7 @@
         <v>0.191994996056851</v>
       </c>
       <c r="E33" t="n">
-        <v>0.217406154831569</v>
+        <v>0.217406154831537</v>
       </c>
     </row>
     <row r="34">
@@ -27763,7 +27765,7 @@
         <v>0.191606577314838</v>
       </c>
       <c r="E34" t="n">
-        <v>0.220273065979368</v>
+        <v>0.22027306597934</v>
       </c>
     </row>
     <row r="35">
@@ -27780,7 +27782,7 @@
         <v>0.191218158572824</v>
       </c>
       <c r="E35" t="n">
-        <v>0.217285725761663</v>
+        <v>0.217285725761754</v>
       </c>
     </row>
     <row r="36">
@@ -27797,7 +27799,7 @@
         <v>0.189678830685113</v>
       </c>
       <c r="E36" t="n">
-        <v>0.214338494530582</v>
+        <v>0.214338494530671</v>
       </c>
     </row>
     <row r="37">
@@ -27814,7 +27816,7 @@
         <v>0.188139502797403</v>
       </c>
       <c r="E37" t="n">
-        <v>0.211431239105086</v>
+        <v>0.211431239105173</v>
       </c>
     </row>
     <row r="38">
@@ -27831,7 +27833,7 @@
         <v>0.186600174909693</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2085634172593</v>
+        <v>0.208563417259385</v>
       </c>
     </row>
     <row r="39">
@@ -27848,7 +27850,7 @@
         <v>0.184646740819725</v>
       </c>
       <c r="E39" t="n">
-        <v>0.205734494122021</v>
+        <v>0.205734494122104</v>
       </c>
     </row>
     <row r="40">
@@ -27865,7 +27867,7 @@
         <v>0.182693306729757</v>
       </c>
       <c r="E40" t="n">
-        <v>0.202943942076959</v>
+        <v>0.202943942077039</v>
       </c>
     </row>
     <row r="41">
@@ -27882,7 +27884,7 @@
         <v>0.18073987263979</v>
       </c>
       <c r="E41" t="n">
-        <v>0.200191240664331</v>
+        <v>0.20019124066441</v>
       </c>
     </row>
     <row r="42">
@@ -27899,7 +27901,7 @@
         <v>0.17992286005204</v>
       </c>
       <c r="E42" t="n">
-        <v>0.197475876483796</v>
+        <v>0.197475876483873</v>
       </c>
     </row>
     <row r="43">
@@ -27916,7 +27918,7 @@
         <v>0.179105847464291</v>
       </c>
       <c r="E43" t="n">
-        <v>0.194797343098697</v>
+        <v>0.194797343098771</v>
       </c>
     </row>
     <row r="44">
@@ -27933,7 +27935,7 @@
         <v>0.178288834876541</v>
       </c>
       <c r="E44" t="n">
-        <v>0.192155140941608</v>
+        <v>0.192155140941681</v>
       </c>
     </row>
     <row r="45">
@@ -27950,7 +27952,7 @@
         <v>0.179042431173914</v>
       </c>
       <c r="E45" t="n">
-        <v>0.189548777221163</v>
+        <v>0.189548777221233</v>
       </c>
     </row>
     <row r="46">
@@ -27967,7 +27969,7 @@
         <v>0.179796027471287</v>
       </c>
       <c r="E46" t="n">
-        <v>0.186977765830142</v>
+        <v>0.186977765830211</v>
       </c>
     </row>
     <row r="47">
@@ -27984,7 +27986,7 @@
         <v>0.180549623768661</v>
       </c>
       <c r="E47" t="n">
-        <v>0.184441627254814</v>
+        <v>0.18444162725488</v>
       </c>
     </row>
     <row r="48">
@@ -28001,7 +28003,7 @@
         <v>0.181027987213799</v>
       </c>
       <c r="E48" t="n">
-        <v>0.181939888485498</v>
+        <v>0.181939888485563</v>
       </c>
     </row>
     <row r="49">
@@ -28018,7 +28020,7 @@
         <v>0.181506350658937</v>
       </c>
       <c r="E49" t="n">
-        <v>0.179472082928349</v>
+        <v>0.179472082928412</v>
       </c>
     </row>
     <row r="50">
@@ -28035,7 +28037,7 @@
         <v>0.181984714104075</v>
       </c>
       <c r="E50" t="n">
-        <v>0.177037750318329</v>
+        <v>0.17703775031839</v>
       </c>
     </row>
     <row r="51">
@@ -28052,7 +28054,7 @@
         <v>0.182821390041931</v>
       </c>
       <c r="E51" t="n">
-        <v>0.174636436633366</v>
+        <v>0.174636436633426</v>
       </c>
     </row>
     <row r="52">
@@ -28069,7 +28071,7 @@
         <v>0.183658065979786</v>
       </c>
       <c r="E52" t="n">
-        <v>0.172267694009678</v>
+        <v>0.172267694009736</v>
       </c>
     </row>
     <row r="53">
@@ -28086,7 +28088,7 @@
         <v>0.184494741917642</v>
       </c>
       <c r="E53" t="n">
-        <v>0.16993108065824</v>
+        <v>0.169931080658297</v>
       </c>
     </row>
     <row r="54">
@@ -28103,7 +28105,7 @@
         <v>0.185611022650923</v>
       </c>
       <c r="E54" t="n">
-        <v>0.167626160782387</v>
+        <v>0.167626160782441</v>
       </c>
     </row>
     <row r="55">
@@ -28120,7 +28122,7 @@
         <v>0.186727303384205</v>
       </c>
       <c r="E55" t="n">
-        <v>0.165352504496534</v>
+        <v>0.165352504496587</v>
       </c>
     </row>
     <row r="56">
@@ -28137,7 +28139,7 @@
         <v>0.187843584117486</v>
       </c>
       <c r="E56" t="n">
-        <v>0.163109687746002</v>
+        <v>0.163109687746054</v>
       </c>
     </row>
     <row r="57">
@@ -28154,7 +28156,7 @@
         <v>0.187607462630365</v>
       </c>
       <c r="E57" t="n">
-        <v>0.160897292227927</v>
+        <v>0.160897292227977</v>
       </c>
     </row>
     <row r="58">
@@ -28171,7 +28173,7 @@
         <v>0.187371341143244</v>
       </c>
       <c r="E58" t="n">
-        <v>0.15871490531324</v>
+        <v>0.158714905313289</v>
       </c>
     </row>
     <row r="59">
@@ -28188,7 +28190,7 @@
         <v>0.187135219656123</v>
       </c>
       <c r="E59" t="n">
-        <v>0.156562119969713</v>
+        <v>0.156562119969761</v>
       </c>
     </row>
     <row r="60">
@@ -28205,7 +28207,7 @@
         <v>0.185283572613553</v>
       </c>
       <c r="E60" t="n">
-        <v>0.154438534686044</v>
+        <v>0.154438534686089</v>
       </c>
     </row>
     <row r="61">
@@ -28222,7 +28224,7 @@
         <v>0.183431925570982</v>
       </c>
       <c r="E61" t="n">
-        <v>0.152343753396966</v>
+        <v>0.152343753397011</v>
       </c>
     </row>
     <row r="62">
@@ -28239,7 +28241,7 @@
         <v>0.181580278528411</v>
       </c>
       <c r="E62" t="n">
-        <v>0.150277385409388</v>
+        <v>0.150277385409431</v>
       </c>
     </row>
     <row r="63">
@@ -28256,7 +28258,7 @@
         <v>0.179671220405439</v>
       </c>
       <c r="E63" t="n">
-        <v>0.148239045329517</v>
+        <v>0.148239045329559</v>
       </c>
     </row>
     <row r="64">
@@ -28273,7 +28275,7 @@
         <v>0.177762162282467</v>
       </c>
       <c r="E64" t="n">
-        <v>0.146228352990988</v>
+        <v>0.146228352991028</v>
       </c>
     </row>
     <row r="65">
@@ -28290,7 +28292,7 @@
         <v>0.175853104159495</v>
       </c>
       <c r="E65" t="n">
-        <v>0.144244933383953</v>
+        <v>0.144244933383992</v>
       </c>
     </row>
     <row r="66">
@@ -28307,7 +28309,7 @@
         <v>0.173123725462984</v>
       </c>
       <c r="E66" t="n">
-        <v>0.142288416585142</v>
+        <v>0.14228841658518</v>
       </c>
     </row>
     <row r="67">
@@ -28324,7 +28326,7 @@
         <v>0.170394346766474</v>
       </c>
       <c r="E67" t="n">
-        <v>0.140358437688872</v>
+        <v>0.140358437688909</v>
       </c>
     </row>
     <row r="68">
@@ -28341,7 +28343,7 @@
         <v>0.167664968069964</v>
       </c>
       <c r="E68" t="n">
-        <v>0.138454636738983</v>
+        <v>0.138454636739019</v>
       </c>
     </row>
     <row r="69">
@@ -28358,7 +28360,7 @@
         <v>0.164146244938319</v>
       </c>
       <c r="E69" t="n">
-        <v>0.136576658661708</v>
+        <v>0.136576658661743</v>
       </c>
     </row>
     <row r="70">
@@ -28375,7 +28377,7 @@
         <v>0.160627521806675</v>
       </c>
       <c r="E70" t="n">
-        <v>0.134724153199449</v>
+        <v>0.134724153199482</v>
       </c>
     </row>
     <row r="71">
@@ -28392,7 +28394,7 @@
         <v>0.15710879867503</v>
       </c>
       <c r="E71" t="n">
-        <v>0.132896774845447</v>
+        <v>0.13289677484548</v>
       </c>
     </row>
     <row r="72">
@@ -28409,7 +28411,7 @@
         <v>0.15295556166299</v>
       </c>
       <c r="E72" t="n">
-        <v>0.131094182779349</v>
+        <v>0.13109418277938</v>
       </c>
     </row>
     <row r="73">
@@ -28426,7 +28428,7 @@
         <v>0.14880232465095</v>
       </c>
       <c r="E73" t="n">
-        <v>0.129316040803635</v>
+        <v>0.129316040803665</v>
       </c>
     </row>
     <row r="74">
@@ -28443,7 +28445,7 @@
         <v>0.14464908763891</v>
       </c>
       <c r="E74" t="n">
-        <v>0.127562017280919</v>
+        <v>0.127562017280948</v>
       </c>
     </row>
     <row r="75">
@@ -28460,7 +28462,7 @@
         <v>0.140739141606624</v>
       </c>
       <c r="E75" t="n">
-        <v>0.125831785072098</v>
+        <v>0.125831785072126</v>
       </c>
     </row>
     <row r="76">
@@ -28477,7 +28479,7 @@
         <v>0.136829195574339</v>
       </c>
       <c r="E76" t="n">
-        <v>0.12412502147533</v>
+        <v>0.124125021475357</v>
       </c>
     </row>
     <row r="77">
@@ -28494,7 +28496,7 @@
         <v>0.132919249542053</v>
       </c>
       <c r="E77" t="n">
-        <v>0.122441408165858</v>
+        <v>0.122441408165884</v>
       </c>
     </row>
     <row r="78">
@@ -28511,7 +28513,7 @@
         <v>0.129514006435575</v>
       </c>
       <c r="E78" t="n">
-        <v>0.120780631136631</v>
+        <v>0.120780631136656</v>
       </c>
     </row>
     <row r="79">
@@ -28528,7 +28530,7 @@
         <v>0.126108763329097</v>
       </c>
       <c r="E79" t="n">
-        <v>0.119142380639743</v>
+        <v>0.119142380639768</v>
       </c>
     </row>
     <row r="80">
@@ -28545,7 +28547,7 @@
         <v>0.122703520222618</v>
       </c>
       <c r="E80" t="n">
-        <v>0.117526351128666</v>
+        <v>0.117526351128689</v>
       </c>
     </row>
     <row r="81">
@@ -28562,7 +28564,7 @@
         <v>0.1193967365134</v>
       </c>
       <c r="E81" t="n">
-        <v>0.115932241201255</v>
+        <v>0.115932241201277</v>
       </c>
     </row>
     <row r="82">
@@ -28579,7 +28581,7 @@
         <v>0.116089952804181</v>
       </c>
       <c r="E82" t="n">
-        <v>0.114359753543541</v>
+        <v>0.114359753543563</v>
       </c>
     </row>
     <row r="83">
@@ -28596,7 +28598,7 @@
         <v>0.112783169094962</v>
       </c>
       <c r="E83" t="n">
-        <v>0.112808594874278</v>
+        <v>0.112808594874299</v>
       </c>
     </row>
     <row r="84">
@@ -28613,7 +28615,7 @@
         <v>0.109169063864951</v>
       </c>
       <c r="E84" t="n">
-        <v>0.111278475890243</v>
+        <v>0.111278475890263</v>
       </c>
     </row>
     <row r="85">
@@ -28630,7 +28632,7 @@
         <v>0.10555495863494</v>
       </c>
       <c r="E85" t="n">
-        <v>0.109769111212277</v>
+        <v>0.109769111212296</v>
       </c>
     </row>
     <row r="86">
@@ -28647,7 +28649,7 @@
         <v>0.101940853404929</v>
       </c>
       <c r="E86" t="n">
-        <v>0.108280219332064</v>
+        <v>0.108280219332082</v>
       </c>
     </row>
     <row r="87">
@@ -28664,7 +28666,7 @@
         <v>0.099340565500944</v>
       </c>
       <c r="E87" t="n">
-        <v>0.106811522559622</v>
+        <v>0.106811522559639</v>
       </c>
     </row>
     <row r="88">
@@ -28681,7 +28683,7 @@
         <v>0.0967402775969591</v>
       </c>
       <c r="E88" t="n">
-        <v>0.105362746971518</v>
+        <v>0.105362746971534</v>
       </c>
     </row>
     <row r="89">
@@ -28698,7 +28700,7 @@
         <v>0.0941399896929743</v>
       </c>
       <c r="E89" t="n">
-        <v>0.103933622359772</v>
+        <v>0.103933622359788</v>
       </c>
     </row>
     <row r="90">
@@ -28715,7 +28717,7 @@
         <v>0.0922033306712248</v>
       </c>
       <c r="E90" t="n">
-        <v>0.102523882181469</v>
+        <v>0.102523882181484</v>
       </c>
     </row>
     <row r="91">
@@ -28732,7 +28734,7 @@
         <v>0.0902666716494752</v>
       </c>
       <c r="E91" t="n">
-        <v>0.101133263509038</v>
+        <v>0.101133263509052</v>
       </c>
     </row>
     <row r="92">
@@ -28749,7 +28751,7 @@
         <v>0.0883300126277257</v>
       </c>
       <c r="E92" t="n">
-        <v>0.0997615069812207</v>
+        <v>0.0997615069812346</v>
       </c>
     </row>
     <row r="93">
@@ -28766,7 +28768,7 @@
         <v>0.0861294300285648</v>
       </c>
       <c r="E93" t="n">
-        <v>0.098408356754697</v>
+        <v>0.0984083567547102</v>
       </c>
     </row>
     <row r="94">
@@ -28783,7 +28785,7 @@
         <v>0.0839288474294038</v>
       </c>
       <c r="E94" t="n">
-        <v>0.0970735604563662</v>
+        <v>0.0970735604563787</v>
       </c>
     </row>
     <row r="95">
@@ -28800,7 +28802,7 @@
         <v>0.0817282648302429</v>
       </c>
       <c r="E95" t="n">
-        <v>0.0957568691362789</v>
+        <v>0.0957568691362908</v>
       </c>
     </row>
     <row r="96">
@@ -28817,7 +28819,7 @@
         <v>0.0798845367710929</v>
       </c>
       <c r="E96" t="n">
-        <v>0.0944580372212062</v>
+        <v>0.0944580372212175</v>
       </c>
     </row>
     <row r="97">
@@ -28834,7 +28836,7 @@
         <v>0.0780408087119429</v>
       </c>
       <c r="E97" t="n">
-        <v>0.0931768224688377</v>
+        <v>0.0931768224688483</v>
       </c>
     </row>
     <row r="98">
@@ -28851,7 +28853,7 @@
         <v>0.0761970806527929</v>
       </c>
       <c r="E98" t="n">
-        <v>0.0919129859226015</v>
+        <v>0.0919129859226115</v>
       </c>
     </row>
     <row r="99">
@@ -28868,7 +28870,7 @@
         <v>0.0752817988300912</v>
       </c>
       <c r="E99" t="n">
-        <v>0.0906662918670971</v>
+        <v>0.0906662918671066</v>
       </c>
     </row>
     <row r="100">
@@ -28885,7 +28887,7 @@
         <v>0.0743665170073895</v>
       </c>
       <c r="E100" t="n">
-        <v>0.089436507784133</v>
+        <v>0.0894365077841418</v>
       </c>
     </row>
     <row r="101">
@@ -28902,7 +28904,7 @@
         <v>0.0734512351846878</v>
       </c>
       <c r="E101" t="n">
-        <v>0.0882234043093591</v>
+        <v>0.0882234043093675</v>
       </c>
     </row>
     <row r="102">
@@ -28919,7 +28921,7 @@
         <v>0.0730436949264373</v>
       </c>
       <c r="E102" t="n">
-        <v>0.08702675518949</v>
+        <v>0.0870267551894978</v>
       </c>
     </row>
     <row r="103">
@@ -28936,7 +28938,7 @@
         <v>0.0726361546681869</v>
       </c>
       <c r="E103" t="n">
-        <v>0.0858463372401055</v>
+        <v>0.0858463372401128</v>
       </c>
     </row>
     <row r="104">
@@ -28953,7 +28955,7 @@
         <v>0.0722286144099365</v>
       </c>
       <c r="E104" t="n">
-        <v>0.084681930304026</v>
+        <v>0.0846819303040327</v>
       </c>
     </row>
     <row r="105">
@@ -28970,7 +28972,7 @@
         <v>0.0725086623425093</v>
       </c>
       <c r="E105" t="n">
-        <v>0.0835333172102509</v>
+        <v>0.0835333172102572</v>
       </c>
     </row>
     <row r="106">
@@ -28987,7 +28989,7 @@
         <v>0.0727887102750822</v>
       </c>
       <c r="E106" t="n">
-        <v>0.0824002837334551</v>
+        <v>0.0824002837334608</v>
       </c>
     </row>
     <row r="107">
@@ -29004,7 +29006,7 @@
         <v>0.073068758207655</v>
       </c>
       <c r="E107" t="n">
-        <v>0.0812826185540334</v>
+        <v>0.0812826185540387</v>
       </c>
     </row>
     <row r="108">
@@ -29021,7 +29023,7 @@
         <v>0.0748444863132765</v>
       </c>
       <c r="E108" t="n">
-        <v>0.0801801132186886</v>
+        <v>0.0801801132186934</v>
       </c>
     </row>
     <row r="109">
@@ -29038,7 +29040,7 @@
         <v>0.076620214418898</v>
       </c>
       <c r="E109" t="n">
-        <v>0.079092562101553</v>
+        <v>0.0790925621015573</v>
       </c>
     </row>
     <row r="110">
@@ -29055,7 +29057,7 @@
         <v>0.0783959425245195</v>
       </c>
       <c r="E110" t="n">
-        <v>0.0780197623658372</v>
+        <v>0.0780197623658411</v>
       </c>
     </row>
     <row r="111">
@@ -29072,7 +29074,7 @@
         <v>0.0798718103144731</v>
       </c>
       <c r="E111" t="n">
-        <v>0.0769615139260003</v>
+        <v>0.0769615139260038</v>
       </c>
     </row>
     <row r="112">
@@ -29089,7 +29091,7 @@
         <v>0.0813476781044268</v>
       </c>
       <c r="E112" t="n">
-        <v>0.0759176194104315</v>
+        <v>0.0759176194104346</v>
       </c>
     </row>
     <row r="113">
@@ -29106,7 +29108,7 @@
         <v>0.0828235458943804</v>
       </c>
       <c r="E113" t="n">
-        <v>0.0748878841246393</v>
+        <v>0.074887884124642</v>
       </c>
     </row>
     <row r="114">
@@ -29123,7 +29125,7 @@
         <v>0.0825822811937095</v>
       </c>
       <c r="E114" t="n">
-        <v>0.0738721160149394</v>
+        <v>0.0738721160149415</v>
       </c>
     </row>
     <row r="115">
@@ -29140,7 +29142,7 @@
         <v>0.0823410164930386</v>
       </c>
       <c r="E115" t="n">
-        <v>0.0728701256326347</v>
+        <v>0.0728701256326366</v>
       </c>
     </row>
     <row r="116">
@@ -29157,7 +29159,7 @@
         <v>0.0820997517923678</v>
       </c>
       <c r="E116" t="n">
-        <v>0.0718817260986824</v>
+        <v>0.0718817260986839</v>
       </c>
     </row>
     <row r="117">
@@ -29174,7 +29176,7 @@
         <v>0.0815237508588604</v>
       </c>
       <c r="E117" t="n">
-        <v>0.0709067330688392</v>
+        <v>0.0709067330688403</v>
       </c>
     </row>
     <row r="118">
@@ -29191,7 +29193,7 @@
         <v>0.080947749925353</v>
       </c>
       <c r="E118" t="n">
-        <v>0.0699449646992795</v>
+        <v>0.0699449646992802</v>
       </c>
     </row>
     <row r="119">
@@ -29208,7 +29210,7 @@
         <v>0.0803717489918457</v>
       </c>
       <c r="E119" t="n">
-        <v>0.0689962416126802</v>
+        <v>0.0689962416126806</v>
       </c>
     </row>
     <row r="120">
@@ -29225,7 +29227,7 @@
         <v>0.0796837868369671</v>
       </c>
       <c r="E120" t="n">
-        <v>0.0680603868647656</v>
+        <v>0.0680603868647657</v>
       </c>
     </row>
     <row r="121">
@@ -29242,7 +29244,7 @@
         <v>0.0789958246820886</v>
       </c>
       <c r="E121" t="n">
-        <v>0.0671372259113061</v>
+        <v>0.0671372259113058</v>
       </c>
     </row>
     <row r="122">
@@ -29259,7 +29261,7 @@
         <v>0.0783078625272101</v>
       </c>
       <c r="E122" t="n">
-        <v>0.0662265865755635</v>
+        <v>0.0662265865755629</v>
       </c>
     </row>
     <row r="123">
@@ -29276,7 +29278,7 @@
         <v>0.0772176727510095</v>
       </c>
       <c r="E123" t="n">
-        <v>0.0653282990161796</v>
+        <v>0.0653282990161787</v>
       </c>
     </row>
     <row r="124">
@@ -29293,7 +29295,7 @@
         <v>0.0761274829748089</v>
       </c>
       <c r="E124" t="n">
-        <v>0.0644421956954991</v>
+        <v>0.0644421956954979</v>
       </c>
     </row>
     <row r="125">
@@ -29310,7 +29312,7 @@
         <v>0.0750372931986082</v>
       </c>
       <c r="E125" t="n">
-        <v>0.0635681113483224</v>
+        <v>0.0635681113483208</v>
       </c>
     </row>
     <row r="126">
@@ -29327,7 +29329,7 @@
         <v>0.0748704799939035</v>
       </c>
       <c r="E126" t="n">
-        <v>0.0627058829510824</v>
+        <v>0.0627058829510806</v>
       </c>
     </row>
     <row r="127">
@@ -29344,7 +29346,7 @@
         <v>0.0747036667891987</v>
       </c>
       <c r="E127" t="n">
-        <v>0.0618553496914395</v>
+        <v>0.0618553496914374</v>
       </c>
     </row>
     <row r="128">
@@ -29361,7 +29363,7 @@
         <v>0.0745368535844939</v>
       </c>
       <c r="E128" t="n">
-        <v>0.0610163529382887</v>
+        <v>0.0610163529382863</v>
       </c>
     </row>
     <row r="129">
@@ -29378,7 +29380,7 @@
         <v>0.074678027945408</v>
       </c>
       <c r="E129" t="n">
-        <v>0.0601887362121737</v>
+        <v>0.0601887362121711</v>
       </c>
     </row>
     <row r="130">
@@ -29395,7 +29397,7 @@
         <v>0.0748192023063221</v>
       </c>
       <c r="E130" t="n">
-        <v>0.0593723451561022</v>
+        <v>0.0593723451560994</v>
       </c>
     </row>
     <row r="131">
@@ -29412,7 +29414,7 @@
         <v>0.0749603766672362</v>
       </c>
       <c r="E131" t="n">
-        <v>0.0585670275067573</v>
+        <v>0.0585670275067542</v>
       </c>
     </row>
     <row r="132">
@@ -29429,7 +29431,7 @@
         <v>0.0747204129519306</v>
       </c>
       <c r="E132" t="n">
-        <v>0.0577726330660989</v>
+        <v>0.0577726330660955</v>
       </c>
     </row>
     <row r="133">
@@ -29446,7 +29448,7 @@
         <v>0.0744804492366251</v>
       </c>
       <c r="E133" t="n">
-        <v>0.0569890136733508</v>
+        <v>0.0569890136733471</v>
       </c>
     </row>
     <row r="134">
@@ -29463,7 +29465,7 @@
         <v>0.0742404855213196</v>
       </c>
       <c r="E134" t="n">
-        <v>0.0562160231773674</v>
+        <v>0.0562160231773636</v>
       </c>
     </row>
     <row r="135">
@@ -29480,7 +29482,7 @@
         <v>0.0732173188197152</v>
       </c>
       <c r="E135" t="n">
-        <v>0.0554535174093758</v>
+        <v>0.0554535174093718</v>
       </c>
     </row>
     <row r="136">
@@ -29497,7 +29499,7 @@
         <v>0.0721941521181107</v>
       </c>
       <c r="E136" t="n">
-        <v>0.0547013541560866</v>
+        <v>0.0547013541560823</v>
       </c>
     </row>
     <row r="137">
@@ -29514,7 +29516,7 @@
         <v>0.0711709854165062</v>
       </c>
       <c r="E137" t="n">
-        <v>0.0539593931331703</v>
+        <v>0.0539593931331658</v>
       </c>
     </row>
     <row r="138">
@@ -29531,7 +29533,7 @@
         <v>0.0690729130644046</v>
       </c>
       <c r="E138" t="n">
-        <v>0.0532274959590931</v>
+        <v>0.0532274959590884</v>
       </c>
     </row>
     <row r="139">
@@ -29548,7 +29550,7 @@
         <v>0.0669748407123029</v>
       </c>
       <c r="E139" t="n">
-        <v>0.052505526129308</v>
+        <v>0.0525055261293032</v>
       </c>
     </row>
     <row r="140">
@@ -29565,7 +29567,7 @@
         <v>0.0648767683602012</v>
       </c>
       <c r="E140" t="n">
-        <v>0.0517933489907952</v>
+        <v>0.0517933489907901</v>
       </c>
     </row>
     <row r="141">
@@ -29582,7 +29584,7 @@
         <v>0.0621932007607709</v>
       </c>
       <c r="E141" t="n">
-        <v>0.0510908317169481</v>
+        <v>0.0510908317169429</v>
       </c>
     </row>
     <row r="142">
@@ -29599,7 +29601,7 @@
         <v>0.0595096331613406</v>
       </c>
       <c r="E142" t="n">
-        <v>0.050397843282801</v>
+        <v>0.0503978432827956</v>
       </c>
     </row>
     <row r="143">
@@ -29616,7 +29618,7 @@
         <v>0.0568260655619103</v>
       </c>
       <c r="E143" t="n">
-        <v>0.0497142544405909</v>
+        <v>0.0497142544405853</v>
       </c>
     </row>
     <row r="144">
@@ -29633,7 +29635,7 @@
         <v>0.0541419079988634</v>
       </c>
       <c r="E144" t="n">
-        <v>0.0490399376956523</v>
+        <v>0.0490399376956466</v>
       </c>
     </row>
     <row r="145">
@@ -29650,7 +29652,7 @@
         <v>0.0514577504358166</v>
       </c>
       <c r="E145" t="n">
-        <v>0.0483747672826385</v>
+        <v>0.0483747672826326</v>
       </c>
     </row>
     <row r="146">
@@ -29667,7 +29669,7 @@
         <v>0.0487735928727697</v>
       </c>
       <c r="E146" t="n">
-        <v>0.0477186191420651</v>
+        <v>0.047718619142059</v>
       </c>
     </row>
     <row r="147">
@@ -29684,7 +29686,7 @@
         <v>0.0464856258293992</v>
       </c>
       <c r="E147" t="n">
-        <v>0.047071370897172</v>
+        <v>0.0470713708971658</v>
       </c>
     </row>
     <row r="148">
@@ -29701,7 +29703,7 @@
         <v>0.0441976587860287</v>
       </c>
       <c r="E148" t="n">
-        <v>0.0464329018310995</v>
+        <v>0.0464329018310931</v>
       </c>
     </row>
     <row r="149">
@@ -29718,7 +29720,7 @@
         <v>0.0419096917426581</v>
       </c>
       <c r="E149" t="n">
-        <v>0.0458030928643731</v>
+        <v>0.0458030928643666</v>
       </c>
     </row>
     <row r="150">
@@ -29735,7 +29737,7 @@
         <v>0.0402963708585038</v>
       </c>
       <c r="E150" t="n">
-        <v>0.0451818265326949</v>
+        <v>0.0451818265326883</v>
       </c>
     </row>
     <row r="151">
@@ -29752,7 +29754,7 @@
         <v>0.0386830499743494</v>
       </c>
       <c r="E151" t="n">
-        <v>0.044568986965035</v>
+        <v>0.0445689869650282</v>
       </c>
     </row>
     <row r="152">
@@ -29769,7 +29771,7 @@
         <v>0.037069729090195</v>
       </c>
       <c r="E152" t="n">
-        <v>0.043964459862021</v>
+        <v>0.0439644598620141</v>
       </c>
     </row>
     <row r="153">
@@ -29786,7 +29788,7 @@
         <v>0.0365102183279321</v>
       </c>
       <c r="E153" t="n">
-        <v>0.0433681324746201</v>
+        <v>0.0433681324746131</v>
       </c>
     </row>
     <row r="154">
@@ -29803,7 +29805,7 @@
         <v>0.0359507075656692</v>
       </c>
       <c r="E154" t="n">
-        <v>0.0427798935831107</v>
+        <v>0.0427798935831036</v>
       </c>
     </row>
     <row r="155">
@@ -29820,7 +29822,7 @@
         <v>0.0353911968034063</v>
       </c>
       <c r="E155" t="n">
-        <v>0.0421996334763388</v>
+        <v>0.0421996334763316</v>
       </c>
     </row>
     <row r="156">
@@ -29837,7 +29839,7 @@
         <v>0.0352242210679906</v>
       </c>
       <c r="E156" t="n">
-        <v>0.0416272439312563</v>
+        <v>0.041627243931249</v>
       </c>
     </row>
     <row r="157">
@@ -29854,7 +29856,7 @@
         <v>0.035057245332575</v>
       </c>
       <c r="E157" t="n">
-        <v>0.0410626181927364</v>
+        <v>0.0410626181927289</v>
       </c>
     </row>
     <row r="158">
@@ -29871,7 +29873,7 @@
         <v>0.0348902695971593</v>
       </c>
       <c r="E158" t="n">
-        <v>0.0405056509536627</v>
+        <v>0.0405056509536552</v>
       </c>
     </row>
     <row r="159">
@@ -29888,7 +29890,7 @@
         <v>0.0352373236055518</v>
       </c>
       <c r="E159" t="n">
-        <v>0.0399562383352892</v>
+        <v>0.0399562383352816</v>
       </c>
     </row>
     <row r="160">
@@ -29905,7 +29907,7 @@
         <v>0.0355843776139443</v>
       </c>
       <c r="E160" t="n">
-        <v>0.0394142778678656</v>
+        <v>0.0394142778678578</v>
       </c>
     </row>
     <row r="161">
@@ -29922,7 +29924,7 @@
         <v>0.0359314316223368</v>
       </c>
       <c r="E161" t="n">
-        <v>0.0388796684715258</v>
+        <v>0.038879668471518</v>
       </c>
     </row>
     <row r="162">
@@ -29939,7 +29941,7 @@
         <v>0.036670597495294</v>
       </c>
       <c r="E162" t="n">
-        <v>0.0383523104374364</v>
+        <v>0.0383523104374285</v>
       </c>
     </row>
     <row r="163">
@@ -29956,7 +29958,7 @@
         <v>0.0374097633682512</v>
       </c>
       <c r="E163" t="n">
-        <v>0.0378321054091995</v>
+        <v>0.0378321054091915</v>
       </c>
     </row>
     <row r="164">
@@ -29973,7 +29975,7 @@
         <v>0.0381489292412084</v>
       </c>
       <c r="E164" t="n">
-        <v>0.0390440101888203</v>
+        <v>0.0390440101888165</v>
       </c>
     </row>
     <row r="165">
@@ -29990,7 +29992,7 @@
         <v>0.0393599130645852</v>
       </c>
       <c r="E165" t="n">
-        <v>0.0403199459001833</v>
+        <v>0.0403199459001794</v>
       </c>
     </row>
     <row r="166">
@@ -30007,7 +30009,7 @@
         <v>0.040570896887962</v>
       </c>
       <c r="E166" t="n">
-        <v>0.0416375784539469</v>
+        <v>0.041637578453943</v>
       </c>
     </row>
     <row r="167">
@@ -30024,7 +30026,7 @@
         <v>0.0417818807113388</v>
       </c>
       <c r="E167" t="n">
-        <v>0.0429982704788475</v>
+        <v>0.0429982704788436</v>
       </c>
     </row>
     <row r="168">
@@ -30041,7 +30043,7 @@
         <v>0.0438895624274346</v>
       </c>
       <c r="E168" t="n">
-        <v>0.0444034291335422</v>
+        <v>0.0444034291335383</v>
       </c>
     </row>
     <row r="169">
@@ -30058,7 +30060,7 @@
         <v>0.0459972441435304</v>
       </c>
       <c r="E169" t="n">
-        <v>0.0458545075618201</v>
+        <v>0.0458545075618162</v>
       </c>
     </row>
     <row r="170">
@@ -30075,7 +30077,7 @@
         <v>0.0481049258596261</v>
       </c>
       <c r="E170" t="n">
-        <v>0.0473530063953708</v>
+        <v>0.0473530063953669</v>
       </c>
     </row>
     <row r="171">
@@ -30092,7 +30094,7 @@
         <v>0.0509578531798852</v>
       </c>
       <c r="E171" t="n">
-        <v>0.048900475305661</v>
+        <v>0.0489004753056571</v>
       </c>
     </row>
     <row r="172">
@@ -30109,7 +30111,7 @@
         <v>0.0538107805001442</v>
       </c>
       <c r="E172" t="n">
-        <v>0.0504985146065261</v>
+        <v>0.0504985146065223</v>
       </c>
     </row>
     <row r="173">
@@ -30126,7 +30128,7 @@
         <v>0.0566637078204032</v>
       </c>
       <c r="E173" t="n">
-        <v>0.0521487769091342</v>
+        <v>0.0521487769091302</v>
       </c>
     </row>
     <row r="174">
@@ -30143,7 +30145,7 @@
         <v>0.0589635465265577</v>
       </c>
       <c r="E174" t="n">
-        <v>0.0538529688310315</v>
+        <v>0.0538529688310276</v>
       </c>
     </row>
     <row r="175">
@@ -30160,7 +30162,7 @@
         <v>0.0612633852327123</v>
       </c>
       <c r="E175" t="n">
-        <v>0.0556128527610409</v>
+        <v>0.0556128527610371</v>
       </c>
     </row>
     <row r="176">
@@ -30177,7 +30179,7 @@
         <v>0.0635632239388668</v>
       </c>
       <c r="E176" t="n">
-        <v>0.0574302486818344</v>
+        <v>0.0574302486818306</v>
       </c>
     </row>
     <row r="177">
@@ -30194,7 +30196,7 @@
         <v>0.0651696274321297</v>
       </c>
       <c r="E177" t="n">
-        <v>0.059307036052067</v>
+        <v>0.0593070360520632</v>
       </c>
     </row>
     <row r="178">
@@ -30211,7 +30213,7 @@
         <v>0.0667760309253926</v>
       </c>
       <c r="E178" t="n">
-        <v>0.0612451557500173</v>
+        <v>0.0612451557500135</v>
       </c>
     </row>
     <row r="179">
@@ -30228,7 +30230,7 @@
         <v>0.0683824344186555</v>
       </c>
       <c r="E179" t="n">
-        <v>0.0632466120807455</v>
+        <v>0.0632466120807418</v>
       </c>
     </row>
     <row r="180">
@@ -30245,7 +30247,7 @@
         <v>0.0708046928987432</v>
       </c>
       <c r="E180" t="n">
-        <v>0.0653134748488443</v>
+        <v>0.0653134748488407</v>
       </c>
     </row>
     <row r="181">
@@ -30262,7 +30264,7 @@
         <v>0.0732269513788308</v>
       </c>
       <c r="E181" t="n">
-        <v>0.0674478814989253</v>
+        <v>0.0674478814989217</v>
       </c>
     </row>
     <row r="182">
@@ -30279,7 +30281,7 @@
         <v>0.0756492098589185</v>
       </c>
       <c r="E182" t="n">
-        <v>0.0696520393260559</v>
+        <v>0.0696520393260524</v>
       </c>
     </row>
     <row r="183">
@@ -30296,7 +30298,7 @@
         <v>0.0789633714666181</v>
       </c>
       <c r="E183" t="n">
-        <v>0.0719282277584322</v>
+        <v>0.0719282277584287</v>
       </c>
     </row>
     <row r="184">
@@ -30313,7 +30315,7 @@
         <v>0.0822775330743177</v>
       </c>
       <c r="E184" t="n">
-        <v>0.0742788007146474</v>
+        <v>0.074278800714644</v>
       </c>
     </row>
     <row r="185">
@@ -30330,7 +30332,7 @@
         <v>0.0855916946820174</v>
       </c>
       <c r="E185" t="n">
-        <v>0.0767061890379956</v>
+        <v>0.0767061890379923</v>
       </c>
     </row>
     <row r="186">
@@ -30347,7 +30349,7 @@
         <v>0.0896021243828024</v>
       </c>
       <c r="E186" t="n">
-        <v>0.0792129030103263</v>
+        <v>0.079212903010323</v>
       </c>
     </row>
     <row r="187">
@@ -30364,7 +30366,7 @@
         <v>0.0936125540835875</v>
       </c>
       <c r="E187" t="n">
-        <v>0.0818015349480504</v>
+        <v>0.0818015349480473</v>
       </c>
     </row>
     <row r="188">
@@ -30381,7 +30383,7 @@
         <v>0.0976229837843726</v>
       </c>
       <c r="E188" t="n">
-        <v>0.0844747618829826</v>
+        <v>0.0844747618829797</v>
       </c>
     </row>
     <row r="189">
@@ -30398,7 +30400,7 @@
         <v>0.102805504868052</v>
       </c>
       <c r="E189" t="n">
-        <v>0.0872353483307919</v>
+        <v>0.087235348330789</v>
       </c>
     </row>
     <row r="190">
@@ -30415,7 +30417,7 @@
         <v>0.107988025951732</v>
       </c>
       <c r="E190" t="n">
-        <v>0.0900861491499228</v>
+        <v>0.09008614914992</v>
       </c>
     </row>
     <row r="191">
@@ -30432,7 +30434,7 @@
         <v>0.113170547035412</v>
       </c>
       <c r="E191" t="n">
-        <v>0.093030112493946</v>
+        <v>0.0930301124939434</v>
       </c>
     </row>
     <row r="192">
@@ -30449,7 +30451,7 @@
         <v>0.118621371633391</v>
       </c>
       <c r="E192" t="n">
-        <v>0.0960702828603888</v>
+        <v>0.0960702828603864</v>
       </c>
     </row>
     <row r="193">
@@ -30466,7 +30468,7 @@
         <v>0.12407219623137</v>
       </c>
       <c r="E193" t="n">
-        <v>0.0992098042391996</v>
+        <v>0.0992098042391975</v>
       </c>
     </row>
     <row r="194">
@@ -30483,7 +30485,7 @@
         <v>0.129523020829349</v>
       </c>
       <c r="E194" t="n">
-        <v>0.102451923364104</v>
+        <v>0.102451923364102</v>
       </c>
     </row>
     <row r="195">
@@ -30500,7 +30502,7 @@
         <v>0.133255050719583</v>
       </c>
       <c r="E195" t="n">
-        <v>0.10579999307021</v>
+        <v>0.105799993070208</v>
       </c>
     </row>
     <row r="196">
@@ -30517,7 +30519,7 @@
         <v>0.136987080609816</v>
       </c>
       <c r="E196" t="n">
-        <v>0.109257475761342</v>
+        <v>0.10925747576134</v>
       </c>
     </row>
     <row r="197">
@@ -30534,7 +30536,7 @@
         <v>0.140719110500049</v>
       </c>
       <c r="E197" t="n">
-        <v>0.112827946990683</v>
+        <v>0.112827946990681</v>
       </c>
     </row>
     <row r="198">
@@ -30551,7 +30553,7 @@
         <v>0.143167855695475</v>
       </c>
       <c r="E198" t="n">
-        <v>0.116515099158428</v>
+        <v>0.116515099158427</v>
       </c>
     </row>
     <row r="199">
@@ -30568,7 +30570,7 @@
         <v>0.1456166008909</v>
       </c>
       <c r="E199" t="n">
-        <v>0.120322745330281</v>
+        <v>0.12032274533028</v>
       </c>
     </row>
     <row r="200">
@@ -30585,7 +30587,7 @@
         <v>0.148065346086325</v>
       </c>
       <c r="E200" t="n">
-        <v>0.124254823180729</v>
+        <v>0.124254823180728</v>
       </c>
     </row>
     <row r="201">
@@ -30636,7 +30638,7 @@
         <v>0.153701844328095</v>
       </c>
       <c r="E203" t="n">
-        <v>0.1368389791312</v>
+        <v>0.136838979131201</v>
       </c>
     </row>
     <row r="204">
@@ -30653,7 +30655,7 @@
         <v>0.15497808346027</v>
       </c>
       <c r="E204" t="n">
-        <v>0.141310797966806</v>
+        <v>0.141310797966807</v>
       </c>
     </row>
     <row r="205">
@@ -30670,7 +30672,7 @@
         <v>0.156254322592445</v>
       </c>
       <c r="E205" t="n">
-        <v>0.145928753260206</v>
+        <v>0.145928753260208</v>
       </c>
     </row>
     <row r="206">
@@ -30687,7 +30689,7 @@
         <v>0.157530561724619</v>
       </c>
       <c r="E206" t="n">
-        <v>0.150697620666472</v>
+        <v>0.150697620666474</v>
       </c>
     </row>
     <row r="207">
@@ -30704,7 +30706,7 @@
         <v>0.159122431072103</v>
       </c>
       <c r="E207" t="n">
-        <v>0.155622331906324</v>
+        <v>0.155622331906327</v>
       </c>
     </row>
     <row r="208">
@@ -30721,7 +30723,7 @@
         <v>0.160714300419586</v>
       </c>
       <c r="E208" t="n">
-        <v>0.16070797986627</v>
+        <v>0.160707979866272</v>
       </c>
     </row>
     <row r="209">
@@ -30738,7 +30740,7 @@
         <v>0.16230616976707</v>
       </c>
       <c r="E209" t="n">
-        <v>0.165959823865406</v>
+        <v>0.165959823865409</v>
       </c>
     </row>
     <row r="210">
@@ -30755,7 +30757,7 @@
         <v>0.164015892771449</v>
       </c>
       <c r="E210" t="n">
-        <v>0.171383295094342</v>
+        <v>0.171383295094347</v>
       </c>
     </row>
     <row r="211">
@@ -30772,7 +30774,7 @@
         <v>0.165725615775828</v>
       </c>
       <c r="E211" t="n">
-        <v>0.176984002231863</v>
+        <v>0.176984002231867</v>
       </c>
     </row>
     <row r="212">
@@ -30789,7 +30791,7 @@
         <v>0.167435338780208</v>
       </c>
       <c r="E212" t="n">
-        <v>0.182767737245133</v>
+        <v>0.182767737245138</v>
       </c>
     </row>
     <row r="213">
@@ -30806,7 +30808,7 @@
         <v>0.169240227554945</v>
       </c>
       <c r="E213" t="n">
-        <v>0.188740481379465</v>
+        <v>0.188740481379471</v>
       </c>
     </row>
     <row r="214">
@@ -30823,7 +30825,7 @@
         <v>0.171045116329683</v>
       </c>
       <c r="E214" t="n">
-        <v>0.194908411343812</v>
+        <v>0.194908411343819</v>
       </c>
     </row>
     <row r="215">
@@ -30840,7 +30842,7 @@
         <v>0.172850005104421</v>
       </c>
       <c r="E215" t="n">
-        <v>0.201277905698411</v>
+        <v>0.201277905698418</v>
       </c>
     </row>
     <row r="216">
@@ -30857,7 +30859,7 @@
         <v>0.174789554015267</v>
       </c>
       <c r="E216" t="n">
-        <v>0.207855551451164</v>
+        <v>0.207855551451173</v>
       </c>
     </row>
     <row r="217">
@@ -30874,7 +30876,7 @@
         <v>0.176729102926113</v>
       </c>
       <c r="E217" t="n">
-        <v>0.21464815086959</v>
+        <v>0.214648150869599</v>
       </c>
     </row>
   </sheetData>
